--- a/bani muzakki 2.xlsx
+++ b/bani muzakki 2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4dd770f5288dd514/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4dd770f5288dd514/Documents/GitHub/familyhood.my.id/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{107DCD37-E142-49A6-A5C7-C5890FD142B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{107DCD37-E142-49A6-A5C7-C5890FD142B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{870BD3E6-2C3D-4F2D-9816-F863933228ED}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5BB80F8E-BB6F-464C-9455-26EC13A679BF}"/>
   </bookViews>
@@ -44,7 +44,7 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="D36" authorId="0" shapeId="0" xr:uid="{AF1F46D2-AE81-41B2-8BCC-10330EF8BD9C}">
+    <comment ref="D37" authorId="0" shapeId="0" xr:uid="{AF1F46D2-AE81-41B2-8BCC-10330EF8BD9C}">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D40" authorId="0" shapeId="0" xr:uid="{C99F29C0-970A-46FD-88BD-45AA74722360}">
+    <comment ref="D41" authorId="0" shapeId="0" xr:uid="{C99F29C0-970A-46FD-88BD-45AA74722360}">
       <text>
         <r>
           <rPr>
@@ -68,7 +68,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D41" authorId="0" shapeId="0" xr:uid="{845CB564-AED8-4E26-A41F-687C241CAEB5}">
+    <comment ref="D42" authorId="0" shapeId="0" xr:uid="{845CB564-AED8-4E26-A41F-687C241CAEB5}">
       <text>
         <r>
           <rPr>
@@ -80,7 +80,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D50" authorId="0" shapeId="0" xr:uid="{E4BCF476-780D-452E-8F0F-E0E8B44286C5}">
+    <comment ref="D51" authorId="0" shapeId="0" xr:uid="{E4BCF476-780D-452E-8F0F-E0E8B44286C5}">
       <text>
         <r>
           <rPr>
@@ -92,7 +92,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D53" authorId="0" shapeId="0" xr:uid="{2BA95F4A-7354-4FDC-80BD-2133092C102B}">
+    <comment ref="D54" authorId="0" shapeId="0" xr:uid="{2BA95F4A-7354-4FDC-80BD-2133092C102B}">
       <text>
         <r>
           <rPr>
@@ -104,7 +104,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D79" authorId="0" shapeId="0" xr:uid="{462043AC-24E8-4B01-BF3B-DBCE99D58342}">
+    <comment ref="D80" authorId="0" shapeId="0" xr:uid="{462043AC-24E8-4B01-BF3B-DBCE99D58342}">
       <text>
         <r>
           <rPr>
@@ -116,7 +116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C81" authorId="0" shapeId="0" xr:uid="{FB1C37D4-72C2-4D9F-A3A1-BE7E0FCFA979}">
+    <comment ref="C82" authorId="0" shapeId="0" xr:uid="{FB1C37D4-72C2-4D9F-A3A1-BE7E0FCFA979}">
       <text>
         <r>
           <rPr>
@@ -128,7 +128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D101" authorId="0" shapeId="0" xr:uid="{B95DBADC-5274-4970-B2EF-BA6EDE495B32}">
+    <comment ref="D102" authorId="0" shapeId="0" xr:uid="{B95DBADC-5274-4970-B2EF-BA6EDE495B32}">
       <text>
         <r>
           <rPr>
@@ -140,7 +140,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D109" authorId="0" shapeId="0" xr:uid="{3D1FECAA-E9AC-469D-968C-B08407A7E555}">
+    <comment ref="D110" authorId="0" shapeId="0" xr:uid="{3D1FECAA-E9AC-469D-968C-B08407A7E555}">
       <text>
         <r>
           <rPr>
@@ -152,7 +152,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D126" authorId="0" shapeId="0" xr:uid="{652EA41B-5E8F-4E35-965E-DC62524B30E4}">
+    <comment ref="D127" authorId="0" shapeId="0" xr:uid="{652EA41B-5E8F-4E35-965E-DC62524B30E4}">
       <text>
         <r>
           <rPr>
@@ -164,7 +164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D131" authorId="0" shapeId="0" xr:uid="{EB3699E2-FEF4-456B-8D80-19A0E1F73915}">
+    <comment ref="D132" authorId="0" shapeId="0" xr:uid="{EB3699E2-FEF4-456B-8D80-19A0E1F73915}">
       <text>
         <r>
           <rPr>
@@ -177,7 +177,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E134" authorId="0" shapeId="0" xr:uid="{248F1982-A68D-4075-B49E-DFE7A3EEE35C}">
+    <comment ref="E135" authorId="0" shapeId="0" xr:uid="{248F1982-A68D-4075-B49E-DFE7A3EEE35C}">
       <text>
         <r>
           <rPr>
@@ -190,7 +190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D136" authorId="0" shapeId="0" xr:uid="{146CA70A-EBE9-449B-8DB8-250759CFD077}">
+    <comment ref="D137" authorId="0" shapeId="0" xr:uid="{146CA70A-EBE9-449B-8DB8-250759CFD077}">
       <text>
         <r>
           <rPr>
@@ -203,7 +203,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D153" authorId="0" shapeId="0" xr:uid="{F773B15B-9F7C-43C0-94D6-9AFFA8926436}">
+    <comment ref="D154" authorId="0" shapeId="0" xr:uid="{F773B15B-9F7C-43C0-94D6-9AFFA8926436}">
       <text>
         <r>
           <rPr>
@@ -215,7 +215,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E170" authorId="0" shapeId="0" xr:uid="{EF3CCB78-BD13-4482-8109-9AB59DD642A1}">
+    <comment ref="E171" authorId="0" shapeId="0" xr:uid="{EF3CCB78-BD13-4482-8109-9AB59DD642A1}">
       <text>
         <r>
           <rPr>
@@ -227,7 +227,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C179" authorId="0" shapeId="0" xr:uid="{5BDAADBF-92C0-4462-823A-597F00B6DA8B}">
+    <comment ref="C180" authorId="0" shapeId="0" xr:uid="{5BDAADBF-92C0-4462-823A-597F00B6DA8B}">
       <text>
         <r>
           <rPr>
@@ -239,7 +239,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C183" authorId="0" shapeId="0" xr:uid="{7115E3C1-ADBA-429A-AB3C-37FAE8BAC9C7}">
+    <comment ref="C184" authorId="0" shapeId="0" xr:uid="{7115E3C1-ADBA-429A-AB3C-37FAE8BAC9C7}">
       <text>
         <r>
           <rPr>
@@ -251,7 +251,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E230" authorId="0" shapeId="0" xr:uid="{EEE70887-3507-410D-908B-63439A987A79}">
+    <comment ref="E231" authorId="0" shapeId="0" xr:uid="{EEE70887-3507-410D-908B-63439A987A79}">
       <text>
         <r>
           <rPr>
@@ -264,7 +264,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D293" authorId="0" shapeId="0" xr:uid="{66A4E9CF-C1FD-417D-8D92-41FDF2D33936}">
+    <comment ref="D294" authorId="0" shapeId="0" xr:uid="{66A4E9CF-C1FD-417D-8D92-41FDF2D33936}">
       <text>
         <r>
           <rPr>
@@ -276,7 +276,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D315" authorId="0" shapeId="0" xr:uid="{F8960E51-4F3B-4B2F-AE76-558F4A32BC38}">
+    <comment ref="D316" authorId="0" shapeId="0" xr:uid="{F8960E51-4F3B-4B2F-AE76-558F4A32BC38}">
       <text>
         <r>
           <rPr>
@@ -293,7 +293,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="328">
   <si>
     <t>MUZAKKI + ZAKIYAH</t>
   </si>
@@ -1253,13 +1253,37 @@
   </si>
   <si>
     <t>SABIQ ZAIN MAKARIM</t>
+  </si>
+  <si>
+    <t>Generasi 1</t>
+  </si>
+  <si>
+    <t>Generasi 2</t>
+  </si>
+  <si>
+    <t>Generasi 3</t>
+  </si>
+  <si>
+    <t>Generasi 4</t>
+  </si>
+  <si>
+    <t>Generasi 5</t>
+  </si>
+  <si>
+    <t>Generasi 6</t>
+  </si>
+  <si>
+    <t>Generasi 7</t>
+  </si>
+  <si>
+    <t>Generasi 8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1273,13 +1297,25 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5E7EB"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1294,8 +1330,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1611,1613 +1648,1648 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C629E1E-B955-4A3C-B56E-5C952373FF63}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F320"/>
+  <dimension ref="A1:H362"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" customWidth="1"/>
-    <col min="3" max="6" width="4.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="56.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="67" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D5" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E6" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E7" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D8" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E9" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E10" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E11" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E12" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D13" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E14" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E15" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D16" t="s">
+    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="E17" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="18" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="E19" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C19" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D21" t="s">
+    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="E22" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="23" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="E27" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D27" t="s">
+    <row r="28" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="E28" t="s">
+    <row r="29" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="E29" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="F29" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="30" spans="3:6" x14ac:dyDescent="0.25">
       <c r="F30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="F31" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="E31" t="s">
+    <row r="32" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="E32" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="F32" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="33" spans="4:6" x14ac:dyDescent="0.25">
       <c r="F33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="4:6" x14ac:dyDescent="0.25">
       <c r="F34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="F35" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="E35" t="s">
+    <row r="36" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="E36" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D36" t="s">
+    <row r="37" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="E37" t="s">
+    <row r="38" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="E38" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="F38" t="s">
+    <row r="39" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="F39" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="E39" t="s">
+    <row r="40" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="E40" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D40" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="41" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D41" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="E42" t="s">
+    <row r="43" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="E43" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D43" t="s">
+    <row r="44" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="E44" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="45" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E45" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E49" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E50" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D50" t="s">
+    <row r="51" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D51" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E51" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="52" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E52" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E53" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="53" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D53" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="54" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D54" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D55" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="55" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E55" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="56" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E56" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E57" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D57" t="s">
+    <row r="58" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D58" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C58" t="s">
+    <row r="59" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C59" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D59" t="s">
+    <row r="60" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E60" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="61" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E62" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E63" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E64" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D64" t="s">
+    <row r="65" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D65" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E65" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="66" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E66" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="67" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E67" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E68" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E69" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D69" t="s">
+    <row r="70" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D70" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C70" t="s">
+    <row r="71" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C71" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D71" t="s">
+    <row r="72" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D72" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="72" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E72" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="73" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E73" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E74" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E75" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D75" t="s">
+    <row r="76" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D76" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="76" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E76" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="77" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E77" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="78" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E78" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E79" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D79" t="s">
+    <row r="80" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D80" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E80" t="s">
+    <row r="81" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E81" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C81" t="s">
+    <row r="82" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C82" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="82" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D82" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="83" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D83" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D84" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E84" t="s">
+    <row r="85" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E85" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D85" t="s">
+    <row r="86" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D86" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="86" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C86" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="87" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C87" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C88" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C89" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D89" t="s">
+    <row r="90" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D90" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E90" t="s">
+    <row r="91" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E91" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="91" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D91" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="92" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D92" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="93" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D93" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D94" t="s">
         <v>92</v>
-      </c>
-    </row>
-    <row r="94" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C94" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="95" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C95" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C96" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D96" t="s">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D97" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="E97" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E98" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E99" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="D99" t="s">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D100" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="E100" t="s">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E101" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="D101" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D102" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D103" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D104" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B104" t="s">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B105" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C105" t="s">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C106" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="D106" t="s">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D107" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="E107" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E108" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="109" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E109" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="D109" t="s">
+    <row r="110" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D110" t="s">
         <v>108</v>
-      </c>
-    </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="E110" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E111" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E112" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="113" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E113" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="114" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E114" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D114" t="s">
+    <row r="115" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D115" t="s">
         <v>113</v>
-      </c>
-    </row>
-    <row r="115" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E115" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="116" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E116" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="117" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E117" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="118" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E118" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="119" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E119" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D119" t="s">
+    <row r="120" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D120" t="s">
         <v>118</v>
-      </c>
-    </row>
-    <row r="120" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E120" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="121" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E121" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="122" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E122" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D122" t="s">
+    <row r="123" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D123" t="s">
         <v>121</v>
-      </c>
-    </row>
-    <row r="123" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E123" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="124" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E124" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="125" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E125" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C125" t="s">
+    <row r="126" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C126" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D126" t="s">
+    <row r="127" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D127" t="s">
         <v>125</v>
-      </c>
-    </row>
-    <row r="127" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E127" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="128" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E128" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="129" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E129" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D129" t="s">
+    <row r="130" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D130" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E130" t="s">
+    <row r="131" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E131" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D131" t="s">
+    <row r="132" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D132" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E132" t="s">
+    <row r="133" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E133" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D133" t="s">
+    <row r="134" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D134" t="s">
         <v>132</v>
-      </c>
-    </row>
-    <row r="134" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E134" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="135" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E135" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="136" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E136" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D136" t="s">
+    <row r="137" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D137" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E137" t="s">
+    <row r="138" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E138" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D138" t="s">
+    <row r="139" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D139" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E139" t="s">
+    <row r="140" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E140" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C140" t="s">
+    <row r="141" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C141" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D141" t="s">
+    <row r="142" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D142" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="142" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E142" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="143" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E143" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="144" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E144" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D144" t="s">
+    <row r="145" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D145" t="s">
         <v>143</v>
-      </c>
-    </row>
-    <row r="145" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E145" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="146" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E146" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="147" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E147" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C147" t="s">
+    <row r="148" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C148" t="s">
         <v>146</v>
-      </c>
-    </row>
-    <row r="148" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D148" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="149" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D149" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="150" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D150" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E150" t="s">
+    <row r="151" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E151" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D151" t="s">
+    <row r="152" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D152" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C152" t="s">
+    <row r="153" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C153" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D153" t="s">
+    <row r="154" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D154" t="s">
         <v>152</v>
-      </c>
-    </row>
-    <row r="154" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E154" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="155" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E155" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="156" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E156" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="156" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D156" t="s">
+    <row r="157" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D157" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="157" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C157" t="s">
+    <row r="158" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C158" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="158" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D158" t="s">
+    <row r="159" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D159" t="s">
         <v>157</v>
-      </c>
-    </row>
-    <row r="159" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E159" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="160" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E160" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="161" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E161" t="s">
         <v>159</v>
-      </c>
-    </row>
-    <row r="161" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D161" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="162" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D162" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="163" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D163" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="163" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C163" t="s">
+    <row r="164" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C164" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="164" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D164" t="s">
+    <row r="165" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D165" t="s">
         <v>163</v>
-      </c>
-    </row>
-    <row r="165" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E165" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="166" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E166" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="167" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E167" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="168" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E168" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="169" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E169" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="169" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D169" t="s">
+    <row r="170" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D170" t="s">
         <v>168</v>
-      </c>
-    </row>
-    <row r="170" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E170" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="171" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E171" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="172" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E172" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="173" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E173" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="174" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E174" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="175" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E175" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="176" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E176" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="176" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D176" t="s">
+    <row r="177" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D177" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="177" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E177" t="s">
+    <row r="178" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E178" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="178" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D178" t="s">
+    <row r="179" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D179" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="179" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C179" t="s">
+    <row r="180" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C180" t="s">
         <v>178</v>
-      </c>
-    </row>
-    <row r="180" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D180" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="181" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D181" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="182" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D182" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="183" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D183" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="183" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C183" t="s">
+    <row r="184" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C184" t="s">
         <v>182</v>
-      </c>
-    </row>
-    <row r="184" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D184" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="185" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D185" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="186" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D186" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="187" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D187" t="s">
         <v>185</v>
-      </c>
-    </row>
-    <row r="187" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C187" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="188" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C188" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="189" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C189" t="s">
         <v>187</v>
-      </c>
-    </row>
-    <row r="189" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D189" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="190" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D190" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="191" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D191" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="191" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E191" t="s">
+    <row r="192" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E192" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="192" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D192" t="s">
+    <row r="193" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D193" t="s">
         <v>191</v>
-      </c>
-    </row>
-    <row r="193" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E193" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="194" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E194" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="195" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E195" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="196" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E196" t="s">
         <v>194</v>
-      </c>
-    </row>
-    <row r="196" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D196" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="197" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D197" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="198" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D198" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="199" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D199" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="199" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C199" t="s">
+    <row r="200" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C200" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="200" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B200" t="s">
+    <row r="201" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B201" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="201" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C201" t="s">
+    <row r="202" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C202" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="202" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D202" t="s">
+    <row r="203" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D203" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="203" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E203" t="s">
+    <row r="204" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E204" t="s">
         <v>202</v>
-      </c>
-    </row>
-    <row r="204" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="F204" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="205" spans="2:6" x14ac:dyDescent="0.25">
       <c r="F205" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="206" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F206" t="s">
         <v>204</v>
-      </c>
-    </row>
-    <row r="206" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E206" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="207" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E207" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="208" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E208" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="208" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D208" t="s">
+    <row r="209" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D209" t="s">
         <v>207</v>
-      </c>
-    </row>
-    <row r="209" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="E209" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="210" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E210" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="211" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E211" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="212" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E212" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="213" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E213" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="214" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E214" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="215" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="E215" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="215" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D215" t="s">
+    <row r="216" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D216" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="216" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="E216" t="s">
+    <row r="217" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="E217" t="s">
         <v>215</v>
-      </c>
-    </row>
-    <row r="217" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="F217" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="218" spans="4:6" x14ac:dyDescent="0.25">
       <c r="F218" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="219" spans="4:6" x14ac:dyDescent="0.25">
       <c r="F219" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="220" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="F220" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="220" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="E220" t="s">
+    <row r="221" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="E221" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="221" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="F221" t="s">
+    <row r="222" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="F222" t="s">
         <v>220</v>
-      </c>
-    </row>
-    <row r="222" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="E222" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="223" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E223" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="224" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E224" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="225" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E225" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="226" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E226" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="227" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="E227" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="227" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D227" t="s">
+    <row r="228" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D228" t="s">
         <v>226</v>
-      </c>
-    </row>
-    <row r="228" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="E228" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="229" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E229" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="230" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E230" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="231" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E231" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="232" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E232" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="233" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="E233" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="233" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D233" t="s">
+    <row r="234" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D234" t="s">
         <v>232</v>
-      </c>
-    </row>
-    <row r="234" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="E234" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="235" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E235" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="236" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="E236" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="236" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D236" t="s">
+    <row r="237" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D237" t="s">
         <v>235</v>
-      </c>
-    </row>
-    <row r="237" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="E237" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="238" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E238" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="239" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="E239" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="239" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D239" t="s">
+    <row r="240" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D240" t="s">
         <v>238</v>
-      </c>
-    </row>
-    <row r="240" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="E240" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="241" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E241" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="242" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E242" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="243" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E243" t="s">
         <v>241</v>
-      </c>
-    </row>
-    <row r="243" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C243" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="244" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C244" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="245" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C245" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="245" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D245" t="s">
+    <row r="246" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D246" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="246" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E246" t="s">
+    <row r="247" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E247" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="247" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D247" t="s">
+    <row r="248" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D248" t="s">
         <v>246</v>
-      </c>
-    </row>
-    <row r="248" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E248" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="249" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E249" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="250" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E250" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="251" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E251" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="251" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D251" t="s">
+    <row r="252" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D252" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="252" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E252" t="s">
+    <row r="253" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E253" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="253" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D253" t="s">
+    <row r="254" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D254" t="s">
         <v>252</v>
-      </c>
-    </row>
-    <row r="254" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E254" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="255" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E255" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="256" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E256" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="256" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D256" t="s">
+    <row r="257" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D257" t="s">
         <v>255</v>
-      </c>
-    </row>
-    <row r="257" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E257" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="258" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E258" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="259" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E259" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="260" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E260" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="260" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C260" t="s">
+    <row r="261" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C261" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="261" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D261" t="s">
+    <row r="262" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D262" t="s">
         <v>260</v>
-      </c>
-    </row>
-    <row r="262" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E262" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="263" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E263" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="264" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E264" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="265" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E265" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="266" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E266" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="266" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D266" t="s">
+    <row r="267" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D267" t="s">
         <v>265</v>
-      </c>
-    </row>
-    <row r="267" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E267" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="268" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E268" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="269" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E269" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="270" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E270" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="270" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D270" t="s">
+    <row r="271" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D271" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="271" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C271" t="s">
+    <row r="272" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C272" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="272" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D272" t="s">
+    <row r="273" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D273" t="s">
         <v>271</v>
-      </c>
-    </row>
-    <row r="273" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E273" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="274" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E274" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="275" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E275" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="276" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E276" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="276" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D276" t="s">
+    <row r="277" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D277" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="277" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E277" t="s">
+    <row r="278" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E278" t="s">
         <v>276</v>
-      </c>
-    </row>
-    <row r="278" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D278" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="279" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D279" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="280" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D280" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="280" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C280" t="s">
+    <row r="281" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C281" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="281" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D281" t="s">
+    <row r="282" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D282" t="s">
         <v>280</v>
-      </c>
-    </row>
-    <row r="282" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E282" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="283" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E283" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="284" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E284" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="285" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E285" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="285" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D285" t="s">
+    <row r="286" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D286" t="s">
         <v>284</v>
-      </c>
-    </row>
-    <row r="286" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E286" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="287" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E287" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="288" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E288" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="289" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E289" t="s">
         <v>287</v>
-      </c>
-    </row>
-    <row r="289" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D289" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="290" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D290" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="291" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D291" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="291" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E291" t="s">
+    <row r="292" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E292" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="292" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C292" t="s">
+    <row r="293" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C293" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="293" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D293" t="s">
+    <row r="294" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D294" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="294" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C294" t="s">
+    <row r="295" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C295" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="295" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D295" t="s">
+    <row r="296" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D296" t="s">
         <v>294</v>
-      </c>
-    </row>
-    <row r="296" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E296" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="297" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E297" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="298" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E298" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="299" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E299" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="299" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D299" t="s">
+    <row r="300" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D300" t="s">
         <v>298</v>
-      </c>
-    </row>
-    <row r="300" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E300" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="301" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E301" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="302" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E302" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="303" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E303" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="303" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D303" t="s">
+    <row r="304" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D304" t="s">
         <v>302</v>
-      </c>
-    </row>
-    <row r="304" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E304" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="305" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E305" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="306" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E306" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="307" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E307" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="308" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E308" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="309" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E309" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="309" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D309" t="s">
+    <row r="310" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D310" t="s">
         <v>308</v>
-      </c>
-    </row>
-    <row r="310" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E310" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="311" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E311" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="312" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E312" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="313" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E313" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="313" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D313" t="s">
+    <row r="314" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D314" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="314" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C314" t="s">
+    <row r="315" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C315" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="315" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D315" t="s">
+    <row r="316" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D316" t="s">
         <v>314</v>
-      </c>
-    </row>
-    <row r="316" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C316" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="317" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C317" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="318" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C318" t="s">
         <v>316</v>
-      </c>
-    </row>
-    <row r="318" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D318" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="319" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D319" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="320" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D320" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="321" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D321" t="s">
         <v>319</v>
+      </c>
+    </row>
+    <row r="362" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F362">
+        <f>COUNTA(F2:F361)</f>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/bani muzakki 2.xlsx
+++ b/bani muzakki 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4dd770f5288dd514/Documents/GitHub/familyhood.my.id/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{107DCD37-E142-49A6-A5C7-C5890FD142B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{870BD3E6-2C3D-4F2D-9816-F863933228ED}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{107DCD37-E142-49A6-A5C7-C5890FD142B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1786E367-F2F0-4A54-A4C7-2C9C66DF4E48}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5BB80F8E-BB6F-464C-9455-26EC13A679BF}"/>
   </bookViews>
@@ -293,7 +293,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="326">
   <si>
     <t>MUZAKKI + ZAKIYAH</t>
   </si>
@@ -1271,12 +1271,6 @@
   </si>
   <si>
     <t>Generasi 6</t>
-  </si>
-  <si>
-    <t>Generasi 7</t>
-  </si>
-  <si>
-    <t>Generasi 8</t>
   </si>
 </sst>
 </file>
@@ -1348,6 +1342,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1648,7 +1646,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C629E1E-B955-4A3C-B56E-5C952373FF63}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H362"/>
+  <dimension ref="A1:F362"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -1657,10 +1655,9 @@
     <col min="4" max="4" width="67" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="56.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>320</v>
       </c>
@@ -1679,84 +1676,78 @@
       <c r="F1" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
         <v>14</v>
       </c>

--- a/bani muzakki 2.xlsx
+++ b/bani muzakki 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4dd770f5288dd514/Documents/GitHub/familyhood.my.id/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{107DCD37-E142-49A6-A5C7-C5890FD142B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1786E367-F2F0-4A54-A4C7-2C9C66DF4E48}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{107DCD37-E142-49A6-A5C7-C5890FD142B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D12EDC8A-B394-43F1-91E2-CF16B48B558C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5BB80F8E-BB6F-464C-9455-26EC13A679BF}"/>
   </bookViews>
@@ -44,7 +44,7 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="D37" authorId="0" shapeId="0" xr:uid="{AF1F46D2-AE81-41B2-8BCC-10330EF8BD9C}">
+    <comment ref="D36" authorId="0" shapeId="0" xr:uid="{AF1F46D2-AE81-41B2-8BCC-10330EF8BD9C}">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D41" authorId="0" shapeId="0" xr:uid="{C99F29C0-970A-46FD-88BD-45AA74722360}">
+    <comment ref="D40" authorId="0" shapeId="0" xr:uid="{C99F29C0-970A-46FD-88BD-45AA74722360}">
       <text>
         <r>
           <rPr>
@@ -68,7 +68,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D42" authorId="0" shapeId="0" xr:uid="{845CB564-AED8-4E26-A41F-687C241CAEB5}">
+    <comment ref="D41" authorId="0" shapeId="0" xr:uid="{845CB564-AED8-4E26-A41F-687C241CAEB5}">
       <text>
         <r>
           <rPr>
@@ -80,7 +80,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D51" authorId="0" shapeId="0" xr:uid="{E4BCF476-780D-452E-8F0F-E0E8B44286C5}">
+    <comment ref="D50" authorId="0" shapeId="0" xr:uid="{E4BCF476-780D-452E-8F0F-E0E8B44286C5}">
       <text>
         <r>
           <rPr>
@@ -92,7 +92,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D54" authorId="0" shapeId="0" xr:uid="{2BA95F4A-7354-4FDC-80BD-2133092C102B}">
+    <comment ref="D53" authorId="0" shapeId="0" xr:uid="{2BA95F4A-7354-4FDC-80BD-2133092C102B}">
       <text>
         <r>
           <rPr>
@@ -104,7 +104,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D80" authorId="0" shapeId="0" xr:uid="{462043AC-24E8-4B01-BF3B-DBCE99D58342}">
+    <comment ref="D79" authorId="0" shapeId="0" xr:uid="{462043AC-24E8-4B01-BF3B-DBCE99D58342}">
       <text>
         <r>
           <rPr>
@@ -116,7 +116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C82" authorId="0" shapeId="0" xr:uid="{FB1C37D4-72C2-4D9F-A3A1-BE7E0FCFA979}">
+    <comment ref="C81" authorId="0" shapeId="0" xr:uid="{FB1C37D4-72C2-4D9F-A3A1-BE7E0FCFA979}">
       <text>
         <r>
           <rPr>
@@ -128,7 +128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D102" authorId="0" shapeId="0" xr:uid="{B95DBADC-5274-4970-B2EF-BA6EDE495B32}">
+    <comment ref="D101" authorId="0" shapeId="0" xr:uid="{B95DBADC-5274-4970-B2EF-BA6EDE495B32}">
       <text>
         <r>
           <rPr>
@@ -140,7 +140,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D110" authorId="0" shapeId="0" xr:uid="{3D1FECAA-E9AC-469D-968C-B08407A7E555}">
+    <comment ref="D109" authorId="0" shapeId="0" xr:uid="{3D1FECAA-E9AC-469D-968C-B08407A7E555}">
       <text>
         <r>
           <rPr>
@@ -152,7 +152,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D127" authorId="0" shapeId="0" xr:uid="{652EA41B-5E8F-4E35-965E-DC62524B30E4}">
+    <comment ref="D126" authorId="0" shapeId="0" xr:uid="{652EA41B-5E8F-4E35-965E-DC62524B30E4}">
       <text>
         <r>
           <rPr>
@@ -164,7 +164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D132" authorId="0" shapeId="0" xr:uid="{EB3699E2-FEF4-456B-8D80-19A0E1F73915}">
+    <comment ref="D131" authorId="0" shapeId="0" xr:uid="{EB3699E2-FEF4-456B-8D80-19A0E1F73915}">
       <text>
         <r>
           <rPr>
@@ -177,7 +177,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E135" authorId="0" shapeId="0" xr:uid="{248F1982-A68D-4075-B49E-DFE7A3EEE35C}">
+    <comment ref="E134" authorId="0" shapeId="0" xr:uid="{248F1982-A68D-4075-B49E-DFE7A3EEE35C}">
       <text>
         <r>
           <rPr>
@@ -190,7 +190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D137" authorId="0" shapeId="0" xr:uid="{146CA70A-EBE9-449B-8DB8-250759CFD077}">
+    <comment ref="D136" authorId="0" shapeId="0" xr:uid="{146CA70A-EBE9-449B-8DB8-250759CFD077}">
       <text>
         <r>
           <rPr>
@@ -203,7 +203,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D154" authorId="0" shapeId="0" xr:uid="{F773B15B-9F7C-43C0-94D6-9AFFA8926436}">
+    <comment ref="D153" authorId="0" shapeId="0" xr:uid="{F773B15B-9F7C-43C0-94D6-9AFFA8926436}">
       <text>
         <r>
           <rPr>
@@ -215,7 +215,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E171" authorId="0" shapeId="0" xr:uid="{EF3CCB78-BD13-4482-8109-9AB59DD642A1}">
+    <comment ref="E170" authorId="0" shapeId="0" xr:uid="{EF3CCB78-BD13-4482-8109-9AB59DD642A1}">
       <text>
         <r>
           <rPr>
@@ -227,7 +227,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C180" authorId="0" shapeId="0" xr:uid="{5BDAADBF-92C0-4462-823A-597F00B6DA8B}">
+    <comment ref="C179" authorId="0" shapeId="0" xr:uid="{5BDAADBF-92C0-4462-823A-597F00B6DA8B}">
       <text>
         <r>
           <rPr>
@@ -239,7 +239,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C184" authorId="0" shapeId="0" xr:uid="{7115E3C1-ADBA-429A-AB3C-37FAE8BAC9C7}">
+    <comment ref="C183" authorId="0" shapeId="0" xr:uid="{7115E3C1-ADBA-429A-AB3C-37FAE8BAC9C7}">
       <text>
         <r>
           <rPr>
@@ -251,7 +251,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E231" authorId="0" shapeId="0" xr:uid="{EEE70887-3507-410D-908B-63439A987A79}">
+    <comment ref="E230" authorId="0" shapeId="0" xr:uid="{EEE70887-3507-410D-908B-63439A987A79}">
       <text>
         <r>
           <rPr>
@@ -264,7 +264,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D294" authorId="0" shapeId="0" xr:uid="{66A4E9CF-C1FD-417D-8D92-41FDF2D33936}">
+    <comment ref="D293" authorId="0" shapeId="0" xr:uid="{66A4E9CF-C1FD-417D-8D92-41FDF2D33936}">
       <text>
         <r>
           <rPr>
@@ -276,7 +276,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D316" authorId="0" shapeId="0" xr:uid="{F8960E51-4F3B-4B2F-AE76-558F4A32BC38}">
+    <comment ref="D315" authorId="0" shapeId="0" xr:uid="{F8960E51-4F3B-4B2F-AE76-558F4A32BC38}">
       <text>
         <r>
           <rPr>
@@ -293,20 +293,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="320">
   <si>
     <t>MUZAKKI + ZAKIYAH</t>
   </si>
   <si>
-    <t xml:space="preserve"> ZUBAIDAH  + SHOLEH  + SHOLIHAHSULIHA Rabu malam Kamis, </t>
-  </si>
-  <si>
-    <t>ROFI'AH Alm</t>
-  </si>
-  <si>
-    <t>MALIHAH Alm  + ABDULLAH ABBAS Alm</t>
-  </si>
-  <si>
     <t>M NUR CHOLIS + USWATUN HASANAH</t>
   </si>
   <si>
@@ -322,9 +313,6 @@
     <t>AZZA MAISHARANI KHOIRUNNISA'</t>
   </si>
   <si>
-    <t>AZZA ALMIRA LALITYA</t>
-  </si>
-  <si>
     <t>AZZA SYAKIRA HASNA</t>
   </si>
   <si>
@@ -349,12 +337,6 @@
     <t>MUHAMMAD FAKHRI HASYIM</t>
   </si>
   <si>
-    <t>TOHA Alm waktu kecil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DJAMALIAH Alm  + SHOLEH BAIDLOWIAlm </t>
-  </si>
-  <si>
     <t>A MACHLUS SADAT + MAS'ULAH SIKHA AFIAH</t>
   </si>
   <si>
@@ -370,12 +352,6 @@
     <t>AHMAD FAKHRY AKRAMUSADAT</t>
   </si>
   <si>
-    <t>ALEESHA RALINE SALSABILA SADAT Kamis,</t>
-  </si>
-  <si>
-    <t>A MUCHLIS RIZAT Ahad Pon,  + USWATUN HASANAH</t>
-  </si>
-  <si>
     <t>SALIMATUL MAKKIYAH + M NAUFAL ZUHDI</t>
   </si>
   <si>
@@ -442,9 +418,6 @@
     <t>ASIAH AROFAT</t>
   </si>
   <si>
-    <t>MAZIDATUL FAIQOH Kamis Wage, + KHOTIB</t>
-  </si>
-  <si>
     <t>M ZAHID</t>
   </si>
   <si>
@@ -535,9 +508,6 @@
     <t>IBNU KHAIRUL AZZAM</t>
   </si>
   <si>
-    <t>FAHRUR ROZI Jumat,+ KHOIRIYAH</t>
-  </si>
-  <si>
     <t>FILDA QURROTU AINI + M NUR KHOZIN</t>
   </si>
   <si>
@@ -550,15 +520,6 @@
     <t>CHAURA ELMATLUBAH LUTFIAH</t>
   </si>
   <si>
-    <t>FAHRUR ROZI Jumat, + MAS'UDAH Jumat,</t>
-  </si>
-  <si>
-    <t>HABIBAH Alm Jumat,</t>
-  </si>
-  <si>
-    <t>M ZAKARIYAH Senin Kliwon, + IZZA MUFLIKAH</t>
-  </si>
-  <si>
     <t>LATHIFAH SAFARAH FALIH + RICCY VINDY PUTRA PERMANA</t>
   </si>
   <si>
@@ -574,9 +535,6 @@
     <t>HANA ELZAHRAH</t>
   </si>
   <si>
-    <t>ISTIQOMAH Alm waktu kecil</t>
-  </si>
-  <si>
     <t>KHOTIB SHOLEH + SITI LATHIFATUS SUN'IYAH</t>
   </si>
   <si>
@@ -589,9 +547,6 @@
     <t>MUHAMMAD IBRAHIM CHALIM</t>
   </si>
   <si>
-    <t xml:space="preserve">AHMADANI MUHAMMAD KHALLAF+NUN FATHATUS SHIVA Kamis Pahing, </t>
-  </si>
-  <si>
     <t>KEN ALI AHMAD MULLA</t>
   </si>
   <si>
@@ -607,9 +562,6 @@
     <t xml:space="preserve"> SALMAH  + HASAN NOER </t>
   </si>
   <si>
-    <t xml:space="preserve">M ROZIQIN HASAN  Senin  + SITI ROSYIDAH Selasa </t>
-  </si>
-  <si>
     <t>MAIDATUL HUSNAH + KHOIRUR ROFIK YUDI ALAMSYAH</t>
   </si>
   <si>
@@ -667,9 +619,6 @@
     <t>ANNISA SALSABILA AHMAD</t>
   </si>
   <si>
-    <t>M RIDLO'I almKamis, + SITI MUDRIKAH</t>
-  </si>
-  <si>
     <t>MOH MACHRUS ALI + JAZILATUN NI'MAH ISTRI KE</t>
   </si>
   <si>
@@ -712,9 +661,6 @@
     <t>A RIFQI NAUFAL</t>
   </si>
   <si>
-    <t>A MADANI Jumat + UMMI KULSUM</t>
-  </si>
-  <si>
     <t>SITI MUZAYANAH + M AMBIYA'</t>
   </si>
   <si>
@@ -763,9 +709,6 @@
     <t>ISA HAIDAR YULIANSAH+TRIANA WULANDARI</t>
   </si>
   <si>
-    <t xml:space="preserve">MAS'UDAH HASAN + MUCHLISUL AMAL Sabtu, </t>
-  </si>
-  <si>
     <t>AHMAD SHODIQUL MASDUQ + ATIK WAHYUNI</t>
   </si>
   <si>
@@ -781,9 +724,6 @@
     <t>ANNISA MAULIDI SYAVIRA</t>
   </si>
   <si>
-    <t>MASFUFAH HASAN + M MUCHDLOR Rabu,</t>
-  </si>
-  <si>
     <t>M FARID SANTOSO + NOVI HARIANI PUSPITASARI</t>
   </si>
   <si>
@@ -829,9 +769,6 @@
     <t>ANNE SALMA</t>
   </si>
   <si>
-    <t>M USMAN HASAN Sabtu Pon, + NIKMATUL HASANAH</t>
-  </si>
-  <si>
     <t>FILDA NURIS SILVI</t>
   </si>
   <si>
@@ -841,27 +778,15 @@
     <t>RIFKA AMALIA IFADHA</t>
   </si>
   <si>
-    <t>UMAR HASAN + DEWI FATMA Alm</t>
-  </si>
-  <si>
     <t>MOH NASIR SAGAF</t>
   </si>
   <si>
-    <t xml:space="preserve">MOH FAISHOL FAQIH Kamis,  </t>
-  </si>
-  <si>
-    <t>M FAHAD</t>
-  </si>
-  <si>
     <t>UMAR HASAN + MASTURAH</t>
   </si>
   <si>
     <t xml:space="preserve">MASRUROH HASAN + M IMRON </t>
   </si>
   <si>
-    <t>MIHSAN Alm</t>
-  </si>
-  <si>
     <t>AMIN QUTBI+KATRIN LUMBAN TOBING</t>
   </si>
   <si>
@@ -889,15 +814,6 @@
     <t>RUQOYYAH</t>
   </si>
   <si>
-    <t xml:space="preserve">ABDUL HARIS  alm umur  bulan </t>
-  </si>
-  <si>
-    <t>QUDSIYAH  + DJAUHARI Jumat  + ALFIYAH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DJUWAIRIYAH Rabu,+MUHAMMAD AMIN Alm </t>
-  </si>
-  <si>
     <t>MUFLIHAH AMIN + MUKHLIS YAHYA</t>
   </si>
   <si>
@@ -916,9 +832,6 @@
     <t>SYAGIFA ALYAN FARUHA</t>
   </si>
   <si>
-    <t xml:space="preserve">MAWADDAH + ROQIB Senin Legi, </t>
-  </si>
-  <si>
     <t>MUYASSAROH</t>
   </si>
   <si>
@@ -973,9 +886,6 @@
     <t>MAJDI MUAYYAD</t>
   </si>
   <si>
-    <t>FITRIYAH + ABD MUQIT Ahad,</t>
-  </si>
-  <si>
     <t>M FATHULLOH</t>
   </si>
   <si>
@@ -1021,21 +931,12 @@
     <t>BADI'UZZAMAN MALFATIH AZMATKHAN</t>
   </si>
   <si>
-    <t>ROBI'AH ADAWIYAH Alm</t>
-  </si>
-  <si>
-    <t>SYAMSUDDIN DJAUHARI Selasa Pon, + NA'IMAH</t>
-  </si>
-  <si>
     <t>LU'AILI ADDINA + MIRZA FAILASUFI</t>
   </si>
   <si>
     <t>MUHAMMAD RASYID FACHRUDDIN</t>
   </si>
   <si>
-    <t>MIFTAHUL FARIHAH Ahad Pon, + RIZKI MUSTAFANI</t>
-  </si>
-  <si>
     <t>M ZUHDI FARIZ ALGHOZALI MACHFUD</t>
   </si>
   <si>
@@ -1072,9 +973,6 @@
     <t>MUHAMMAD AZAM ASHFIYAK</t>
   </si>
   <si>
-    <t xml:space="preserve">MUNIFAH Jumat Wage, + UBAIDILLAH UMAR Senin Wage,  </t>
-  </si>
-  <si>
     <t>FARAQLIT RAMDLAN + WI'AM MURAD</t>
   </si>
   <si>
@@ -1102,9 +1000,6 @@
     <t>MOHAMMAD ALWI HAKIM</t>
   </si>
   <si>
-    <t xml:space="preserve">BADRUT TAMAM Alm Mkh, </t>
-  </si>
-  <si>
     <t>M ASYIK DJAUHARI + NUR INDAH</t>
   </si>
   <si>
@@ -1132,9 +1027,6 @@
     <t>MOH IZZUL AUZAD</t>
   </si>
   <si>
-    <t xml:space="preserve">QIBTIYAH + SUADI Kamis Pahing, </t>
-  </si>
-  <si>
     <t>MIKYATUL ADIYAH + M SYIFA'UDDIN</t>
   </si>
   <si>
@@ -1168,15 +1060,9 @@
     <t>MUHAMMAD AHNAF SARFARAZ ZAYYAN</t>
   </si>
   <si>
-    <t>MUSTHOFA Alm + MAIDATUL JANNAH</t>
-  </si>
-  <si>
     <t>NUR FITROTUL KAMILA*</t>
   </si>
   <si>
-    <t>MARIYAH ULFA Senin Legi,  + ZAINUL MUROD</t>
-  </si>
-  <si>
     <t>WI'AM MURAD+ FARAQLIT RAMDLAN</t>
   </si>
   <si>
@@ -1255,29 +1141,125 @@
     <t>SABIQ ZAIN MAKARIM</t>
   </si>
   <si>
-    <t>Generasi 1</t>
-  </si>
-  <si>
-    <t>Generasi 2</t>
-  </si>
-  <si>
-    <t>Generasi 3</t>
-  </si>
-  <si>
-    <t>Generasi 4</t>
-  </si>
-  <si>
-    <t>Generasi 5</t>
-  </si>
-  <si>
-    <t>Generasi 6</t>
+    <t xml:space="preserve"> ZUBAIDAH  + SHOLEH  + SHOLIHAHSULIHA</t>
+  </si>
+  <si>
+    <t>ROFI'AH</t>
+  </si>
+  <si>
+    <t>MALIHAH + ABDULLAH ABBAS</t>
+  </si>
+  <si>
+    <t>AZZAIRA LALITYA</t>
+  </si>
+  <si>
+    <t>UMAR HASAN + DEWI FATMA</t>
+  </si>
+  <si>
+    <t>MIHSAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABDUL HARIS  umur  bulan </t>
+  </si>
+  <si>
+    <t>ROBI'AH ADAWIYAH</t>
+  </si>
+  <si>
+    <t>MUSTHOFA + MAIDATUL JANNAH</t>
+  </si>
+  <si>
+    <t>DJAMALIAH  + SHOLEH BAIDLOWIA</t>
+  </si>
+  <si>
+    <t>M F</t>
+  </si>
+  <si>
+    <t>A MADANI  + UMMI KULSUM</t>
+  </si>
+  <si>
+    <t>QUDSIYAH  + DJAUHARI   + ALFIYAH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M ROZIQIN HASAN    + SITI ROSYIDAH  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEESHA RALINE SALSABILA SADAT </t>
+  </si>
+  <si>
+    <t>A MUCHLIS RIZAT   + USWATUN HASANAH</t>
+  </si>
+  <si>
+    <t>MAZIDATUL FAIQOH   + KHOTIB</t>
+  </si>
+  <si>
+    <t>FAHRUR ROZI + KHOIRIYAH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAHRUR ROZI  + MAS'UDAH </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HABIBAH </t>
+  </si>
+  <si>
+    <t>M ZAKARIYAH   + IZZA MUFLIKAH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHMADANI MUHAMMAD KHALLAF+NUN FATHATUS SHIVA   </t>
+  </si>
+  <si>
+    <t>M RIDLO'I + SITI MUDRIKAH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAS'UDAH HASAN + MUCHLISUL AMAL  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MASFUFAH HASAN + M MUCHDLOR </t>
+  </si>
+  <si>
+    <t>M USMAN HASAN  + NIKMATUL HASANAH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOH FAISHOL FAQIH   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DJUWAIRIYAH +MUHAMMAD AMIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAWADDAH + ROQIB   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FITRIYAH + ABD MUQIT </t>
+  </si>
+  <si>
+    <t>SYAMSUDDIN DJAUHARI  + NA'IMAH</t>
+  </si>
+  <si>
+    <t>MIFTAHUL FARIHAH  + RIZKI MUSTAFANI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MUNIFAH   + UBAIDILLAH UMAR    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BADRUT TAMAM Mkh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QIBTIYAH + SUADI   </t>
+  </si>
+  <si>
+    <t>MARIYAH ULFA    + ZAINUL MUROD</t>
+  </si>
+  <si>
+    <t>TOHA</t>
+  </si>
+  <si>
+    <t>ISTIQOMAH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1291,25 +1273,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5E7EB"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1324,9 +1294,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1342,10 +1311,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1646,7 +1611,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C629E1E-B955-4A3C-B56E-5C952373FF63}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F362"/>
+  <dimension ref="A1:F361"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -1657,1629 +1622,1609 @@
     <col min="6" max="6" width="28.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D6" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E7" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E8" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D9" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E10" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E11" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E12" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E13" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D14" t="s">
+    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D17" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="18" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E18" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="E19" t="s">
-        <v>17</v>
+      <c r="C19" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>18</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C21" t="s">
-        <v>19</v>
+      <c r="D21" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D22" t="s">
-        <v>20</v>
+      <c r="E22" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E23" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E24" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E25" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E26" t="s">
-        <v>24</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="E27" t="s">
-        <v>25</v>
+      <c r="D27" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="28" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D28" t="s">
-        <v>26</v>
+      <c r="E28" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="E29" t="s">
-        <v>27</v>
+      <c r="F29" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="3:6" x14ac:dyDescent="0.25">
       <c r="F30" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="F31" t="s">
-        <v>29</v>
+      <c r="E31" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="E32" t="s">
-        <v>30</v>
+      <c r="F32" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="4:6" x14ac:dyDescent="0.25">
       <c r="F33" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="4:6" x14ac:dyDescent="0.25">
       <c r="F34" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="F35" t="s">
-        <v>33</v>
+      <c r="E35" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="E36" t="s">
-        <v>34</v>
+      <c r="D36" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D37" t="s">
-        <v>35</v>
+      <c r="E37" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="E38" t="s">
-        <v>36</v>
+      <c r="F38" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="39" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="F39" t="s">
-        <v>37</v>
+      <c r="E39" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="E40" t="s">
-        <v>38</v>
+      <c r="D40" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D41" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D42" t="s">
-        <v>40</v>
+      <c r="E42" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="E43" t="s">
-        <v>41</v>
+      <c r="D43" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="44" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D44" t="s">
-        <v>42</v>
+      <c r="E44" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E45" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E46" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E47" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E48" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E49" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E50" t="s">
-        <v>48</v>
+      <c r="D50" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="51" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D51" t="s">
-        <v>49</v>
+      <c r="E51" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E52" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E53" t="s">
-        <v>51</v>
+      <c r="D53" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="54" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D54" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D55" t="s">
-        <v>53</v>
+      <c r="E55" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E56" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E57" t="s">
-        <v>55</v>
+      <c r="D57" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D58" t="s">
-        <v>56</v>
+      <c r="C58" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C59" t="s">
-        <v>57</v>
+      <c r="D59" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D60" t="s">
-        <v>58</v>
+      <c r="E60" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E61" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E62" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E63" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E64" t="s">
-        <v>62</v>
+      <c r="D64" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D65" t="s">
-        <v>63</v>
+      <c r="E65" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E66" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E67" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E68" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E69" t="s">
-        <v>67</v>
+      <c r="D69" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="70" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D70" t="s">
-        <v>68</v>
+      <c r="C70" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C71" t="s">
-        <v>69</v>
+      <c r="D71" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="72" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D72" t="s">
-        <v>70</v>
+      <c r="E72" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="73" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E73" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="74" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E74" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="75" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E75" t="s">
-        <v>73</v>
+      <c r="D75" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="76" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D76" t="s">
-        <v>74</v>
+      <c r="E76" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="77" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E77" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="78" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E78" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="79" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E79" t="s">
-        <v>77</v>
+      <c r="D79" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="80" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D80" t="s">
-        <v>78</v>
+      <c r="E80" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="81" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E81" t="s">
-        <v>79</v>
+      <c r="C81" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="82" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C82" t="s">
-        <v>80</v>
+      <c r="D82" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="83" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D83" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="84" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D84" t="s">
-        <v>82</v>
+      <c r="E84" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="85" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E85" t="s">
-        <v>83</v>
+      <c r="D85" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="86" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D86" t="s">
-        <v>84</v>
+      <c r="C86" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="87" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C87" t="s">
-        <v>85</v>
+        <v>301</v>
       </c>
     </row>
     <row r="88" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C88" t="s">
-        <v>86</v>
+        <v>302</v>
       </c>
     </row>
     <row r="89" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C89" t="s">
-        <v>87</v>
+      <c r="D89" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="90" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D90" t="s">
-        <v>88</v>
+      <c r="E90" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="91" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E91" t="s">
-        <v>89</v>
+      <c r="D91" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="92" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D92" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="93" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D93" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D94" t="s">
-        <v>92</v>
+      <c r="C94" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="95" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C95" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C96" t="s">
-        <v>94</v>
+      <c r="D96" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="D97" t="s">
-        <v>95</v>
+      <c r="E97" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E98" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="E99" t="s">
-        <v>97</v>
+      <c r="D99" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="D100" t="s">
-        <v>98</v>
+      <c r="E100" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="E101" t="s">
-        <v>99</v>
+      <c r="D101" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D102" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D103" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="D104" t="s">
-        <v>102</v>
+      <c r="B104" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B105" t="s">
-        <v>103</v>
+      <c r="C105" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C106" t="s">
-        <v>104</v>
+      <c r="D106" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="D107" t="s">
-        <v>105</v>
+      <c r="E107" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E108" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="E109" t="s">
-        <v>107</v>
+      <c r="D109" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="D110" t="s">
-        <v>108</v>
+      <c r="E110" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E111" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E112" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="113" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E113" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
     </row>
     <row r="114" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E114" t="s">
-        <v>112</v>
+      <c r="D114" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="115" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D115" t="s">
-        <v>113</v>
+      <c r="E115" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="116" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E116" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="117" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E117" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="118" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E118" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="119" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E119" t="s">
-        <v>117</v>
+      <c r="D119" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="120" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D120" t="s">
-        <v>118</v>
+      <c r="E120" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="121" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E121" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
     </row>
     <row r="122" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E122" t="s">
-        <v>120</v>
+      <c r="D122" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="123" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D123" t="s">
-        <v>121</v>
+      <c r="E123" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="124" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E124" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="125" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E125" t="s">
-        <v>123</v>
+      <c r="C125" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="126" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C126" t="s">
-        <v>124</v>
+      <c r="D126" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="127" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D127" t="s">
-        <v>125</v>
+      <c r="E127" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="128" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E128" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
     </row>
     <row r="129" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E129" t="s">
-        <v>127</v>
+      <c r="D129" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="130" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D130" t="s">
-        <v>128</v>
+      <c r="E130" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="131" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E131" t="s">
-        <v>129</v>
+      <c r="D131" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="132" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D132" t="s">
-        <v>130</v>
+      <c r="E132" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="133" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E133" t="s">
-        <v>131</v>
+      <c r="D133" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="134" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D134" t="s">
-        <v>132</v>
+      <c r="E134" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="135" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E135" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
     </row>
     <row r="136" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E136" t="s">
-        <v>134</v>
+      <c r="D136" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="137" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D137" t="s">
-        <v>135</v>
+      <c r="E137" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="138" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E138" t="s">
-        <v>136</v>
+      <c r="D138" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="139" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D139" t="s">
-        <v>137</v>
+      <c r="E139" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="140" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E140" t="s">
-        <v>138</v>
+      <c r="C140" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="141" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C141" t="s">
-        <v>139</v>
+      <c r="D141" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="142" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D142" t="s">
-        <v>140</v>
+      <c r="E142" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="143" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E143" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
     </row>
     <row r="144" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E144" t="s">
-        <v>142</v>
+      <c r="D144" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="145" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D145" t="s">
-        <v>143</v>
+      <c r="E145" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="146" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E146" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
     </row>
     <row r="147" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E147" t="s">
-        <v>145</v>
+      <c r="C147" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="148" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C148" t="s">
-        <v>146</v>
+      <c r="D148" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="149" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D149" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
     </row>
     <row r="150" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D150" t="s">
-        <v>148</v>
+      <c r="E150" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="151" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E151" t="s">
-        <v>149</v>
+      <c r="D151" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="152" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D152" t="s">
-        <v>150</v>
+      <c r="C152" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="153" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C153" t="s">
-        <v>151</v>
+      <c r="D153" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="154" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D154" t="s">
-        <v>152</v>
+      <c r="E154" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="155" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E155" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
     </row>
     <row r="156" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E156" t="s">
-        <v>154</v>
+      <c r="D156" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="157" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D157" t="s">
-        <v>155</v>
+      <c r="C157" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="158" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C158" t="s">
-        <v>156</v>
+      <c r="D158" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="159" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D159" t="s">
-        <v>157</v>
+      <c r="E159" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="160" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E160" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
     </row>
     <row r="161" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E161" t="s">
-        <v>159</v>
+      <c r="D161" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="162" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D162" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
     </row>
     <row r="163" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D163" t="s">
-        <v>161</v>
+      <c r="C163" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="164" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C164" t="s">
-        <v>162</v>
+      <c r="D164" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="165" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D165" t="s">
-        <v>163</v>
+      <c r="E165" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="166" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E166" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
     </row>
     <row r="167" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E167" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
     </row>
     <row r="168" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E168" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
     </row>
     <row r="169" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E169" t="s">
-        <v>167</v>
+      <c r="D169" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="170" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D170" t="s">
-        <v>168</v>
+      <c r="E170" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="171" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E171" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="172" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E172" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
     </row>
     <row r="173" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E173" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
     </row>
     <row r="174" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E174" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
     </row>
     <row r="175" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E175" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
     </row>
     <row r="176" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E176" t="s">
-        <v>174</v>
+      <c r="D176" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="177" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D177" t="s">
-        <v>175</v>
+      <c r="E177" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="178" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E178" t="s">
-        <v>176</v>
+      <c r="D178" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="179" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D179" t="s">
-        <v>177</v>
+      <c r="C179" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="180" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C180" t="s">
-        <v>178</v>
+      <c r="D180" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="181" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D181" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
     </row>
     <row r="182" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D182" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
     </row>
     <row r="183" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D183" t="s">
-        <v>181</v>
+      <c r="C183" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="184" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C184" t="s">
-        <v>182</v>
+      <c r="D184" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="185" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D185" t="s">
-        <v>183</v>
+        <v>308</v>
       </c>
     </row>
     <row r="186" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D186" t="s">
-        <v>184</v>
+        <v>292</v>
       </c>
     </row>
     <row r="187" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D187" t="s">
-        <v>185</v>
+      <c r="C187" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="188" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C188" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
     </row>
     <row r="189" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C189" t="s">
-        <v>187</v>
+      <c r="D189" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="190" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D190" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
     </row>
     <row r="191" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D191" t="s">
-        <v>189</v>
+      <c r="E191" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="192" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E192" t="s">
-        <v>190</v>
+      <c r="D192" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="193" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D193" t="s">
-        <v>191</v>
+      <c r="E193" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="194" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E194" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
     </row>
     <row r="195" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E195" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="196" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E196" t="s">
-        <v>194</v>
+      <c r="D196" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="197" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D197" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
     </row>
     <row r="198" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D198" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
     </row>
     <row r="199" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D199" t="s">
-        <v>197</v>
+      <c r="C199" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="200" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C200" t="s">
-        <v>198</v>
+      <c r="B200" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="201" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B201" t="s">
-        <v>199</v>
+      <c r="C201" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="202" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C202" t="s">
-        <v>200</v>
+      <c r="D202" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="203" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D203" t="s">
-        <v>201</v>
+      <c r="E203" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="204" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E204" t="s">
-        <v>202</v>
+      <c r="F204" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="205" spans="2:6" x14ac:dyDescent="0.25">
       <c r="F205" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
     </row>
     <row r="206" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="F206" t="s">
-        <v>204</v>
+      <c r="E206" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="207" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E207" t="s">
-        <v>205</v>
+        <v>178</v>
       </c>
     </row>
     <row r="208" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E208" t="s">
-        <v>206</v>
+      <c r="D208" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="209" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D209" t="s">
-        <v>207</v>
+      <c r="E209" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="210" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E210" t="s">
-        <v>208</v>
+        <v>180</v>
       </c>
     </row>
     <row r="211" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E211" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
     </row>
     <row r="212" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E212" t="s">
-        <v>210</v>
+        <v>182</v>
       </c>
     </row>
     <row r="213" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E213" t="s">
-        <v>211</v>
+        <v>183</v>
       </c>
     </row>
     <row r="214" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E214" t="s">
-        <v>212</v>
+        <v>184</v>
       </c>
     </row>
     <row r="215" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="E215" t="s">
-        <v>213</v>
+      <c r="D215" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="216" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D216" t="s">
-        <v>214</v>
+      <c r="E216" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="217" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="E217" t="s">
-        <v>215</v>
+      <c r="F217" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="218" spans="4:6" x14ac:dyDescent="0.25">
       <c r="F218" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
     </row>
     <row r="219" spans="4:6" x14ac:dyDescent="0.25">
       <c r="F219" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
     </row>
     <row r="220" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="F220" t="s">
-        <v>218</v>
+      <c r="E220" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="221" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="E221" t="s">
-        <v>219</v>
+      <c r="F221" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="222" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="F222" t="s">
-        <v>220</v>
+      <c r="E222" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="223" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E223" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="224" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E224" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
     </row>
     <row r="225" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E225" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
     </row>
     <row r="226" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E226" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
     </row>
     <row r="227" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="E227" t="s">
-        <v>225</v>
+      <c r="D227" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="228" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D228" t="s">
-        <v>226</v>
+      <c r="E228" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="229" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E229" t="s">
-        <v>227</v>
+        <v>198</v>
       </c>
     </row>
     <row r="230" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E230" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
     </row>
     <row r="231" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E231" t="s">
-        <v>229</v>
+        <v>200</v>
       </c>
     </row>
     <row r="232" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E232" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
     </row>
     <row r="233" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="E233" t="s">
-        <v>231</v>
+      <c r="D233" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="234" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D234" t="s">
-        <v>232</v>
+      <c r="E234" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="235" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E235" t="s">
-        <v>233</v>
+        <v>204</v>
       </c>
     </row>
     <row r="236" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="E236" t="s">
-        <v>234</v>
+      <c r="D236" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="237" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D237" t="s">
-        <v>235</v>
+      <c r="E237" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="238" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E238" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
     </row>
     <row r="239" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="E239" t="s">
-        <v>237</v>
+      <c r="D239" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="240" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D240" t="s">
-        <v>238</v>
+      <c r="E240" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="241" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E241" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
     </row>
     <row r="242" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E242" t="s">
-        <v>240</v>
+        <v>211</v>
       </c>
     </row>
     <row r="243" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E243" t="s">
-        <v>241</v>
+      <c r="C243" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="244" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C244" t="s">
-        <v>242</v>
+        <v>312</v>
       </c>
     </row>
     <row r="245" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C245" t="s">
-        <v>243</v>
+      <c r="D245" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="246" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D246" t="s">
-        <v>244</v>
+      <c r="E246" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="247" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E247" t="s">
-        <v>245</v>
+      <c r="D247" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="248" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D248" t="s">
-        <v>246</v>
+      <c r="E248" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="249" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E249" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
     </row>
     <row r="250" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E250" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
     </row>
     <row r="251" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E251" t="s">
-        <v>249</v>
+      <c r="D251" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="252" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D252" t="s">
-        <v>250</v>
+      <c r="E252" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="253" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E253" t="s">
-        <v>251</v>
+      <c r="D253" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="254" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D254" t="s">
-        <v>252</v>
+      <c r="E254" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="255" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E255" t="s">
-        <v>253</v>
+        <v>221</v>
       </c>
     </row>
     <row r="256" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E256" t="s">
-        <v>254</v>
+      <c r="D256" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="257" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D257" t="s">
-        <v>255</v>
+      <c r="E257" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="258" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E258" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
     </row>
     <row r="259" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E259" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
     </row>
     <row r="260" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E260" t="s">
-        <v>258</v>
+      <c r="C260" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="261" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C261" t="s">
-        <v>259</v>
+      <c r="D261" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="262" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D262" t="s">
-        <v>260</v>
+      <c r="E262" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="263" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E263" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
     </row>
     <row r="264" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E264" t="s">
-        <v>262</v>
+        <v>229</v>
       </c>
     </row>
     <row r="265" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E265" t="s">
-        <v>263</v>
+        <v>230</v>
       </c>
     </row>
     <row r="266" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E266" t="s">
-        <v>264</v>
+      <c r="D266" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="267" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D267" t="s">
-        <v>265</v>
+      <c r="E267" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="268" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E268" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
     </row>
     <row r="269" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E269" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
     </row>
     <row r="270" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E270" t="s">
-        <v>268</v>
+      <c r="D270" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="271" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D271" t="s">
-        <v>269</v>
+      <c r="C271" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="272" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C272" t="s">
-        <v>270</v>
+      <c r="D272" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="273" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D273" t="s">
-        <v>271</v>
+      <c r="E273" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="274" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E274" t="s">
-        <v>272</v>
+        <v>238</v>
       </c>
     </row>
     <row r="275" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E275" t="s">
-        <v>273</v>
+        <v>239</v>
       </c>
     </row>
     <row r="276" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E276" t="s">
-        <v>274</v>
+      <c r="D276" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="277" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D277" t="s">
-        <v>275</v>
+      <c r="E277" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="278" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E278" t="s">
-        <v>276</v>
+      <c r="D278" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="279" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D279" t="s">
-        <v>277</v>
+        <v>243</v>
       </c>
     </row>
     <row r="280" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D280" t="s">
-        <v>278</v>
+      <c r="C280" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="281" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C281" t="s">
-        <v>279</v>
+      <c r="D281" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="282" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D282" t="s">
-        <v>280</v>
+      <c r="E282" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="283" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E283" t="s">
-        <v>281</v>
+        <v>246</v>
       </c>
     </row>
     <row r="284" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E284" t="s">
-        <v>282</v>
+        <v>247</v>
       </c>
     </row>
     <row r="285" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E285" t="s">
-        <v>283</v>
+      <c r="D285" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="286" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D286" t="s">
-        <v>284</v>
+      <c r="E286" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="287" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E287" t="s">
-        <v>285</v>
+        <v>250</v>
       </c>
     </row>
     <row r="288" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E288" t="s">
-        <v>286</v>
+        <v>251</v>
       </c>
     </row>
     <row r="289" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E289" t="s">
-        <v>287</v>
+      <c r="D289" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="290" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D290" t="s">
-        <v>288</v>
+        <v>253</v>
       </c>
     </row>
     <row r="291" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D291" t="s">
-        <v>289</v>
+      <c r="E291" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="292" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E292" t="s">
+      <c r="C292" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="293" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C293" t="s">
-        <v>291</v>
+      <c r="D293" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="294" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D294" t="s">
-        <v>292</v>
+      <c r="C294" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="295" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C295" t="s">
-        <v>293</v>
+      <c r="D295" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="296" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D296" t="s">
-        <v>294</v>
+      <c r="E296" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="297" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E297" t="s">
-        <v>295</v>
+        <v>258</v>
       </c>
     </row>
     <row r="298" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E298" t="s">
-        <v>296</v>
+        <v>259</v>
       </c>
     </row>
     <row r="299" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E299" t="s">
-        <v>297</v>
+      <c r="D299" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="300" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D300" t="s">
-        <v>298</v>
+      <c r="E300" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="301" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E301" t="s">
-        <v>299</v>
+        <v>262</v>
       </c>
     </row>
     <row r="302" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E302" t="s">
-        <v>300</v>
+        <v>263</v>
       </c>
     </row>
     <row r="303" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E303" t="s">
-        <v>301</v>
+      <c r="D303" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="304" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D304" t="s">
-        <v>302</v>
+      <c r="E304" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="305" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E305" t="s">
-        <v>303</v>
+        <v>266</v>
       </c>
     </row>
     <row r="306" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E306" t="s">
-        <v>304</v>
+        <v>267</v>
       </c>
     </row>
     <row r="307" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E307" t="s">
-        <v>305</v>
+        <v>268</v>
       </c>
     </row>
     <row r="308" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E308" t="s">
-        <v>306</v>
+        <v>269</v>
       </c>
     </row>
     <row r="309" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E309" t="s">
-        <v>307</v>
+      <c r="D309" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="310" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D310" t="s">
-        <v>308</v>
+      <c r="E310" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="311" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E311" t="s">
-        <v>309</v>
+        <v>272</v>
       </c>
     </row>
     <row r="312" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E312" t="s">
-        <v>310</v>
+        <v>273</v>
       </c>
     </row>
     <row r="313" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E313" t="s">
-        <v>311</v>
+      <c r="D313" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="314" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D314" t="s">
-        <v>312</v>
+      <c r="C314" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="315" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C315" t="s">
-        <v>313</v>
+      <c r="D315" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="316" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D316" t="s">
-        <v>314</v>
+      <c r="C316" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="317" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C317" t="s">
-        <v>315</v>
+        <v>278</v>
       </c>
     </row>
     <row r="318" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C318" t="s">
-        <v>316</v>
+      <c r="D318" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="319" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D319" t="s">
-        <v>317</v>
+        <v>280</v>
       </c>
     </row>
     <row r="320" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D320" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="321" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D321" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="362" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F362">
-        <f>COUNTA(F2:F361)</f>
+        <v>281</v>
+      </c>
+    </row>
+    <row r="361" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F361">
+        <f>COUNTA(F1:F360)</f>
         <v>12</v>
       </c>
     </row>

--- a/bani muzakki 2.xlsx
+++ b/bani muzakki 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4dd770f5288dd514/Documents/GitHub/familyhood.my.id/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{107DCD37-E142-49A6-A5C7-C5890FD142B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D12EDC8A-B394-43F1-91E2-CF16B48B558C}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="8_{107DCD37-E142-49A6-A5C7-C5890FD142B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9E8225F-FEF6-4455-8A28-7AFE388BC41C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5BB80F8E-BB6F-464C-9455-26EC13A679BF}"/>
   </bookViews>
@@ -293,7 +293,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="318">
   <si>
     <t>MUZAKKI + ZAKIYAH</t>
   </si>
@@ -307,9 +307,6 @@
     <t>NASYWA AZZAHRO</t>
   </si>
   <si>
-    <t>AHMAD ZAKY +  YUYUN DWI WAHYUNI</t>
-  </si>
-  <si>
     <t>AZZA MAISHARANI KHOIRUNNISA'</t>
   </si>
   <si>
@@ -328,9 +325,6 @@
     <t>AISYAH NAILA SABRINA</t>
   </si>
   <si>
-    <t>FAUZAN FR +  AINI ZAHIDAH</t>
-  </si>
-  <si>
     <t>JANEETA EMIRA SHABRIYA</t>
   </si>
   <si>
@@ -391,9 +385,6 @@
     <t>MASLUH ANI AMIROH + TRI SUSANTO</t>
   </si>
   <si>
-    <t>MUKHLAS ARAFAT  + FARIDA S</t>
-  </si>
-  <si>
     <t>QONITA AROFAT</t>
   </si>
   <si>
@@ -427,18 +418,12 @@
     <t>MAZIDATUL FAIQOH + SEMIL SANTOSO</t>
   </si>
   <si>
-    <t>ANISATUS SHOBIHAH  + MUHAMMAD YUNANDI</t>
-  </si>
-  <si>
     <t>VINA NIHLATUR RAJWA</t>
   </si>
   <si>
     <t>ARINA HILYA EL HUSNA</t>
   </si>
   <si>
-    <t>RATU HUMAIRO  + LUTFI AFANDI</t>
-  </si>
-  <si>
     <t>SYAFIUDDIN + SITI ZUMAROH</t>
   </si>
   <si>
@@ -559,9 +544,6 @@
     <t>GHAZI BI LATHAIFILLAH ELKHOTIB</t>
   </si>
   <si>
-    <t xml:space="preserve"> SALMAH  + HASAN NOER </t>
-  </si>
-  <si>
     <t>MAIDATUL HUSNAH + KHOIRUR ROFIK YUDI ALAMSYAH</t>
   </si>
   <si>
@@ -739,9 +721,6 @@
     <t>ABDULLAH HANIF</t>
   </si>
   <si>
-    <t>VIVIEN FARIDAH +  M YASIN</t>
-  </si>
-  <si>
     <t xml:space="preserve">SILATUL FARHAH RIHADATUL AISY ASFA* + </t>
   </si>
   <si>
@@ -1060,9 +1039,6 @@
     <t>MUHAMMAD AHNAF SARFARAZ ZAYYAN</t>
   </si>
   <si>
-    <t>NUR FITROTUL KAMILA*</t>
-  </si>
-  <si>
     <t>WI'AM MURAD+ FARAQLIT RAMDLAN</t>
   </si>
   <si>
@@ -1123,9 +1099,6 @@
     <t>DAMANHURI + NUR MASLAHAH</t>
   </si>
   <si>
-    <t>JINDAN AHMAD ASRORI*</t>
-  </si>
-  <si>
     <t>FADHILAH</t>
   </si>
   <si>
@@ -1141,9 +1114,6 @@
     <t>SABIQ ZAIN MAKARIM</t>
   </si>
   <si>
-    <t xml:space="preserve"> ZUBAIDAH  + SHOLEH  + SHOLIHAHSULIHA</t>
-  </si>
-  <si>
     <t>ROFI'AH</t>
   </si>
   <si>
@@ -1159,100 +1129,124 @@
     <t>MIHSAN</t>
   </si>
   <si>
-    <t xml:space="preserve">ABDUL HARIS  umur  bulan </t>
-  </si>
-  <si>
     <t>ROBI'AH ADAWIYAH</t>
   </si>
   <si>
     <t>MUSTHOFA + MAIDATUL JANNAH</t>
   </si>
   <si>
-    <t>DJAMALIAH  + SHOLEH BAIDLOWIA</t>
-  </si>
-  <si>
     <t>M F</t>
   </si>
   <si>
-    <t>A MADANI  + UMMI KULSUM</t>
-  </si>
-  <si>
-    <t>QUDSIYAH  + DJAUHARI   + ALFIYAH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M ROZIQIN HASAN    + SITI ROSYIDAH  </t>
-  </si>
-  <si>
     <t xml:space="preserve">ALEESHA RALINE SALSABILA SADAT </t>
   </si>
   <si>
-    <t>A MUCHLIS RIZAT   + USWATUN HASANAH</t>
-  </si>
-  <si>
-    <t>MAZIDATUL FAIQOH   + KHOTIB</t>
-  </si>
-  <si>
     <t>FAHRUR ROZI + KHOIRIYAH</t>
   </si>
   <si>
-    <t xml:space="preserve">FAHRUR ROZI  + MAS'UDAH </t>
-  </si>
-  <si>
     <t xml:space="preserve">HABIBAH </t>
   </si>
   <si>
-    <t>M ZAKARIYAH   + IZZA MUFLIKAH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHMADANI MUHAMMAD KHALLAF+NUN FATHATUS SHIVA   </t>
-  </si>
-  <si>
     <t>M RIDLO'I + SITI MUDRIKAH</t>
   </si>
   <si>
-    <t xml:space="preserve">MAS'UDAH HASAN + MUCHLISUL AMAL  </t>
-  </si>
-  <si>
     <t xml:space="preserve">MASFUFAH HASAN + M MUCHDLOR </t>
   </si>
   <si>
-    <t>M USMAN HASAN  + NIKMATUL HASANAH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOH FAISHOL FAQIH   </t>
-  </si>
-  <si>
     <t xml:space="preserve">DJUWAIRIYAH +MUHAMMAD AMIN </t>
   </si>
   <si>
-    <t xml:space="preserve">MAWADDAH + ROQIB   </t>
-  </si>
-  <si>
     <t xml:space="preserve">FITRIYAH + ABD MUQIT </t>
   </si>
   <si>
-    <t>SYAMSUDDIN DJAUHARI  + NA'IMAH</t>
-  </si>
-  <si>
-    <t>MIFTAHUL FARIHAH  + RIZKI MUSTAFANI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MUNIFAH   + UBAIDILLAH UMAR    </t>
-  </si>
-  <si>
     <t xml:space="preserve">BADRUT TAMAM Mkh </t>
   </si>
   <si>
-    <t xml:space="preserve">QIBTIYAH + SUADI   </t>
-  </si>
-  <si>
-    <t>MARIYAH ULFA    + ZAINUL MUROD</t>
-  </si>
-  <si>
     <t>TOHA</t>
   </si>
   <si>
     <t>ISTIQOMAH</t>
+  </si>
+  <si>
+    <t>ABDUL HARIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ZUBAIDAH + SHOLEH + SHOLIHAHSULIHA</t>
+  </si>
+  <si>
+    <t>AHMAD ZAKY + YUYUN DWI WAHYUNI</t>
+  </si>
+  <si>
+    <t>FAUZAN FR + AINI ZAHIDAH</t>
+  </si>
+  <si>
+    <t>DJAMALIAH + SHOLEH BAIDLOWIA</t>
+  </si>
+  <si>
+    <t>MUKHLAS ARAFAT + FARIDA S</t>
+  </si>
+  <si>
+    <t>ANISATUS SHOBIHAH + MUHAMMAD YUNANDI</t>
+  </si>
+  <si>
+    <t>RATU HUMAIRO + LUTFI AFANDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAHRUR ROZI + MAS'UDAH </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SALMAH + HASAN NOER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">M ROZIQIN HASAN + SITI ROSYIDAH </t>
+  </si>
+  <si>
+    <t>A MADANI + UMMI KULSUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAS'UDAH HASAN + MUCHLISUL AMAL </t>
+  </si>
+  <si>
+    <t>VIVIEN FARIDAH + M YASIN</t>
+  </si>
+  <si>
+    <t>M USMAN HASAN + NIKMATUL HASANAH</t>
+  </si>
+  <si>
+    <t>SYAMSUDDIN DJAUHARI + NA'IMAH</t>
+  </si>
+  <si>
+    <t>MIFTAHUL FARIHAH + RIZKI MUSTAFANI</t>
+  </si>
+  <si>
+    <t>A MUCHLIS RIZAT + USWATUN HASANAH</t>
+  </si>
+  <si>
+    <t>MAZIDATUL FAIQOH + KHOTIB</t>
+  </si>
+  <si>
+    <t>M ZAKARIYAH + IZZA MUFLIKAH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHMADANI MUHAMMAD KHALLAF+NUN FATHATUS SHIVA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOH FAISHOL FAQIH </t>
+  </si>
+  <si>
+    <t>QUDSIYAH + DJAUHARI + ALFIYAH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAWADDAH + ROQIB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MUNIFAH + UBAIDILLAH UMAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QIBTIYAH + SUADI </t>
+  </si>
+  <si>
+    <t>MARIYAH ULFA + ZAINUL MUROD</t>
   </si>
 </sst>
 </file>
@@ -1311,6 +1305,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1629,17 +1627,17 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1659,1362 +1657,1362 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>4</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
-        <v>11</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E17" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>318</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E23" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E24" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E25" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E26" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
     </row>
     <row r="27" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D27" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="28" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E28" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="3:6" x14ac:dyDescent="0.25">
       <c r="F29" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="3:6" x14ac:dyDescent="0.25">
       <c r="F30" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E31" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="3:6" x14ac:dyDescent="0.25">
       <c r="F32" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="4:6" x14ac:dyDescent="0.25">
       <c r="F33" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="4:6" x14ac:dyDescent="0.25">
       <c r="F34" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E35" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D36" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E37" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="4:6" x14ac:dyDescent="0.25">
       <c r="F38" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E39" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D40" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D41" t="s">
-        <v>32</v>
+        <v>296</v>
       </c>
     </row>
     <row r="42" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E42" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D43" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E44" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E45" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E46" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E47" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E48" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E49" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D50" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E51" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E52" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D53" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D54" t="s">
-        <v>44</v>
+        <v>297</v>
       </c>
     </row>
     <row r="55" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E55" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E56" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D57" t="s">
-        <v>47</v>
+        <v>298</v>
       </c>
     </row>
     <row r="58" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C58" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D59" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E60" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E61" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E62" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E63" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D64" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E65" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E66" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E67" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E68" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D69" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="71" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D71" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E72" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E73" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="74" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E74" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="75" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D75" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="76" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E76" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="77" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E77" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="78" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E78" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="79" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D79" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="80" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E80" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="81" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C81" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
     </row>
     <row r="82" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D82" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="83" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D83" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="84" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E84" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="85" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D85" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="86" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C86" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="87" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C87" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
     </row>
     <row r="88" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C88" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
     </row>
     <row r="89" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D89" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="90" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E90" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="91" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D91" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="92" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D92" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="93" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D93" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="94" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C94" t="s">
-        <v>319</v>
+        <v>290</v>
       </c>
     </row>
     <row r="95" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C95" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="96" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D96" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E97" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E98" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D99" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E100" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D101" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D102" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D103" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>88</v>
+        <v>300</v>
       </c>
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C105" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D106" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E107" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E108" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D109" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E110" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E111" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E112" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="113" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E113" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="114" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D114" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="115" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E115" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="116" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E116" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="117" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E117" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="118" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E118" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="119" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D119" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="120" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E120" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="121" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E121" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="122" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D122" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="123" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E123" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="124" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E124" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="125" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C125" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
     </row>
     <row r="126" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D126" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="127" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E127" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="128" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E128" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="129" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D129" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="130" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E130" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="131" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D131" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="132" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E132" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="133" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D133" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="134" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E134" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="135" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E135" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="136" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D136" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="137" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E137" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="138" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D138" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="139" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E139" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="140" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C140" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
     </row>
     <row r="141" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D141" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="142" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E142" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="143" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E143" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="144" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D144" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="145" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E145" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="146" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E146" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="147" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C147" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="148" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D148" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="149" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D149" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="150" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E150" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="151" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D151" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="152" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C152" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="153" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D153" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="154" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E154" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="155" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E155" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="156" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D156" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="157" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C157" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="158" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D158" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="159" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E159" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="160" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E160" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="161" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D161" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="162" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D162" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="163" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C163" t="s">
-        <v>306</v>
+        <v>285</v>
       </c>
     </row>
     <row r="164" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D164" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="165" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E165" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="166" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E166" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="167" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E167" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="168" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E168" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="169" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D169" t="s">
-        <v>148</v>
+        <v>304</v>
       </c>
     </row>
     <row r="170" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E170" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="171" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E171" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="172" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E172" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="173" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E173" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="174" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E174" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="175" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E175" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="176" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D176" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="177" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E177" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="178" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D178" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="179" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C179" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="180" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D180" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="181" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D181" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="182" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D182" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="183" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C183" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
     </row>
     <row r="184" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D184" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
     </row>
     <row r="185" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D185" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="186" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D186" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
     </row>
     <row r="187" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C187" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="188" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C188" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="189" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D189" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
     </row>
     <row r="190" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D190" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="191" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E191" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="192" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D192" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
     </row>
     <row r="193" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E193" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="194" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E194" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="195" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E195" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="196" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D196" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="197" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D197" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
     </row>
     <row r="198" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D198" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
     </row>
     <row r="199" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C199" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="200" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
     </row>
     <row r="201" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C201" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
     </row>
     <row r="202" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D202" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="203" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E203" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="204" spans="2:6" x14ac:dyDescent="0.25">
       <c r="F204" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="205" spans="2:6" x14ac:dyDescent="0.25">
       <c r="F205" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="206" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E206" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
     </row>
     <row r="207" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E207" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="208" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D208" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="209" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E209" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="210" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E210" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="211" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E211" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="212" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E212" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="213" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E213" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="214" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E214" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="215" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D215" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
     </row>
     <row r="216" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E216" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="217" spans="4:6" x14ac:dyDescent="0.25">
       <c r="F217" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="218" spans="4:6" x14ac:dyDescent="0.25">
       <c r="F218" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="219" spans="4:6" x14ac:dyDescent="0.25">
       <c r="F219" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="220" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E220" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="221" spans="4:6" x14ac:dyDescent="0.25">
       <c r="F221" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="222" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E222" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="223" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E223" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="224" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E224" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="225" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E225" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
     </row>
     <row r="226" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E226" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="227" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D227" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
     </row>
     <row r="228" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E228" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="229" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E229" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="230" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E230" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="231" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E231" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="232" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E232" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
     <row r="233" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D233" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="234" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E234" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="235" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E235" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="236" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D236" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="237" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E237" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="238" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E238" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="239" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D239" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="240" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E240" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="241" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E241" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="242" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E242" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="243" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C243" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
     </row>
     <row r="244" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C244" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="245" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D245" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="246" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E246" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
     </row>
     <row r="247" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D247" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="248" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E248" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="249" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E249" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="250" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E250" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="251" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D251" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="252" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E252" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="253" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D253" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="254" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E254" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="255" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E255" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
     </row>
     <row r="256" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D256" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
     </row>
     <row r="257" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E257" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
     </row>
     <row r="258" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E258" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
     </row>
     <row r="259" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E259" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="260" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C260" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="261" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D261" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
     <row r="262" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E262" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="263" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E263" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="264" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E264" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
     </row>
     <row r="265" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E265" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
     </row>
     <row r="266" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D266" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
     </row>
     <row r="267" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E267" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="268" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E268" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="269" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E269" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="270" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D270" t="s">
-        <v>315</v>
+        <v>288</v>
       </c>
     </row>
     <row r="271" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C271" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
     </row>
     <row r="272" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D272" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
     </row>
     <row r="273" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E273" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
     </row>
     <row r="274" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E274" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
     </row>
     <row r="275" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E275" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
     </row>
     <row r="276" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D276" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
     </row>
     <row r="277" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E277" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="278" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D278" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
     </row>
     <row r="279" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D279" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="280" spans="3:5" x14ac:dyDescent="0.25">
@@ -3024,67 +3022,67 @@
     </row>
     <row r="281" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D281" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
     </row>
     <row r="282" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E282" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
     <row r="283" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E283" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
     </row>
     <row r="284" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E284" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
     </row>
     <row r="285" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D285" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="286" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E286" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
     </row>
     <row r="287" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E287" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="288" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E288" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="289" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D289" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
     </row>
     <row r="290" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D290" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="291" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E291" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
     <row r="292" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C292" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
     </row>
     <row r="293" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D293" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
     </row>
     <row r="294" spans="3:5" x14ac:dyDescent="0.25">
@@ -3094,132 +3092,132 @@
     </row>
     <row r="295" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D295" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="296" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E296" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
     <row r="297" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E297" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="298" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E298" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
     </row>
     <row r="299" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D299" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
     </row>
     <row r="300" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E300" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
     </row>
     <row r="301" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E301" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="302" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E302" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="303" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D303" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="304" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E304" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="305" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E305" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
     </row>
     <row r="306" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E306" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="307" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E307" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="308" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E308" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
     </row>
     <row r="309" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D309" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="310" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E310" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="311" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E311" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="312" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E312" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="313" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D313" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="314" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C314" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
     </row>
     <row r="315" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D315" t="s">
-        <v>276</v>
+        <v>192</v>
       </c>
     </row>
     <row r="316" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C316" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="317" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C317" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
     </row>
     <row r="318" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D318" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
     </row>
     <row r="319" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D319" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
     </row>
     <row r="320" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D320" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="361" spans="6:6" x14ac:dyDescent="0.25">

--- a/bani muzakki 2.xlsx
+++ b/bani muzakki 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4dd770f5288dd514/Documents/GitHub/familyhood.my.id/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{107DCD37-E142-49A6-A5C7-C5890FD142B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9E8225F-FEF6-4455-8A28-7AFE388BC41C}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{107DCD37-E142-49A6-A5C7-C5890FD142B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D35A4742-D70D-4464-B59E-3EC3BE51B38F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5BB80F8E-BB6F-464C-9455-26EC13A679BF}"/>
   </bookViews>
@@ -1135,9 +1135,6 @@
     <t>MUSTHOFA + MAIDATUL JANNAH</t>
   </si>
   <si>
-    <t>M F</t>
-  </si>
-  <si>
     <t xml:space="preserve">ALEESHA RALINE SALSABILA SADAT </t>
   </si>
   <si>
@@ -1247,6 +1244,9 @@
   </si>
   <si>
     <t>MARIYAH ULFA + ZAINUL MUROD</t>
+  </si>
+  <si>
+    <t>M FAHAD</t>
   </si>
 </sst>
 </file>
@@ -1609,7 +1609,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C629E1E-B955-4A3C-B56E-5C952373FF63}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F361"/>
+  <dimension ref="A1:F320"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -1627,7 +1627,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1657,7 +1657,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1697,7 +1697,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17" spans="3:6" x14ac:dyDescent="0.25">
@@ -1712,12 +1712,12 @@
     </row>
     <row r="19" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
@@ -1747,12 +1747,12 @@
     </row>
     <row r="26" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E26" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D27" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="28" spans="3:6" x14ac:dyDescent="0.25">
@@ -1822,7 +1822,7 @@
     </row>
     <row r="41" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D41" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="42" spans="4:6" x14ac:dyDescent="0.25">
@@ -1867,7 +1867,7 @@
     </row>
     <row r="50" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D50" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="51" spans="3:5" x14ac:dyDescent="0.25">
@@ -1887,7 +1887,7 @@
     </row>
     <row r="54" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D54" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="55" spans="3:5" x14ac:dyDescent="0.25">
@@ -1902,7 +1902,7 @@
     </row>
     <row r="57" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D57" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="58" spans="3:5" x14ac:dyDescent="0.25">
@@ -2022,7 +2022,7 @@
     </row>
     <row r="81" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C81" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="82" spans="3:5" x14ac:dyDescent="0.25">
@@ -2047,17 +2047,17 @@
     </row>
     <row r="86" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C86" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="87" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C87" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="88" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C88" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="89" spans="3:5" x14ac:dyDescent="0.25">
@@ -2087,7 +2087,7 @@
     </row>
     <row r="94" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C94" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="95" spans="3:5" x14ac:dyDescent="0.25">
@@ -2112,7 +2112,7 @@
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D99" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.25">
@@ -2137,12 +2137,12 @@
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C105" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.25">
@@ -2242,7 +2242,7 @@
     </row>
     <row r="125" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C125" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="126" spans="3:5" x14ac:dyDescent="0.25">
@@ -2317,7 +2317,7 @@
     </row>
     <row r="140" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C140" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="141" spans="3:5" x14ac:dyDescent="0.25">
@@ -2402,7 +2402,7 @@
     </row>
     <row r="157" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C157" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="158" spans="3:5" x14ac:dyDescent="0.25">
@@ -2432,7 +2432,7 @@
     </row>
     <row r="163" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C163" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="164" spans="3:5" x14ac:dyDescent="0.25">
@@ -2462,7 +2462,7 @@
     </row>
     <row r="169" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D169" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="170" spans="3:5" x14ac:dyDescent="0.25">
@@ -2512,7 +2512,7 @@
     </row>
     <row r="179" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C179" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="180" spans="3:5" x14ac:dyDescent="0.25">
@@ -2542,12 +2542,12 @@
     </row>
     <row r="185" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D185" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="186" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D186" t="s">
-        <v>280</v>
+        <v>317</v>
       </c>
     </row>
     <row r="187" spans="3:5" x14ac:dyDescent="0.25">
@@ -2612,17 +2612,17 @@
     </row>
     <row r="199" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C199" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="200" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="201" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C201" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="202" spans="2:6" x14ac:dyDescent="0.25">
@@ -2657,7 +2657,7 @@
     </row>
     <row r="208" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D208" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="209" spans="4:6" x14ac:dyDescent="0.25">
@@ -2752,7 +2752,7 @@
     </row>
     <row r="227" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D227" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="228" spans="4:5" x14ac:dyDescent="0.25">
@@ -2837,7 +2837,7 @@
     </row>
     <row r="244" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C244" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="245" spans="3:5" x14ac:dyDescent="0.25">
@@ -2852,7 +2852,7 @@
     </row>
     <row r="247" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D247" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="248" spans="3:5" x14ac:dyDescent="0.25">
@@ -2917,7 +2917,7 @@
     </row>
     <row r="260" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C260" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="261" spans="3:5" x14ac:dyDescent="0.25">
@@ -2967,7 +2967,7 @@
     </row>
     <row r="270" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D270" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="271" spans="3:5" x14ac:dyDescent="0.25">
@@ -3017,7 +3017,7 @@
     </row>
     <row r="280" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C280" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="281" spans="3:5" x14ac:dyDescent="0.25">
@@ -3087,7 +3087,7 @@
     </row>
     <row r="294" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C294" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="295" spans="3:5" x14ac:dyDescent="0.25">
@@ -3218,12 +3218,6 @@
     <row r="320" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D320" t="s">
         <v>272</v>
-      </c>
-    </row>
-    <row r="361" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F361">
-        <f>COUNTA(F1:F360)</f>
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/bani muzakki 2.xlsx
+++ b/bani muzakki 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4dd770f5288dd514/Documents/GitHub/familyhood.my.id/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="8_{107DCD37-E142-49A6-A5C7-C5890FD142B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A27A2B9-37B6-4ACF-8E38-01F1564B39D3}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="8_{107DCD37-E142-49A6-A5C7-C5890FD142B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26FE771E-E933-4DB7-837B-87CACEAE55E2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5BB80F8E-BB6F-464C-9455-26EC13A679BF}"/>
   </bookViews>
@@ -293,7 +293,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="874">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="875">
   <si>
     <t>MUZAKKI + ZAKIYAH</t>
   </si>
@@ -1228,9 +1228,6 @@
     <t xml:space="preserve"> Sukosari Gondanglegi Malang</t>
   </si>
   <si>
-    <t>ALMARHUMAIN</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Sidokare Asri AW 30 RT 22 RW 6 Sidoarjo email: rizqinamaulidas@yahoo.com</t>
   </si>
   <si>
@@ -1249,10 +1246,6 @@
     <t xml:space="preserve"> Perum Tirtasari Raya Blok I no.9 Sukun Malang Telp. 0341-805023 Hp. 08986350223; 08883809332 email: ahmaz1974@gmail.com WA Yuyun 088227120677</t>
   </si>
   <si>
-    <t>081331141625 
-081332496151</t>
-  </si>
-  <si>
     <t>27-10-2002</t>
   </si>
   <si>
@@ -1268,9 +1261,6 @@
     <t xml:space="preserve"> Tambaksari RT 02 RW 01 Tajinan Malang</t>
   </si>
   <si>
-    <t>085791995081 085331195369 08123318493</t>
-  </si>
-  <si>
     <t>07-05-2002</t>
   </si>
   <si>
@@ -1280,9 +1270,6 @@
     <t xml:space="preserve"> Sumurber RT 10 RW 03 Panceng Gresik</t>
   </si>
   <si>
-    <t>08563173399 085331195369 085791995081</t>
-  </si>
-  <si>
     <t>Gresik</t>
   </si>
   <si>
@@ -1295,15 +1282,9 @@
     <t xml:space="preserve"> Jl. Kol. Sugiono IIIA/234 Malang </t>
   </si>
   <si>
-    <t>0811362388   0341-364200</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Jl. Sadar Raya 99 RT.03/04 Ciganjur Jaksel 12630 Email: evy@msadat.net  ; sadat@amsadat.net</t>
   </si>
   <si>
-    <t>08111895825 08111895826</t>
-  </si>
-  <si>
     <t>20-10-2001</t>
   </si>
   <si>
@@ -1325,15 +1306,9 @@
     <t>Jl. Palmerah V E-14 Villa Gunung Buring Cemorokandang Malang</t>
   </si>
   <si>
-    <t xml:space="preserve">081334556501 </t>
-  </si>
-  <si>
     <t>Jl. Palmerah V F-30 Villa Gunung Buring Cemorokandang Malang</t>
   </si>
   <si>
-    <t>089528440825 081252656114 0341-327698</t>
-  </si>
-  <si>
     <t>12-10-2022</t>
   </si>
   <si>
@@ -1343,9 +1318,6 @@
     <t>Jl. Trunojoyo No 138 Tapaan Bugul Kidul Pasuruan</t>
   </si>
   <si>
-    <t>089519264424 085736002132</t>
-  </si>
-  <si>
     <t>25-08-2021</t>
   </si>
   <si>
@@ -1364,9 +1336,6 @@
     <t xml:space="preserve"> Karangsuko Gondanglegi Malang</t>
   </si>
   <si>
-    <t>081333506003 081233784080</t>
-  </si>
-  <si>
     <t>09-03-2025</t>
   </si>
   <si>
@@ -1379,9 +1348,6 @@
     <t xml:space="preserve"> Jl. Raya Tlogowaru RT 06/04 Malang Email: arofat@agrisatwa.com</t>
   </si>
   <si>
-    <t>0811362565 0341-751589</t>
-  </si>
-  <si>
     <t>21-02-2006</t>
   </si>
   <si>
@@ -1406,9 +1372,6 @@
     <t xml:space="preserve"> Perum Gadang Cahaya Raya Malang</t>
   </si>
   <si>
-    <t>081252866984  0341-806466</t>
-  </si>
-  <si>
     <t>15-01-2003</t>
   </si>
   <si>
@@ -1418,16 +1381,9 @@
     <t xml:space="preserve"> Jl. Kol. Sugiono 149 Malang  Permata Jingga Blok Anggrek II No 24 Malang</t>
   </si>
   <si>
-    <t>082132092782 081945999475</t>
-  </si>
-  <si>
     <t>Perumahan Bumi Palapa Blok A-1/16 Jl. Soxofone Malang 65141</t>
   </si>
   <si>
-    <t>08113647378 
-081334904555</t>
-  </si>
-  <si>
     <t>25-02-2006</t>
   </si>
   <si>
@@ -1440,20 +1396,10 @@
     <t>Perumahan Permata Jingga Block Pakis No. 19 Tunggul Wulung Lowokwaru Malang 65143</t>
   </si>
   <si>
-    <t>081233764282 081333323047</t>
-  </si>
-  <si>
     <t>Jl. MT Haryono XVII No.10 Dinoyo Malang</t>
   </si>
   <si>
-    <t>0811314534 
-0895391484141</t>
-  </si>
-  <si>
     <t>Cascadia Residence Blok B No 9 Jl. Raya Tole Iskandar  RT.07 RW.02 Mekarjaya Sukmajaya Depok 16411 email: mukhsonrofi@gmail.com WA 08158719527</t>
-  </si>
-  <si>
-    <t>081513236368 08129623682 081399313391</t>
   </si>
   <si>
     <t>Depok</t>
@@ -1506,10 +1452,6 @@
     <t>Mahoni Town House Kav 7, Jl Haji Kair no 45 RT 06 RW 04 Ragunan Telp. 081520465164 021-94568760 Jaksel Email:lukpras@yahoo.com WA 081513091706</t>
   </si>
   <si>
-    <t>081513091706 
-081513091705</t>
-  </si>
-  <si>
     <t>13-05-2011</t>
   </si>
   <si>
@@ -1538,9 +1480,6 @@
     <t>Vila Grand Tomang 2 Cluster Venice, Blok G 2A No 8, Periuk, Tangerang</t>
   </si>
   <si>
-    <t>082244660090 085855064000</t>
-  </si>
-  <si>
     <t>Tangerang</t>
   </si>
   <si>
@@ -1550,9 +1489,6 @@
     <t xml:space="preserve"> Dinoyo VID/888 Malang </t>
   </si>
   <si>
-    <t>085230699198 082334869168</t>
-  </si>
-  <si>
     <t>Dsn Krajan Desa Karang Harjo 89 RT 3/RW 2 Silo Jember</t>
   </si>
   <si>
@@ -1590,12 +1526,6 @@
   </si>
   <si>
     <t xml:space="preserve"> Sukosari Gondanglegi Malang Telp. 0341-879701</t>
-  </si>
-  <si>
-    <t>08123312714 085855403456</t>
-  </si>
-  <si>
-    <t>085736000771 082233831276 085331461682</t>
   </si>
   <si>
     <t>25-05-2019</t>
@@ -1620,9 +1550,6 @@
 Simo Sungelebak Karanggeneng Lamongan 62254</t>
   </si>
   <si>
-    <t xml:space="preserve"> 085730027445 08563197951</t>
-  </si>
-  <si>
     <t>Jl. Siwalankerto Utara II No. 35 RT. 04 RW. 03 Siwalankerto Surabaya</t>
   </si>
   <si>
@@ -1664,9 +1591,6 @@
     <t>Jl. Banyulegi II RT 28 RW 04 Ketawang Gondanglegi 65174</t>
   </si>
   <si>
-    <t>085235914511 085258848604</t>
-  </si>
-  <si>
     <t>27-10-1999</t>
   </si>
   <si>
@@ -1703,9 +1627,6 @@
     <t>Jl. Badjuri I RT 03 RW 01 Pakisaji Pakisaji Malang 65162</t>
   </si>
   <si>
-    <t>08123312768 081232578774</t>
-  </si>
-  <si>
     <t>16-03-2016</t>
   </si>
   <si>
@@ -1745,18 +1666,12 @@
     <t>Jl. Ahmad Dahlan RT. 06 RW. 02 Sukosari Gondanglegi Malang</t>
   </si>
   <si>
-    <t>081334555667 085707971917</t>
-  </si>
-  <si>
     <t>08-03-2020</t>
   </si>
   <si>
     <t>Krebet Bululawang Malang</t>
   </si>
   <si>
-    <t>083848083890 085231645900</t>
-  </si>
-  <si>
     <t>02-12-2011</t>
   </si>
   <si>
@@ -1799,9 +1714,6 @@
     <t>Dusun Baran Desa Urek Urek RT 03 RW 02 Gondanglegi Malang 65174</t>
   </si>
   <si>
-    <t>085101530244 085748180327</t>
-  </si>
-  <si>
     <t>11-01-2009</t>
   </si>
   <si>
@@ -1811,36 +1723,21 @@
     <t xml:space="preserve"> Areng-areng Sambisirah Wonorejo Pasuruan</t>
   </si>
   <si>
-    <t>082264422288 082228203780</t>
-  </si>
-  <si>
     <t>Perumahan Permata Regency Blok 25 No 5 Ngijo Karangploso Malang dan/atau Kumbo Tlogosari 02/04 Tutur Tutur Pasuruan</t>
   </si>
   <si>
-    <t>085753224282 081555467300</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Areng-areng RT.02 RW.02 Sambisirah Wonorejo Pasuruan</t>
   </si>
   <si>
-    <t>081333237330 085733438388</t>
-  </si>
-  <si>
     <t>10-02-2016</t>
   </si>
   <si>
     <t>Pasuruan + Pasuruan</t>
   </si>
   <si>
-    <t>082231241225 085645722453</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Jl Bungur No. 156  RT.1/1 Gebang Patrang Jember </t>
   </si>
   <si>
-    <t>085336777363 081559552288</t>
-  </si>
-  <si>
     <t>Jember</t>
   </si>
   <si>
@@ -1856,15 +1753,9 @@
     <t>Dusun Duk Tengah Ketapang Daya Ketapang Sampang Madura</t>
   </si>
   <si>
-    <t>081331748487 082331134916</t>
-  </si>
-  <si>
     <t>Dsn. Gujing, Ds. Ketapang Laok, Kec. Ketapang Kab. Sampang Madura</t>
   </si>
   <si>
-    <t>082233170333 082337607055</t>
-  </si>
-  <si>
     <t>Sampang</t>
   </si>
   <si>
@@ -1893,9 +1784,6 @@
   </si>
   <si>
     <t>Jl Sidomulyo II No 18 RT 25 RW 07 Wandanpuro Bululawang Malang 65171</t>
-  </si>
-  <si>
-    <t>08563588731 081357988841</t>
   </si>
   <si>
     <t>06-06-2007</t>
@@ -1938,9 +1826,6 @@
     <t>Putatkidul RT 02 RT 02 Putatkumpul Turi Lamongan</t>
   </si>
   <si>
-    <t>085732798966 085732703028</t>
-  </si>
-  <si>
     <t>13-03-2019</t>
   </si>
   <si>
@@ -1950,9 +1835,6 @@
     <t>Dusun Penjalinan Gondanglegikulon RT 04 RW 04 Gondanglegi Malang 65174</t>
   </si>
   <si>
-    <t>085850675472 089508843183 0341-879744</t>
-  </si>
-  <si>
     <t>12-08-1995</t>
   </si>
   <si>
@@ -2026,18 +1908,12 @@
   </si>
   <si>
     <t xml:space="preserve"> Sukosari RT.01/01 no 39 Gondanglegi Malang</t>
-  </si>
-  <si>
-    <t>085101891897 0341-878428</t>
   </si>
   <si>
     <t>PP. Raudlatul Ulum I
 Jl. Sumber Ilmu No.127, Ganjaran Selatan, Ganjaran, Kec. Gondanglegi, Kabupaten Malang, Jawa Timur 65174</t>
   </si>
   <si>
-    <t>085334533900 085649544398 085233153172</t>
-  </si>
-  <si>
     <t>02-09-2018</t>
   </si>
   <si>
@@ -2078,9 +1954,6 @@
 Jl. Ali Basah Sentot, RT.09/RW.03, Krajan, Gondanglegi Wetan, Kec. Gondanglegi, Kabupaten Malang, Jawa Timur 65174</t>
   </si>
   <si>
-    <t>081555770707 085607104449</t>
-  </si>
-  <si>
     <t>11-06-2017</t>
   </si>
   <si>
@@ -2134,10 +2007,6 @@
 Website: http://hoeda.web.id</t>
   </si>
   <si>
-    <t>085646551924  
-081331574000</t>
-  </si>
-  <si>
     <t>29-01-2007</t>
   </si>
   <si>
@@ -2147,9 +2016,6 @@
     <t>Kajarharjo Depan Masjid Babus Salam Kalibaru Banyuwangi (KH. Nasir)</t>
   </si>
   <si>
-    <t>085336581498 082333063477</t>
-  </si>
-  <si>
     <t>Banyuwangi</t>
   </si>
   <si>
@@ -2162,9 +2028,6 @@
     <t>Jl Masjid AN NUR 313 Pasar Sumber Urip Krajan Pronojiwo Lumajang</t>
   </si>
   <si>
-    <t xml:space="preserve">081233137007 081334228777 </t>
-  </si>
-  <si>
     <t>Lumajang</t>
   </si>
   <si>
@@ -2180,21 +2043,12 @@
     <t xml:space="preserve"> Jl Bimasakti 4 Malang Email: dsyamsuddin@gmail.com</t>
   </si>
   <si>
-    <t>081334614439 081333890885</t>
-  </si>
-  <si>
-    <t>081333078488 081334710359</t>
-  </si>
-  <si>
     <t>18-05-2015</t>
   </si>
   <si>
     <t>Tumapel Singosari Kab. Malang</t>
   </si>
   <si>
-    <t>081334575513 08990391029</t>
-  </si>
-  <si>
     <t>18-05-2012</t>
   </si>
   <si>
@@ -2205,9 +2059,6 @@
   </si>
   <si>
     <t>Jl. Venus No. 14 Dinoyo Malang/ Jl. Permata Kencana Saxofone No. 30 Tunggulwulung Malang</t>
-  </si>
-  <si>
-    <t>081333890884 085646777975</t>
   </si>
   <si>
     <t>11-01-2021</t>
@@ -2229,9 +2080,6 @@
     <t>17-09-2025</t>
   </si>
   <si>
-    <t>081334318035 08563488452</t>
-  </si>
-  <si>
     <t>07-07-2020</t>
   </si>
   <si>
@@ -2245,16 +2093,10 @@
 Jl Kenongo RT.03/01 Putat Lor Gd.legi</t>
   </si>
   <si>
-    <t>03417319519 085655519666</t>
-  </si>
-  <si>
     <t>PP. Jauharotul Muzakky
 Jl. Trunojoyo RT 06 RW 02 Sukosari Gondanglegi Malang</t>
   </si>
   <si>
-    <t xml:space="preserve">085785066409 085855837802 </t>
-  </si>
-  <si>
     <t>17-01-2008</t>
   </si>
   <si>
@@ -2271,9 +2113,6 @@
 Baran, Jl. Kenongo No.204, Putat Lor, Kec. Gondanglegi, Kabupaten Malang, Jawa Timur 65174</t>
   </si>
   <si>
-    <t>085649901168 0341-879014</t>
-  </si>
-  <si>
     <t>26-02-2006</t>
   </si>
   <si>
@@ -2289,13 +2128,7 @@
     <t xml:space="preserve"> Jl. Hayam Wuruk I RT.01/01 Gondanglegi Malang </t>
   </si>
   <si>
-    <t>085330111238 085234656567</t>
-  </si>
-  <si>
     <t>Jl. Pande RT 02 RW 02 Junrejo Batu</t>
-  </si>
-  <si>
-    <t>082337252344 081222774423</t>
   </si>
   <si>
     <t>09-09-2015</t>
@@ -2326,9 +2159,6 @@
 Jl. Pronoyudo No 1 Dadaprejo Junrejo Batu Malang Telp. 03417724249 03417734402</t>
   </si>
   <si>
-    <t xml:space="preserve">085100734402 081233898854 </t>
-  </si>
-  <si>
     <t>19-03-2007</t>
   </si>
   <si>
@@ -2341,9 +2171,6 @@
     <t>16-07-2012</t>
   </si>
   <si>
-    <t>081252202269 085731350268 081216870142</t>
-  </si>
-  <si>
     <t>26-12-2013</t>
   </si>
   <si>
@@ -2359,30 +2186,18 @@
     <t xml:space="preserve"> Sukosari 33 Gondanglegi Malang  Urek Urek Gondanglegi</t>
   </si>
   <si>
-    <t>082244062897 087855506663</t>
-  </si>
-  <si>
     <t>11-12-2021</t>
   </si>
   <si>
     <t xml:space="preserve"> Sukosari Gondanglegi Malang </t>
   </si>
   <si>
-    <t>03418680727 0341-878429</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Karangsuko Gondanglegi Malang </t>
   </si>
   <si>
-    <t>081333149994 0341-878431</t>
-  </si>
-  <si>
     <t>Jl. Trunojoyo RT 06 RW 02 Sukosari Gondanglegi Malang</t>
   </si>
   <si>
-    <t>085855837802 085785066409</t>
-  </si>
-  <si>
     <t>Jl. Sunan Bonang RT.003 RW.001 Bulupitu Gondanglegi Malang 65174</t>
   </si>
   <si>
@@ -2401,9 +2216,6 @@
     <t>Jl. H. Agus Salim III/16 Sampang</t>
   </si>
   <si>
-    <t>082132420003 087849372637</t>
-  </si>
-  <si>
     <t>31-03-2012</t>
   </si>
   <si>
@@ -2425,9 +2237,6 @@
     <t>PP. AT TARAQQI Karongan Sampang Madura</t>
   </si>
   <si>
-    <t>081233984946 085608020715</t>
-  </si>
-  <si>
     <t>28-11-2017</t>
   </si>
   <si>
@@ -2440,18 +2249,12 @@
     <t>17-08-1999</t>
   </si>
   <si>
-    <t>08123324993 03417659993</t>
-  </si>
-  <si>
     <t>20-05-1975</t>
   </si>
   <si>
     <t xml:space="preserve"> PP.  Mambaul Huda Karangploso Malang </t>
   </si>
   <si>
-    <t>082245703607 081233391555</t>
-  </si>
-  <si>
     <t>30-08-2003</t>
   </si>
   <si>
@@ -2782,9 +2585,6 @@
     <t>30-01-1998 +  20-10-1992</t>
   </si>
   <si>
-    <t xml:space="preserve"> + 966558737564 + 966509217708 + 966508710121</t>
-  </si>
-  <si>
     <t>13-01-1977 +  13-05-1973</t>
   </si>
   <si>
@@ -2936,13 +2736,216 @@
   </si>
   <si>
     <t>No Hp</t>
+  </si>
+  <si>
+    <t>85294499531</t>
+  </si>
+  <si>
+    <t>966507181873</t>
+  </si>
+  <si>
+    <t>081331141625+
+081332496151</t>
+  </si>
+  <si>
+    <t>085791995081+085331195369+08123318493</t>
+  </si>
+  <si>
+    <t>08563173399+085331195369+085791995081</t>
+  </si>
+  <si>
+    <t>08111895825+08111895826</t>
+  </si>
+  <si>
+    <t>081334556501+</t>
+  </si>
+  <si>
+    <t>089528440825+081252656114+0341-327698</t>
+  </si>
+  <si>
+    <t>089519264424+085736002132</t>
+  </si>
+  <si>
+    <t>081333506003+081233784080</t>
+  </si>
+  <si>
+    <t>0811362565+0341-751589</t>
+  </si>
+  <si>
+    <t>082132092782+081945999475</t>
+  </si>
+  <si>
+    <t>08113647378+
+081334904555</t>
+  </si>
+  <si>
+    <t>081233764282+081333323047</t>
+  </si>
+  <si>
+    <t>0811314534+
+0895391484141</t>
+  </si>
+  <si>
+    <t>081513236368+08129623682+081399313391</t>
+  </si>
+  <si>
+    <t>081513091706+
+081513091705</t>
+  </si>
+  <si>
+    <t>082244660090+085855064000</t>
+  </si>
+  <si>
+    <t>085230699198+082334869168</t>
+  </si>
+  <si>
+    <t>08123312714+085855403456</t>
+  </si>
+  <si>
+    <t>085736000771+082233831276+085331461682</t>
+  </si>
+  <si>
+    <t>+085730027445+08563197951</t>
+  </si>
+  <si>
+    <t>085235914511+085258848604</t>
+  </si>
+  <si>
+    <t>08123312768+081232578774</t>
+  </si>
+  <si>
+    <t>081334555667+085707971917</t>
+  </si>
+  <si>
+    <t>083848083890+085231645900</t>
+  </si>
+  <si>
+    <t>085101530244+085748180327</t>
+  </si>
+  <si>
+    <t>082264422288+082228203780</t>
+  </si>
+  <si>
+    <t>085753224282+081555467300</t>
+  </si>
+  <si>
+    <t>081333237330+085733438388</t>
+  </si>
+  <si>
+    <t>082231241225+085645722453</t>
+  </si>
+  <si>
+    <t>085336777363+081559552288</t>
+  </si>
+  <si>
+    <t>081331748487+082331134916</t>
+  </si>
+  <si>
+    <t>082233170333+082337607055</t>
+  </si>
+  <si>
+    <t>08563588731+081357988841</t>
+  </si>
+  <si>
+    <t>085732798966+085732703028</t>
+  </si>
+  <si>
+    <t>085850675472+089508843183+0341-879744</t>
+  </si>
+  <si>
+    <t>085101891897+0341-878428</t>
+  </si>
+  <si>
+    <t>085334533900+085649544398+085233153172</t>
+  </si>
+  <si>
+    <t>081555770707+085607104449</t>
+  </si>
+  <si>
+    <t>085336581498+082333063477</t>
+  </si>
+  <si>
+    <t>081233137007+081334228777+</t>
+  </si>
+  <si>
+    <t>081334614439+081333890885</t>
+  </si>
+  <si>
+    <t>081333078488+081334710359</t>
+  </si>
+  <si>
+    <t>081334575513+08990391029</t>
+  </si>
+  <si>
+    <t>081333890884+085646777975</t>
+  </si>
+  <si>
+    <t>081334318035+08563488452</t>
+  </si>
+  <si>
+    <t>03417319519+085655519666</t>
+  </si>
+  <si>
+    <t>085785066409+085855837802+</t>
+  </si>
+  <si>
+    <t>085649901168+0341-879014</t>
+  </si>
+  <si>
+    <t>085330111238+085234656567</t>
+  </si>
+  <si>
+    <t>082337252344+081222774423</t>
+  </si>
+  <si>
+    <t>085100734402+081233898854+</t>
+  </si>
+  <si>
+    <t>081252202269+085731350268+081216870142</t>
+  </si>
+  <si>
+    <t>082244062897+087855506663</t>
+  </si>
+  <si>
+    <t>03418680727+0341-878429</t>
+  </si>
+  <si>
+    <t>081333149994+0341-878431</t>
+  </si>
+  <si>
+    <t>085855837802+085785066409</t>
+  </si>
+  <si>
+    <t>082132420003+087849372637</t>
+  </si>
+  <si>
+    <t>081233984946+085608020715</t>
+  </si>
+  <si>
+    <t>08123324993+03417659993</t>
+  </si>
+  <si>
+    <t>082245703607+081233391555</t>
+  </si>
+  <si>
+    <t>0811362388+0341-364200</t>
+  </si>
+  <si>
+    <t>+966558737564+966509217708+966508710121</t>
+  </si>
+  <si>
+    <t>081252866984+0341-806466</t>
+  </si>
+  <si>
+    <t>085646551924+
+081331574000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2962,6 +2965,12 @@
       <family val="2"/>
       <charset val="1"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2984,9 +2993,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3308,8 +3318,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C629E1E-B955-4A3C-B56E-5C952373FF63}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J321"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J357"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
@@ -3320,61 +3330,63 @@
     <col min="7" max="7" width="21.140625" customWidth="1"/>
     <col min="8" max="8" width="31.42578125" customWidth="1"/>
     <col min="9" max="9" width="138.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="41.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>864</v>
+        <v>799</v>
       </c>
       <c r="B1" t="s">
-        <v>865</v>
+        <v>800</v>
       </c>
       <c r="C1" t="s">
-        <v>866</v>
+        <v>801</v>
       </c>
       <c r="D1" t="s">
-        <v>867</v>
+        <v>802</v>
       </c>
       <c r="E1" t="s">
-        <v>868</v>
+        <v>803</v>
       </c>
       <c r="F1" t="s">
-        <v>869</v>
+        <v>804</v>
       </c>
       <c r="G1" t="s">
-        <v>871</v>
+        <v>806</v>
       </c>
       <c r="H1" t="s">
-        <v>872</v>
+        <v>807</v>
       </c>
       <c r="I1" t="s">
-        <v>870</v>
+        <v>805</v>
       </c>
       <c r="J1" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="B3" t="s">
         <v>282</v>
       </c>
       <c r="G3" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H3" t="s">
-        <v>863</v>
+        <v>798</v>
       </c>
       <c r="I3" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J3" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="C4" t="s">
         <v>265</v>
       </c>
@@ -3382,80 +3394,92 @@
         <v>309</v>
       </c>
       <c r="H4" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <v>678</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="C5" t="s">
         <v>266</v>
       </c>
       <c r="G5" t="s">
-        <v>714</v>
+        <v>650</v>
       </c>
       <c r="H5" t="s">
-        <v>743</v>
+        <v>679</v>
       </c>
       <c r="I5" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J5" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="D6" t="s">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>715</v>
+        <v>651</v>
       </c>
       <c r="H6" t="s">
-        <v>744</v>
+        <v>680</v>
       </c>
       <c r="I6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="E7" t="s">
         <v>2</v>
       </c>
       <c r="G7" t="s">
+        <v>312</v>
+      </c>
+      <c r="H7" t="s">
         <v>313</v>
       </c>
-      <c r="H7" t="s">
-        <v>314</v>
-      </c>
-      <c r="J7" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J7" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="E8" t="s">
         <v>3</v>
       </c>
       <c r="G8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H8" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="D9" t="s">
         <v>283</v>
       </c>
       <c r="G9" t="s">
-        <v>716</v>
+        <v>652</v>
       </c>
       <c r="H9" t="s">
-        <v>745</v>
+        <v>681</v>
       </c>
       <c r="I9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="E10" t="s">
         <v>4</v>
       </c>
@@ -3463,10 +3487,13 @@
         <v>309</v>
       </c>
       <c r="H10" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>317</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="E11" t="s">
         <v>267</v>
       </c>
@@ -3474,10 +3501,13 @@
         <v>309</v>
       </c>
       <c r="H11" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="E12" t="s">
         <v>5</v>
       </c>
@@ -3485,10 +3515,13 @@
         <v>309</v>
       </c>
       <c r="H12" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="E13" t="s">
         <v>6</v>
       </c>
@@ -3496,27 +3529,30 @@
         <v>309</v>
       </c>
       <c r="H13" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="D14" t="s">
         <v>7</v>
       </c>
       <c r="G14" t="s">
-        <v>716</v>
+        <v>652</v>
       </c>
       <c r="H14" t="s">
-        <v>746</v>
+        <v>682</v>
       </c>
       <c r="I14" t="s">
-        <v>323</v>
-      </c>
-      <c r="J14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="E15" t="s">
         <v>8</v>
       </c>
@@ -3524,10 +3560,13 @@
         <v>309</v>
       </c>
       <c r="H15" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="E16" t="s">
         <v>9</v>
       </c>
@@ -3535,49 +3574,58 @@
         <v>309</v>
       </c>
       <c r="H16" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10">
       <c r="D17" t="s">
         <v>284</v>
       </c>
       <c r="G17" t="s">
-        <v>717</v>
+        <v>653</v>
       </c>
       <c r="H17" t="s">
-        <v>747</v>
+        <v>683</v>
       </c>
       <c r="I17" t="s">
-        <v>327</v>
-      </c>
-      <c r="J17" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10">
       <c r="E18" t="s">
         <v>10</v>
       </c>
       <c r="G18" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="H18" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10">
       <c r="E19" t="s">
         <v>11</v>
       </c>
       <c r="G19" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="H19" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10">
       <c r="C20" t="s">
         <v>279</v>
       </c>
@@ -3585,133 +3633,151 @@
         <v>309</v>
       </c>
       <c r="H20" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
+        <v>678</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10">
       <c r="C21" t="s">
         <v>285</v>
       </c>
       <c r="G21" t="s">
-        <v>718</v>
+        <v>654</v>
       </c>
       <c r="H21" t="s">
-        <v>748</v>
+        <v>684</v>
       </c>
       <c r="I21" t="s">
-        <v>332</v>
-      </c>
-      <c r="J21" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10">
       <c r="D22" t="s">
         <v>12</v>
       </c>
       <c r="G22" t="s">
-        <v>715</v>
+        <v>651</v>
       </c>
       <c r="H22" t="s">
-        <v>749</v>
+        <v>685</v>
       </c>
       <c r="I22" t="s">
-        <v>334</v>
-      </c>
-      <c r="J22" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10">
       <c r="E23" t="s">
         <v>13</v>
       </c>
       <c r="G23" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H23" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10">
       <c r="E24" t="s">
         <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H24" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.25">
+        <v>331</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10">
       <c r="E25" t="s">
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H25" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.25">
+        <v>332</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10">
       <c r="E26" t="s">
         <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="H26" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10">
       <c r="E27" t="s">
         <v>272</v>
       </c>
       <c r="G27" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="H27" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10">
       <c r="D28" t="s">
         <v>298</v>
       </c>
       <c r="G28" t="s">
-        <v>719</v>
+        <v>655</v>
       </c>
       <c r="H28" t="s">
-        <v>750</v>
+        <v>686</v>
       </c>
       <c r="I28" t="s">
-        <v>342</v>
-      </c>
-      <c r="J28" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10">
       <c r="E29" t="s">
         <v>17</v>
       </c>
       <c r="G29" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H29" t="s">
-        <v>751</v>
+        <v>687</v>
       </c>
       <c r="I29" t="s">
-        <v>344</v>
-      </c>
-      <c r="J29" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.25">
+        <v>337</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10">
       <c r="F30" t="s">
         <v>18</v>
       </c>
@@ -3719,10 +3785,13 @@
         <v>309</v>
       </c>
       <c r="H30" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.25">
+        <v>338</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10">
       <c r="F31" t="s">
         <v>19</v>
       </c>
@@ -3730,27 +3799,30 @@
         <v>309</v>
       </c>
       <c r="H31" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10">
       <c r="E32" t="s">
         <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>719</v>
+        <v>655</v>
       </c>
       <c r="H32" t="s">
-        <v>752</v>
+        <v>688</v>
       </c>
       <c r="I32" t="s">
-        <v>348</v>
-      </c>
-      <c r="J32" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="33" spans="4:10" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="33" spans="4:10">
       <c r="F33" t="s">
         <v>21</v>
       </c>
@@ -3758,32 +3830,41 @@
         <v>309</v>
       </c>
       <c r="H33" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="34" spans="4:10" x14ac:dyDescent="0.25">
+        <v>341</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="34" spans="4:10">
       <c r="F34" t="s">
         <v>22</v>
       </c>
       <c r="G34" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="H34" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="35" spans="4:10" x14ac:dyDescent="0.25">
+        <v>343</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="35" spans="4:10">
       <c r="F35" t="s">
         <v>23</v>
       </c>
       <c r="G35" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="H35" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="36" spans="4:10" x14ac:dyDescent="0.25">
+        <v>344</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="36" spans="4:10">
       <c r="E36" t="s">
         <v>24</v>
       </c>
@@ -3791,38 +3872,44 @@
         <v>309</v>
       </c>
       <c r="H36" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="37" spans="4:10" x14ac:dyDescent="0.25">
+        <v>345</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="37" spans="4:10">
       <c r="D37" t="s">
         <v>25</v>
       </c>
       <c r="G37" t="s">
-        <v>714</v>
+        <v>650</v>
       </c>
       <c r="H37" t="s">
-        <v>753</v>
+        <v>689</v>
       </c>
       <c r="I37" t="s">
-        <v>355</v>
-      </c>
-      <c r="J37" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="38" spans="4:10" x14ac:dyDescent="0.25">
+        <v>346</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="38" spans="4:10">
       <c r="E38" t="s">
         <v>26</v>
       </c>
       <c r="G38" t="s">
-        <v>754</v>
+        <v>690</v>
       </c>
       <c r="H38" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="39" spans="4:10" x14ac:dyDescent="0.25">
+        <v>691</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="39" spans="4:10">
       <c r="F39" t="s">
         <v>27</v>
       </c>
@@ -3830,10 +3917,13 @@
         <v>309</v>
       </c>
       <c r="H39" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="40" spans="4:10" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="40" spans="4:10">
       <c r="E40" t="s">
         <v>28</v>
       </c>
@@ -3841,41 +3931,47 @@
         <v>309</v>
       </c>
       <c r="H40" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="41" spans="4:10" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="41" spans="4:10">
       <c r="D41" t="s">
         <v>29</v>
       </c>
       <c r="G41" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H41" t="s">
-        <v>756</v>
+        <v>692</v>
       </c>
       <c r="I41" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="42" spans="4:10" x14ac:dyDescent="0.25">
+        <v>349</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="42" spans="4:10">
       <c r="D42" t="s">
         <v>286</v>
       </c>
       <c r="G42" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H42" t="s">
-        <v>757</v>
+        <v>693</v>
       </c>
       <c r="I42" t="s">
-        <v>360</v>
-      </c>
-      <c r="J42" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="43" spans="4:10" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="43" spans="4:10">
       <c r="E43" t="s">
         <v>30</v>
       </c>
@@ -3883,21 +3979,27 @@
         <v>309</v>
       </c>
       <c r="H43" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="44" spans="4:10" x14ac:dyDescent="0.25">
+        <v>351</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="44" spans="4:10">
       <c r="D44" t="s">
         <v>31</v>
       </c>
       <c r="G44" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H44" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="45" spans="4:10" x14ac:dyDescent="0.25">
+        <v>694</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="45" spans="4:10">
       <c r="E45" t="s">
         <v>32</v>
       </c>
@@ -3905,10 +4007,13 @@
         <v>309</v>
       </c>
       <c r="H45" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="46" spans="4:10" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="46" spans="4:10">
       <c r="E46" t="s">
         <v>33</v>
       </c>
@@ -3916,10 +4021,13 @@
         <v>309</v>
       </c>
       <c r="H46" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="47" spans="4:10" x14ac:dyDescent="0.25">
+        <v>353</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="47" spans="4:10">
       <c r="E47" t="s">
         <v>34</v>
       </c>
@@ -3927,10 +4035,13 @@
         <v>309</v>
       </c>
       <c r="H47" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="48" spans="4:10" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="48" spans="4:10">
       <c r="E48" t="s">
         <v>35</v>
       </c>
@@ -3938,10 +4049,13 @@
         <v>309</v>
       </c>
       <c r="H48" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="49" spans="3:10" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="49" spans="3:10">
       <c r="E49" t="s">
         <v>36</v>
       </c>
@@ -3949,10 +4063,13 @@
         <v>309</v>
       </c>
       <c r="H49" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="50" spans="3:10" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="50" spans="3:10">
       <c r="E50" t="s">
         <v>37</v>
       </c>
@@ -3960,27 +4077,30 @@
         <v>309</v>
       </c>
       <c r="H50" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="51" spans="3:10" x14ac:dyDescent="0.25">
+        <v>357</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="51" spans="3:10">
       <c r="D51" t="s">
         <v>299</v>
       </c>
       <c r="G51" t="s">
-        <v>718</v>
+        <v>654</v>
       </c>
       <c r="H51" t="s">
-        <v>759</v>
+        <v>695</v>
       </c>
       <c r="I51" t="s">
-        <v>369</v>
-      </c>
-      <c r="J51" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="52" spans="3:10" x14ac:dyDescent="0.25">
+        <v>358</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="52" spans="3:10">
       <c r="E52" t="s">
         <v>38</v>
       </c>
@@ -3988,10 +4108,13 @@
         <v>309</v>
       </c>
       <c r="H52" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="53" spans="3:10" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="53" spans="3:10">
       <c r="E53" t="s">
         <v>39</v>
       </c>
@@ -3999,44 +4122,47 @@
         <v>309</v>
       </c>
       <c r="H53" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="54" spans="3:10" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="54" spans="3:10">
       <c r="D54" t="s">
         <v>40</v>
       </c>
       <c r="G54" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H54" t="s">
-        <v>760</v>
+        <v>696</v>
       </c>
       <c r="I54" t="s">
-        <v>373</v>
-      </c>
-      <c r="J54" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="55" spans="3:10" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="55" spans="3:10">
       <c r="D55" t="s">
         <v>287</v>
       </c>
       <c r="G55" t="s">
-        <v>720</v>
+        <v>656</v>
       </c>
       <c r="H55" t="s">
-        <v>761</v>
+        <v>697</v>
       </c>
       <c r="I55" t="s">
-        <v>375</v>
-      </c>
-      <c r="J55" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="56" spans="3:10" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="56" spans="3:10">
       <c r="E56" t="s">
         <v>41</v>
       </c>
@@ -4044,13 +4170,16 @@
         <v>309</v>
       </c>
       <c r="H56" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="I56" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="57" spans="3:10" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="57" spans="3:10">
       <c r="E57" t="s">
         <v>42</v>
       </c>
@@ -4058,166 +4187,193 @@
         <v>309</v>
       </c>
       <c r="H57" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="58" spans="3:10" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="58" spans="3:10">
       <c r="D58" t="s">
         <v>288</v>
       </c>
       <c r="G58" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H58" t="s">
-        <v>762</v>
+        <v>698</v>
       </c>
       <c r="I58" t="s">
-        <v>380</v>
-      </c>
-      <c r="J58" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="59" spans="3:10" x14ac:dyDescent="0.25">
+        <v>366</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="59" spans="3:10">
       <c r="C59" t="s">
         <v>43</v>
       </c>
       <c r="G59" t="s">
-        <v>715</v>
+        <v>651</v>
       </c>
       <c r="H59" t="s">
-        <v>763</v>
+        <v>699</v>
       </c>
       <c r="I59" t="s">
-        <v>382</v>
-      </c>
-      <c r="J59" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="60" spans="3:10" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="60" spans="3:10">
       <c r="D60" t="s">
         <v>44</v>
       </c>
       <c r="G60" t="s">
-        <v>721</v>
+        <v>657</v>
       </c>
       <c r="H60" t="s">
-        <v>764</v>
+        <v>700</v>
       </c>
       <c r="I60" t="s">
-        <v>384</v>
-      </c>
-      <c r="J60" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="61" spans="3:10" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="61" spans="3:10">
       <c r="E61" t="s">
         <v>45</v>
       </c>
       <c r="G61" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="H61" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="62" spans="3:10" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="62" spans="3:10">
       <c r="E62" t="s">
         <v>46</v>
       </c>
       <c r="G62" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="H62" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="63" spans="3:10" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="63" spans="3:10">
       <c r="E63" t="s">
         <v>47</v>
       </c>
       <c r="G63" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="H63" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="64" spans="3:10" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="64" spans="3:10">
       <c r="E64" t="s">
         <v>48</v>
       </c>
       <c r="G64" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="H64" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="65" spans="3:10" x14ac:dyDescent="0.25">
+        <v>373</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="65" spans="3:10">
       <c r="D65" t="s">
         <v>49</v>
       </c>
       <c r="G65" t="s">
-        <v>722</v>
+        <v>658</v>
       </c>
       <c r="H65" t="s">
-        <v>765</v>
+        <v>701</v>
       </c>
       <c r="I65" t="s">
-        <v>391</v>
-      </c>
-      <c r="J65" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="66" spans="3:10" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="66" spans="3:10">
       <c r="E66" t="s">
         <v>50</v>
       </c>
       <c r="G66" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="H66" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="67" spans="3:10" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="67" spans="3:10">
       <c r="E67" t="s">
         <v>51</v>
       </c>
       <c r="G67" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="H67" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="68" spans="3:10" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="68" spans="3:10">
       <c r="E68" t="s">
         <v>52</v>
       </c>
       <c r="G68" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="H68" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="69" spans="3:10" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="69" spans="3:10">
       <c r="E69" t="s">
         <v>53</v>
       </c>
       <c r="G69" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="H69" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="70" spans="3:10" x14ac:dyDescent="0.25">
+        <v>379</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="70" spans="3:10">
       <c r="D70" t="s">
         <v>54</v>
       </c>
@@ -4225,223 +4381,247 @@
         <v>309</v>
       </c>
       <c r="H70" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="I70" t="s">
-        <v>382</v>
-      </c>
-      <c r="J70" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="71" spans="3:10" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="71" spans="3:10">
       <c r="C71" t="s">
         <v>55</v>
       </c>
       <c r="G71" t="s">
-        <v>738</v>
+        <v>674</v>
       </c>
       <c r="H71" t="s">
-        <v>766</v>
+        <v>702</v>
       </c>
       <c r="I71" t="s">
-        <v>399</v>
-      </c>
-      <c r="J71" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="72" spans="3:10" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="72" spans="3:10">
       <c r="D72" t="s">
         <v>56</v>
       </c>
       <c r="G72" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H72" t="s">
-        <v>767</v>
+        <v>703</v>
       </c>
       <c r="I72" t="s">
-        <v>401</v>
-      </c>
-      <c r="J72" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="73" spans="3:10" x14ac:dyDescent="0.25">
+        <v>384</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="73" spans="3:10">
       <c r="E73" t="s">
         <v>57</v>
       </c>
       <c r="G73" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="H73" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="74" spans="3:10" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="74" spans="3:10">
       <c r="E74" t="s">
         <v>58</v>
       </c>
       <c r="G74" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="H74" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="75" spans="3:10" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="75" spans="3:10">
       <c r="E75" t="s">
         <v>59</v>
       </c>
       <c r="G75" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="H75" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="76" spans="3:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="76" spans="3:10">
       <c r="D76" t="s">
         <v>60</v>
       </c>
       <c r="G76" t="s">
-        <v>723</v>
+        <v>659</v>
       </c>
       <c r="H76" t="s">
-        <v>768</v>
+        <v>704</v>
       </c>
       <c r="I76" t="s">
-        <v>405</v>
-      </c>
-      <c r="J76" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="77" spans="3:10" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="77" spans="3:10">
       <c r="E77" t="s">
         <v>61</v>
       </c>
       <c r="G77" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="H77" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="78" spans="3:10" x14ac:dyDescent="0.25">
+        <v>390</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="78" spans="3:10">
       <c r="E78" t="s">
         <v>62</v>
       </c>
       <c r="G78" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="H78" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="79" spans="3:10" x14ac:dyDescent="0.25">
+        <v>391</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="79" spans="3:10">
       <c r="E79" t="s">
         <v>63</v>
       </c>
       <c r="G79" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="H79" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="80" spans="3:10" x14ac:dyDescent="0.25">
+        <v>392</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="80" spans="3:10">
       <c r="D80" t="s">
         <v>64</v>
       </c>
       <c r="G80" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H80" t="s">
-        <v>769</v>
+        <v>705</v>
       </c>
       <c r="I80" t="s">
-        <v>411</v>
-      </c>
-      <c r="J80" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="81" spans="3:10" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="81" spans="3:10">
       <c r="E81" t="s">
         <v>65</v>
       </c>
       <c r="G81" t="s">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="H81" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="82" spans="3:10" x14ac:dyDescent="0.25">
+        <v>395</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="82" spans="3:10">
       <c r="C82" t="s">
         <v>273</v>
       </c>
       <c r="G82" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H82" t="s">
-        <v>770</v>
+        <v>706</v>
       </c>
       <c r="I82" t="s">
-        <v>415</v>
-      </c>
-      <c r="J82" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="83" spans="3:10" x14ac:dyDescent="0.25">
+        <v>396</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="83" spans="3:10">
       <c r="D83" t="s">
         <v>66</v>
       </c>
       <c r="G83" t="s">
-        <v>724</v>
+        <v>660</v>
       </c>
       <c r="H83" t="s">
-        <v>771</v>
+        <v>707</v>
       </c>
       <c r="I83" t="s">
-        <v>417</v>
-      </c>
-      <c r="J83" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="84" spans="3:10" x14ac:dyDescent="0.25">
+        <v>397</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="84" spans="3:10">
       <c r="D84" t="s">
         <v>67</v>
       </c>
       <c r="G84" t="s">
-        <v>725</v>
+        <v>661</v>
       </c>
       <c r="H84" t="s">
-        <v>772</v>
+        <v>708</v>
       </c>
       <c r="I84" t="s">
-        <v>419</v>
-      </c>
-      <c r="J84" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="85" spans="3:10" x14ac:dyDescent="0.25">
+        <v>399</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="85" spans="3:10">
       <c r="E85" t="s">
         <v>68</v>
       </c>
       <c r="G85" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="H85" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="86" spans="3:10" x14ac:dyDescent="0.25">
+        <v>402</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="86" spans="3:10">
       <c r="D86" t="s">
         <v>69</v>
       </c>
@@ -4449,30 +4629,33 @@
         <v>309</v>
       </c>
       <c r="H86" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="I86" t="s">
-        <v>424</v>
-      </c>
-      <c r="J86" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="87" spans="3:10" x14ac:dyDescent="0.25">
+        <v>404</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="87" spans="3:10">
       <c r="C87" t="s">
         <v>289</v>
       </c>
       <c r="G87" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H87" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="I87" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="88" spans="3:10" x14ac:dyDescent="0.25">
+        <v>407</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="88" spans="3:10">
       <c r="C88" t="s">
         <v>274</v>
       </c>
@@ -4480,44 +4663,47 @@
         <v>309</v>
       </c>
       <c r="H88" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="I88" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="89" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="J88" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="89" spans="3:10">
       <c r="C89" t="s">
         <v>300</v>
       </c>
       <c r="G89" t="s">
-        <v>726</v>
+        <v>662</v>
       </c>
       <c r="H89" t="s">
-        <v>773</v>
+        <v>709</v>
       </c>
       <c r="I89" t="s">
-        <v>429</v>
-      </c>
-      <c r="J89" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="90" spans="3:10" x14ac:dyDescent="0.25">
+        <v>409</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="90" spans="3:10">
       <c r="D90" t="s">
         <v>70</v>
       </c>
       <c r="G90" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H90" t="s">
-        <v>774</v>
-      </c>
-      <c r="J90" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="91" spans="3:10" x14ac:dyDescent="0.25">
+        <v>710</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="91" spans="3:10">
       <c r="E91" t="s">
         <v>71</v>
       </c>
@@ -4525,24 +4711,27 @@
         <v>309</v>
       </c>
       <c r="H91" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="92" spans="3:10" x14ac:dyDescent="0.25">
+        <v>410</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="92" spans="3:10">
       <c r="D92" t="s">
         <v>72</v>
       </c>
       <c r="G92" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H92" t="s">
-        <v>775</v>
-      </c>
-      <c r="J92" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="93" spans="3:10" x14ac:dyDescent="0.25">
+        <v>711</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="93" spans="3:10">
       <c r="D93" t="s">
         <v>73</v>
       </c>
@@ -4550,13 +4739,13 @@
         <v>309</v>
       </c>
       <c r="H93" t="s">
-        <v>435</v>
-      </c>
-      <c r="J93" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="94" spans="3:10" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="94" spans="3:10">
       <c r="D94" t="s">
         <v>74</v>
       </c>
@@ -4564,138 +4753,162 @@
         <v>309</v>
       </c>
       <c r="H94" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="95" spans="3:10" x14ac:dyDescent="0.25">
+        <v>415</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="95" spans="3:10">
       <c r="C95" t="s">
         <v>280</v>
       </c>
       <c r="G95" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="96" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="J95" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="96" spans="3:10">
       <c r="C96" t="s">
         <v>75</v>
       </c>
       <c r="G96" t="s">
-        <v>725</v>
+        <v>661</v>
       </c>
       <c r="H96" t="s">
-        <v>776</v>
+        <v>712</v>
       </c>
       <c r="I96" t="s">
-        <v>438</v>
-      </c>
-      <c r="J96" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
+        <v>416</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10">
       <c r="D97" t="s">
         <v>76</v>
       </c>
       <c r="G97" t="s">
-        <v>727</v>
+        <v>663</v>
       </c>
       <c r="H97" t="s">
-        <v>777</v>
+        <v>713</v>
       </c>
       <c r="I97" t="s">
-        <v>440</v>
-      </c>
-      <c r="J97" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
+        <v>417</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10">
       <c r="E98" t="s">
         <v>77</v>
       </c>
       <c r="G98" t="s">
-        <v>442</v>
+        <v>419</v>
       </c>
       <c r="H98" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
+        <v>420</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10">
       <c r="E99" t="s">
         <v>78</v>
       </c>
       <c r="G99" t="s">
-        <v>442</v>
+        <v>419</v>
       </c>
       <c r="H99" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
+        <v>421</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10">
       <c r="D100" t="s">
-        <v>778</v>
+        <v>714</v>
       </c>
       <c r="G100" t="s">
-        <v>728</v>
+        <v>664</v>
       </c>
       <c r="H100" t="s">
-        <v>779</v>
+        <v>715</v>
       </c>
       <c r="I100" t="s">
-        <v>445</v>
-      </c>
-      <c r="J100" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
+        <v>422</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10">
       <c r="E101" t="s">
         <v>79</v>
       </c>
       <c r="G101" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="H101" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10">
       <c r="D102" t="s">
         <v>80</v>
       </c>
       <c r="G102" t="s">
-        <v>729</v>
+        <v>665</v>
       </c>
       <c r="H102" t="s">
-        <v>780</v>
+        <v>716</v>
       </c>
       <c r="I102" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
+        <v>425</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10">
       <c r="D103" t="s">
         <v>81</v>
       </c>
       <c r="G103" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="H103" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
+        <v>426</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="104" spans="2:10">
       <c r="D104" t="s">
         <v>82</v>
       </c>
       <c r="G104" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="H104" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
+        <v>427</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="105" spans="2:10">
       <c r="B105" t="s">
         <v>290</v>
       </c>
@@ -4703,50 +4916,46 @@
         <v>309</v>
       </c>
       <c r="H105" t="s">
-        <v>742</v>
+        <v>678</v>
       </c>
       <c r="I105" t="s">
-        <v>451</v>
-      </c>
-      <c r="J105" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
+        <v>428</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="106" spans="2:10">
       <c r="C106" t="s">
         <v>291</v>
       </c>
       <c r="G106" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H106" t="s">
-        <v>781</v>
+        <v>717</v>
       </c>
       <c r="I106" t="s">
-        <v>452</v>
-      </c>
-      <c r="J106" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
+        <v>429</v>
+      </c>
+      <c r="J106" s="1"/>
+    </row>
+    <row r="107" spans="2:10">
       <c r="D107" t="s">
         <v>83</v>
       </c>
       <c r="G107" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H107" t="s">
-        <v>782</v>
+        <v>718</v>
       </c>
       <c r="I107" t="s">
-        <v>452</v>
-      </c>
-      <c r="J107" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
+        <v>429</v>
+      </c>
+      <c r="J107" s="1"/>
+    </row>
+    <row r="108" spans="2:10">
       <c r="E108" t="s">
         <v>84</v>
       </c>
@@ -4754,10 +4963,13 @@
         <v>309</v>
       </c>
       <c r="H108" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
+        <v>430</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="109" spans="2:10">
       <c r="E109" t="s">
         <v>85</v>
       </c>
@@ -4765,28 +4977,30 @@
         <v>309</v>
       </c>
       <c r="H109" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
+        <v>431</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="110" spans="2:10">
       <c r="D110" t="s">
         <v>86</v>
       </c>
       <c r="G110" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H110" t="s">
-        <v>783</v>
+        <v>719</v>
       </c>
       <c r="I110" t="s">
-        <v>452</v>
-      </c>
-      <c r="J110">
-        <f>85294499531</f>
-        <v>85294499531</v>
-      </c>
-    </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
+        <v>429</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="111" spans="2:10">
       <c r="E111" t="s">
         <v>87</v>
       </c>
@@ -4794,10 +5008,13 @@
         <v>309</v>
       </c>
       <c r="H111" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
+        <v>432</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="112" spans="2:10">
       <c r="E112" t="s">
         <v>88</v>
       </c>
@@ -4805,13 +5022,13 @@
         <v>309</v>
       </c>
       <c r="H112" t="s">
-        <v>457</v>
-      </c>
-      <c r="J112" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="113" spans="3:10" x14ac:dyDescent="0.25">
+        <v>433</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="113" spans="3:10">
       <c r="E113" t="s">
         <v>89</v>
       </c>
@@ -4819,10 +5036,13 @@
         <v>309</v>
       </c>
       <c r="H113" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="114" spans="3:10" x14ac:dyDescent="0.25">
+        <v>433</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="114" spans="3:10">
       <c r="E114" t="s">
         <v>90</v>
       </c>
@@ -4830,27 +5050,30 @@
         <v>309</v>
       </c>
       <c r="H114" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="115" spans="3:10" x14ac:dyDescent="0.25">
+        <v>435</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="115" spans="3:10">
       <c r="D115" t="s">
         <v>91</v>
       </c>
       <c r="G115" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H115" t="s">
-        <v>784</v>
+        <v>720</v>
       </c>
       <c r="I115" t="s">
-        <v>452</v>
-      </c>
-      <c r="J115" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="116" spans="3:10" x14ac:dyDescent="0.25">
+        <v>429</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="116" spans="3:10">
       <c r="E116" t="s">
         <v>92</v>
       </c>
@@ -4858,10 +5081,13 @@
         <v>309</v>
       </c>
       <c r="H116" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="117" spans="3:10" x14ac:dyDescent="0.25">
+        <v>437</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="117" spans="3:10">
       <c r="E117" t="s">
         <v>93</v>
       </c>
@@ -4869,10 +5095,13 @@
         <v>309</v>
       </c>
       <c r="H117" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="118" spans="3:10" x14ac:dyDescent="0.25">
+        <v>438</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="118" spans="3:10">
       <c r="E118" t="s">
         <v>94</v>
       </c>
@@ -4880,10 +5109,13 @@
         <v>309</v>
       </c>
       <c r="H118" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="119" spans="3:10" x14ac:dyDescent="0.25">
+        <v>439</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="119" spans="3:10">
       <c r="E119" t="s">
         <v>95</v>
       </c>
@@ -4891,27 +5123,30 @@
         <v>309</v>
       </c>
       <c r="H119" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="120" spans="3:10" x14ac:dyDescent="0.25">
+        <v>440</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="120" spans="3:10">
       <c r="D120" t="s">
         <v>96</v>
       </c>
       <c r="G120" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H120" t="s">
-        <v>785</v>
+        <v>721</v>
       </c>
       <c r="I120" t="s">
-        <v>465</v>
-      </c>
-      <c r="J120" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="121" spans="3:10" x14ac:dyDescent="0.25">
+        <v>441</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="121" spans="3:10">
       <c r="E121" t="s">
         <v>97</v>
       </c>
@@ -4919,10 +5154,13 @@
         <v>309</v>
       </c>
       <c r="H121" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="122" spans="3:10" x14ac:dyDescent="0.25">
+        <v>442</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="122" spans="3:10">
       <c r="E122" t="s">
         <v>98</v>
       </c>
@@ -4930,27 +5168,30 @@
         <v>309</v>
       </c>
       <c r="H122" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="123" spans="3:10" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="123" spans="3:10">
       <c r="D123" t="s">
         <v>99</v>
       </c>
       <c r="G123" t="s">
-        <v>730</v>
+        <v>666</v>
       </c>
       <c r="H123" t="s">
-        <v>786</v>
+        <v>722</v>
       </c>
       <c r="I123" t="s">
-        <v>469</v>
-      </c>
-      <c r="J123" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="124" spans="3:10" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="124" spans="3:10">
       <c r="E124" t="s">
         <v>100</v>
       </c>
@@ -4958,10 +5199,13 @@
         <v>309</v>
       </c>
       <c r="H124" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="125" spans="3:10" x14ac:dyDescent="0.25">
+        <v>446</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="125" spans="3:10">
       <c r="E125" t="s">
         <v>101</v>
       </c>
@@ -4969,44 +5213,47 @@
         <v>309</v>
       </c>
       <c r="H125" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="126" spans="3:10" x14ac:dyDescent="0.25">
+        <v>447</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="126" spans="3:10">
       <c r="C126" t="s">
         <v>275</v>
       </c>
       <c r="G126" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H126" t="s">
-        <v>787</v>
+        <v>723</v>
       </c>
       <c r="I126" t="s">
-        <v>473</v>
-      </c>
-      <c r="J126" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="127" spans="3:10" x14ac:dyDescent="0.25">
+        <v>448</v>
+      </c>
+      <c r="J126" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="127" spans="3:10">
       <c r="D127" t="s">
         <v>102</v>
       </c>
       <c r="G127" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H127" t="s">
-        <v>788</v>
+        <v>724</v>
       </c>
       <c r="I127" t="s">
-        <v>475</v>
-      </c>
-      <c r="J127" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="128" spans="3:10" x14ac:dyDescent="0.25">
+        <v>450</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="128" spans="3:10">
       <c r="E128" t="s">
         <v>103</v>
       </c>
@@ -5014,10 +5261,13 @@
         <v>309</v>
       </c>
       <c r="H128" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="129" spans="3:10" x14ac:dyDescent="0.25">
+        <v>452</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="129" spans="3:10">
       <c r="E129" t="s">
         <v>104</v>
       </c>
@@ -5025,27 +5275,30 @@
         <v>309</v>
       </c>
       <c r="H129" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="130" spans="3:10" x14ac:dyDescent="0.25">
+        <v>453</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="130" spans="3:10">
       <c r="D130" t="s">
         <v>105</v>
       </c>
       <c r="G130" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H130" t="s">
-        <v>789</v>
+        <v>725</v>
       </c>
       <c r="I130" t="s">
-        <v>479</v>
-      </c>
-      <c r="J130" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="131" spans="3:10" x14ac:dyDescent="0.25">
+        <v>454</v>
+      </c>
+      <c r="J130" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="131" spans="3:10">
       <c r="E131" t="s">
         <v>106</v>
       </c>
@@ -5053,27 +5306,30 @@
         <v>309</v>
       </c>
       <c r="H131" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="132" spans="3:10" x14ac:dyDescent="0.25">
+        <v>455</v>
+      </c>
+      <c r="J131" s="1" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="132" spans="3:10">
       <c r="D132" t="s">
         <v>107</v>
       </c>
       <c r="G132" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H132" t="s">
-        <v>790</v>
+        <v>726</v>
       </c>
       <c r="I132" t="s">
-        <v>482</v>
-      </c>
-      <c r="J132" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="133" spans="3:10" x14ac:dyDescent="0.25">
+        <v>456</v>
+      </c>
+      <c r="J132" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="133" spans="3:10">
       <c r="E133" t="s">
         <v>108</v>
       </c>
@@ -5081,27 +5337,30 @@
         <v>309</v>
       </c>
       <c r="H133" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="134" spans="3:10" x14ac:dyDescent="0.25">
+        <v>457</v>
+      </c>
+      <c r="J133" s="1" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="134" spans="3:10">
       <c r="D134" t="s">
         <v>109</v>
       </c>
       <c r="G134" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H134" t="s">
-        <v>791</v>
+        <v>727</v>
       </c>
       <c r="I134" t="s">
-        <v>485</v>
-      </c>
-      <c r="J134" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="135" spans="3:10" x14ac:dyDescent="0.25">
+        <v>458</v>
+      </c>
+      <c r="J134" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="135" spans="3:10">
       <c r="E135" t="s">
         <v>110</v>
       </c>
@@ -5109,10 +5368,13 @@
         <v>309</v>
       </c>
       <c r="H135" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="136" spans="3:10" x14ac:dyDescent="0.25">
+        <v>460</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="136" spans="3:10">
       <c r="E136" t="s">
         <v>111</v>
       </c>
@@ -5120,10 +5382,13 @@
         <v>309</v>
       </c>
       <c r="H136" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="137" spans="3:10" x14ac:dyDescent="0.25">
+        <v>461</v>
+      </c>
+      <c r="J136" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="137" spans="3:10">
       <c r="D137" t="s">
         <v>112</v>
       </c>
@@ -5131,16 +5396,16 @@
         <v>309</v>
       </c>
       <c r="H137" t="s">
-        <v>792</v>
+        <v>728</v>
       </c>
       <c r="I137" t="s">
-        <v>489</v>
-      </c>
-      <c r="J137" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="138" spans="3:10" x14ac:dyDescent="0.25">
+        <v>462</v>
+      </c>
+      <c r="J137" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="138" spans="3:10">
       <c r="E138" t="s">
         <v>113</v>
       </c>
@@ -5148,27 +5413,30 @@
         <v>309</v>
       </c>
       <c r="H138" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="139" spans="3:10" x14ac:dyDescent="0.25">
+        <v>464</v>
+      </c>
+      <c r="J138" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="139" spans="3:10">
       <c r="D139" t="s">
         <v>114</v>
       </c>
       <c r="G139" t="s">
-        <v>731</v>
+        <v>667</v>
       </c>
       <c r="H139" t="s">
-        <v>793</v>
+        <v>729</v>
       </c>
       <c r="I139" t="s">
-        <v>473</v>
-      </c>
-      <c r="J139" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="140" spans="3:10" x14ac:dyDescent="0.25">
+        <v>448</v>
+      </c>
+      <c r="J139" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="140" spans="3:10">
       <c r="E140" t="s">
         <v>115</v>
       </c>
@@ -5176,38 +5444,47 @@
         <v>309</v>
       </c>
       <c r="H140" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="141" spans="3:10" x14ac:dyDescent="0.25">
+        <v>465</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="141" spans="3:10">
       <c r="C141" t="s">
         <v>292</v>
       </c>
       <c r="G141" t="s">
-        <v>732</v>
+        <v>668</v>
       </c>
       <c r="H141" t="s">
-        <v>794</v>
+        <v>730</v>
       </c>
       <c r="I141" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="142" spans="3:10" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+      <c r="J141" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="142" spans="3:10">
       <c r="D142" t="s">
         <v>116</v>
       </c>
       <c r="G142" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H142" t="s">
-        <v>795</v>
+        <v>731</v>
       </c>
       <c r="I142" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="143" spans="3:10" x14ac:dyDescent="0.25">
+        <v>467</v>
+      </c>
+      <c r="J142" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="143" spans="3:10">
       <c r="E143" t="s">
         <v>117</v>
       </c>
@@ -5215,10 +5492,13 @@
         <v>309</v>
       </c>
       <c r="H143" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="144" spans="3:10" x14ac:dyDescent="0.25">
+        <v>468</v>
+      </c>
+      <c r="J143" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="144" spans="3:10">
       <c r="E144" t="s">
         <v>118</v>
       </c>
@@ -5226,27 +5506,30 @@
         <v>309</v>
       </c>
       <c r="H144" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="145" spans="3:10" x14ac:dyDescent="0.25">
+        <v>469</v>
+      </c>
+      <c r="J144" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="145" spans="3:10">
       <c r="D145" t="s">
         <v>119</v>
       </c>
       <c r="G145" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H145" t="s">
-        <v>796</v>
+        <v>732</v>
       </c>
       <c r="I145" t="s">
-        <v>497</v>
-      </c>
-      <c r="J145" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="146" spans="3:10" x14ac:dyDescent="0.25">
+        <v>470</v>
+      </c>
+      <c r="J145" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="146" spans="3:10">
       <c r="E146" t="s">
         <v>120</v>
       </c>
@@ -5254,10 +5537,13 @@
         <v>309</v>
       </c>
       <c r="H146" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="147" spans="3:10" x14ac:dyDescent="0.25">
+        <v>471</v>
+      </c>
+      <c r="J146" s="1" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="147" spans="3:10">
       <c r="E147" t="s">
         <v>121</v>
       </c>
@@ -5265,274 +5551,295 @@
         <v>309</v>
       </c>
       <c r="H147" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="148" spans="3:10" x14ac:dyDescent="0.25">
+        <v>472</v>
+      </c>
+      <c r="J147" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="148" spans="3:10">
       <c r="C148" t="s">
         <v>122</v>
       </c>
       <c r="G148" t="s">
-        <v>719</v>
+        <v>655</v>
       </c>
       <c r="H148" t="s">
-        <v>797</v>
+        <v>733</v>
       </c>
       <c r="I148" t="s">
-        <v>501</v>
-      </c>
-      <c r="J148" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="149" spans="3:10" x14ac:dyDescent="0.25">
+        <v>473</v>
+      </c>
+      <c r="J148" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="149" spans="3:10">
       <c r="D149" t="s">
         <v>123</v>
       </c>
       <c r="G149" t="s">
-        <v>508</v>
+        <v>477</v>
       </c>
       <c r="H149" t="s">
-        <v>798</v>
+        <v>734</v>
       </c>
       <c r="I149" t="s">
-        <v>503</v>
-      </c>
-      <c r="J149" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="150" spans="3:10" x14ac:dyDescent="0.25">
+        <v>474</v>
+      </c>
+      <c r="J149" s="1" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="150" spans="3:10">
       <c r="D150" t="s">
         <v>124</v>
       </c>
       <c r="G150" t="s">
-        <v>733</v>
+        <v>669</v>
       </c>
       <c r="H150" t="s">
-        <v>799</v>
+        <v>735</v>
       </c>
       <c r="I150" t="s">
-        <v>505</v>
-      </c>
-      <c r="J150" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="151" spans="3:10" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+      <c r="J150" s="1" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="151" spans="3:10">
       <c r="E151" t="s">
         <v>125</v>
       </c>
       <c r="G151" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="H151" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="152" spans="3:10" x14ac:dyDescent="0.25">
+        <v>476</v>
+      </c>
+      <c r="J151" s="1" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="152" spans="3:10">
       <c r="D152" t="s">
         <v>126</v>
       </c>
       <c r="G152" t="s">
-        <v>508</v>
+        <v>477</v>
       </c>
       <c r="H152" t="s">
-        <v>800</v>
+        <v>736</v>
       </c>
       <c r="I152" t="s">
-        <v>501</v>
-      </c>
-      <c r="J152" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="153" spans="3:10" x14ac:dyDescent="0.25">
+        <v>473</v>
+      </c>
+      <c r="J152" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="153" spans="3:10">
       <c r="C153" t="s">
         <v>127</v>
       </c>
       <c r="G153" t="s">
-        <v>724</v>
+        <v>660</v>
       </c>
       <c r="H153" t="s">
-        <v>801</v>
+        <v>737</v>
       </c>
       <c r="I153" t="s">
-        <v>510</v>
-      </c>
-      <c r="J153" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="154" spans="3:10" x14ac:dyDescent="0.25">
+        <v>478</v>
+      </c>
+      <c r="J153" s="1" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="154" spans="3:10">
       <c r="D154" t="s">
-        <v>802</v>
+        <v>738</v>
       </c>
       <c r="G154" t="s">
-        <v>734</v>
+        <v>670</v>
       </c>
       <c r="H154" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="155" spans="3:10" x14ac:dyDescent="0.25">
+        <v>739</v>
+      </c>
+      <c r="J154" s="1" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="155" spans="3:10">
       <c r="E155" t="s">
         <v>128</v>
       </c>
       <c r="G155" t="s">
-        <v>512</v>
+        <v>479</v>
       </c>
       <c r="H155" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="156" spans="3:10" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+      <c r="J155" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="156" spans="3:10">
       <c r="E156" t="s">
         <v>129</v>
       </c>
       <c r="G156" t="s">
-        <v>512</v>
+        <v>479</v>
       </c>
       <c r="H156" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="157" spans="3:10" x14ac:dyDescent="0.25">
+        <v>481</v>
+      </c>
+      <c r="J156" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="157" spans="3:10">
       <c r="D157" t="s">
-        <v>804</v>
+        <v>740</v>
       </c>
       <c r="G157" t="s">
-        <v>735</v>
+        <v>671</v>
       </c>
       <c r="H157" t="s">
-        <v>805</v>
-      </c>
-      <c r="J157" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="158" spans="3:10" x14ac:dyDescent="0.25">
+        <v>741</v>
+      </c>
+      <c r="J157" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="158" spans="3:10">
       <c r="C158" t="s">
         <v>293</v>
       </c>
       <c r="G158" t="s">
-        <v>718</v>
+        <v>654</v>
       </c>
       <c r="H158" t="s">
-        <v>806</v>
+        <v>742</v>
       </c>
       <c r="I158" t="s">
-        <v>516</v>
-      </c>
-      <c r="J158" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="159" spans="3:10" x14ac:dyDescent="0.25">
+        <v>483</v>
+      </c>
+      <c r="J158" s="1" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="159" spans="3:10">
       <c r="D159" t="s">
         <v>130</v>
       </c>
       <c r="G159" t="s">
-        <v>736</v>
+        <v>672</v>
       </c>
       <c r="H159" t="s">
-        <v>807</v>
+        <v>743</v>
       </c>
       <c r="I159" t="s">
-        <v>518</v>
-      </c>
-      <c r="J159" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="160" spans="3:10" x14ac:dyDescent="0.25">
+        <v>484</v>
+      </c>
+      <c r="J159" s="1" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="160" spans="3:10">
       <c r="E160" t="s">
         <v>131</v>
       </c>
       <c r="G160" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="H160" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="161" spans="3:10" x14ac:dyDescent="0.25">
+        <v>486</v>
+      </c>
+      <c r="J160" s="1" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="161" spans="3:10">
       <c r="E161" t="s">
         <v>132</v>
       </c>
       <c r="G161" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="H161" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="162" spans="3:10" x14ac:dyDescent="0.25">
+        <v>487</v>
+      </c>
+      <c r="J161" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="162" spans="3:10">
       <c r="D162" t="s">
         <v>133</v>
       </c>
       <c r="G162" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="H162" t="s">
-        <v>523</v>
+        <v>488</v>
       </c>
       <c r="I162" t="s">
-        <v>516</v>
-      </c>
-      <c r="J162" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="163" spans="3:10" x14ac:dyDescent="0.25">
+        <v>483</v>
+      </c>
+      <c r="J162" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="163" spans="3:10">
       <c r="D163" t="s">
         <v>134</v>
       </c>
       <c r="G163" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="H163" t="s">
-        <v>525</v>
-      </c>
-      <c r="J163" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="164" spans="3:10" x14ac:dyDescent="0.25">
+        <v>490</v>
+      </c>
+      <c r="J163" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="164" spans="3:10">
       <c r="C164" t="s">
         <v>276</v>
       </c>
       <c r="G164" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H164" t="s">
-        <v>808</v>
+        <v>744</v>
       </c>
       <c r="I164" t="s">
-        <v>527</v>
-      </c>
-      <c r="J164" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="165" spans="3:10" x14ac:dyDescent="0.25">
+        <v>492</v>
+      </c>
+      <c r="J164" s="1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="165" spans="3:10">
       <c r="D165" t="s">
         <v>135</v>
       </c>
       <c r="G165" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H165" t="s">
-        <v>809</v>
+        <v>745</v>
       </c>
       <c r="I165" t="s">
-        <v>529</v>
-      </c>
-      <c r="J165" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="166" spans="3:10" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+      <c r="J165" s="1" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="166" spans="3:10">
       <c r="E166" t="s">
         <v>136</v>
       </c>
@@ -5540,10 +5847,13 @@
         <v>309</v>
       </c>
       <c r="H166" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="167" spans="3:10" x14ac:dyDescent="0.25">
+        <v>495</v>
+      </c>
+      <c r="J166" s="1" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="167" spans="3:10">
       <c r="E167" t="s">
         <v>137</v>
       </c>
@@ -5551,10 +5861,13 @@
         <v>309</v>
       </c>
       <c r="H167" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="168" spans="3:10" x14ac:dyDescent="0.25">
+        <v>496</v>
+      </c>
+      <c r="J167" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="168" spans="3:10">
       <c r="E168" t="s">
         <v>138</v>
       </c>
@@ -5562,10 +5875,13 @@
         <v>309</v>
       </c>
       <c r="H168" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="169" spans="3:10" x14ac:dyDescent="0.25">
+        <v>497</v>
+      </c>
+      <c r="J168" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="169" spans="3:10">
       <c r="E169" t="s">
         <v>139</v>
       </c>
@@ -5573,27 +5889,30 @@
         <v>309</v>
       </c>
       <c r="H169" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="170" spans="3:10" x14ac:dyDescent="0.25">
+        <v>498</v>
+      </c>
+      <c r="J169" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="170" spans="3:10">
       <c r="D170" t="s">
         <v>294</v>
       </c>
       <c r="G170" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H170" t="s">
-        <v>810</v>
+        <v>746</v>
       </c>
       <c r="I170" t="s">
-        <v>535</v>
-      </c>
-      <c r="J170" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="171" spans="3:10" x14ac:dyDescent="0.25">
+        <v>499</v>
+      </c>
+      <c r="J170" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="171" spans="3:10">
       <c r="E171" t="s">
         <v>140</v>
       </c>
@@ -5601,10 +5920,13 @@
         <v>309</v>
       </c>
       <c r="H171" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="172" spans="3:10" x14ac:dyDescent="0.25">
+        <v>501</v>
+      </c>
+      <c r="J171" s="1" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="172" spans="3:10">
       <c r="E172" t="s">
         <v>141</v>
       </c>
@@ -5612,10 +5934,13 @@
         <v>309</v>
       </c>
       <c r="H172" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="173" spans="3:10" x14ac:dyDescent="0.25">
+        <v>502</v>
+      </c>
+      <c r="J172" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="173" spans="3:10">
       <c r="E173" t="s">
         <v>142</v>
       </c>
@@ -5623,10 +5948,13 @@
         <v>309</v>
       </c>
       <c r="H173" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="174" spans="3:10" x14ac:dyDescent="0.25">
+        <v>503</v>
+      </c>
+      <c r="J173" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="174" spans="3:10">
       <c r="E174" t="s">
         <v>143</v>
       </c>
@@ -5634,10 +5962,13 @@
         <v>309</v>
       </c>
       <c r="H174" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="175" spans="3:10" x14ac:dyDescent="0.25">
+        <v>504</v>
+      </c>
+      <c r="J174" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="175" spans="3:10">
       <c r="E175" t="s">
         <v>144</v>
       </c>
@@ -5645,10 +5976,13 @@
         <v>309</v>
       </c>
       <c r="H175" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="176" spans="3:10" x14ac:dyDescent="0.25">
+        <v>505</v>
+      </c>
+      <c r="J175" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="176" spans="3:10">
       <c r="E176" t="s">
         <v>145</v>
       </c>
@@ -5656,38 +5990,44 @@
         <v>309</v>
       </c>
       <c r="H176" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="177" spans="3:10" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+      <c r="J176" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="177" spans="3:10">
       <c r="D177" t="s">
         <v>146</v>
       </c>
       <c r="G177" t="s">
-        <v>725</v>
+        <v>661</v>
       </c>
       <c r="H177" t="s">
-        <v>811</v>
+        <v>747</v>
       </c>
       <c r="I177" t="s">
-        <v>543</v>
-      </c>
-      <c r="J177" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="178" spans="3:10" x14ac:dyDescent="0.25">
+        <v>507</v>
+      </c>
+      <c r="J177" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="178" spans="3:10">
       <c r="E178" t="s">
         <v>147</v>
       </c>
       <c r="G178" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="H178" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="179" spans="3:10" x14ac:dyDescent="0.25">
+        <v>508</v>
+      </c>
+      <c r="J178" s="1" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="179" spans="3:10">
       <c r="D179" t="s">
         <v>148</v>
       </c>
@@ -5695,33 +6035,33 @@
         <v>309</v>
       </c>
       <c r="H179" t="s">
-        <v>546</v>
+        <v>509</v>
       </c>
       <c r="I179" t="s">
-        <v>529</v>
-      </c>
-      <c r="J179" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="180" spans="3:10" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+      <c r="J179" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="180" spans="3:10">
       <c r="C180" t="s">
         <v>295</v>
       </c>
       <c r="G180" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H180" t="s">
-        <v>812</v>
+        <v>748</v>
       </c>
       <c r="I180" t="s">
-        <v>547</v>
-      </c>
-      <c r="J180" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="181" spans="3:10" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+      <c r="J180" s="1" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="181" spans="3:10">
       <c r="D181" t="s">
         <v>149</v>
       </c>
@@ -5729,10 +6069,13 @@
         <v>309</v>
       </c>
       <c r="H181" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="182" spans="3:10" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+      <c r="J181" s="1" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="182" spans="3:10">
       <c r="D182" t="s">
         <v>150</v>
       </c>
@@ -5740,10 +6083,13 @@
         <v>309</v>
       </c>
       <c r="H182" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="183" spans="3:10" x14ac:dyDescent="0.25">
+        <v>512</v>
+      </c>
+      <c r="J182" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="183" spans="3:10">
       <c r="D183" t="s">
         <v>151</v>
       </c>
@@ -5751,28 +6097,30 @@
         <v>309</v>
       </c>
       <c r="H183" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="184" spans="3:10" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+      <c r="J183" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="184" spans="3:10">
       <c r="C184" t="s">
         <v>268</v>
       </c>
       <c r="G184" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H184" t="s">
-        <v>813</v>
+        <v>749</v>
       </c>
       <c r="I184" t="s">
-        <v>552</v>
-      </c>
-      <c r="J184">
-        <f>966507181873</f>
-        <v>966507181873</v>
-      </c>
-    </row>
-    <row r="185" spans="3:10" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+      <c r="J184" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="185" spans="3:10">
       <c r="D185" t="s">
         <v>152</v>
       </c>
@@ -5780,13 +6128,13 @@
         <v>309</v>
       </c>
       <c r="H185" t="s">
-        <v>553</v>
-      </c>
-      <c r="J185" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="186" spans="3:10" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+      <c r="J185" s="1" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="186" spans="3:10">
       <c r="D186" t="s">
         <v>301</v>
       </c>
@@ -5794,10 +6142,13 @@
         <v>309</v>
       </c>
       <c r="H186" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="187" spans="3:10" x14ac:dyDescent="0.25">
+        <v>517</v>
+      </c>
+      <c r="J186" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="187" spans="3:10">
       <c r="D187" t="s">
         <v>307</v>
       </c>
@@ -5805,10 +6156,13 @@
         <v>309</v>
       </c>
       <c r="H187" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="188" spans="3:10" x14ac:dyDescent="0.25">
+        <v>518</v>
+      </c>
+      <c r="J187" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="188" spans="3:10">
       <c r="C188" t="s">
         <v>153</v>
       </c>
@@ -5816,149 +6170,170 @@
         <v>309</v>
       </c>
       <c r="H188" t="s">
-        <v>557</v>
-      </c>
-      <c r="J188" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="189" spans="3:10" x14ac:dyDescent="0.25">
+        <v>519</v>
+      </c>
+      <c r="J188" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="189" spans="3:10">
       <c r="C189" t="s">
         <v>154</v>
       </c>
       <c r="G189" t="s">
-        <v>718</v>
+        <v>654</v>
       </c>
       <c r="H189" t="s">
-        <v>814</v>
+        <v>750</v>
       </c>
       <c r="I189" t="s">
-        <v>559</v>
-      </c>
-      <c r="J189" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="190" spans="3:10" x14ac:dyDescent="0.25">
+        <v>521</v>
+      </c>
+      <c r="J189" s="1" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="190" spans="3:10">
       <c r="D190" t="s">
         <v>269</v>
       </c>
       <c r="G190" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="H190" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="191" spans="3:10" x14ac:dyDescent="0.25">
+        <v>523</v>
+      </c>
+      <c r="J190" s="1" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="191" spans="3:10">
       <c r="D191" t="s">
-        <v>815</v>
+        <v>751</v>
       </c>
       <c r="G191" t="s">
-        <v>737</v>
+        <v>673</v>
       </c>
       <c r="H191" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="192" spans="3:10" x14ac:dyDescent="0.25">
+        <v>752</v>
+      </c>
+      <c r="J191" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="192" spans="3:10">
       <c r="E192" t="s">
         <v>155</v>
       </c>
       <c r="G192" t="s">
-        <v>562</v>
+        <v>524</v>
       </c>
       <c r="H192" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="193" spans="2:10" x14ac:dyDescent="0.25">
+        <v>402</v>
+      </c>
+      <c r="J192" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="193" spans="2:10">
       <c r="D193" t="s">
         <v>156</v>
       </c>
       <c r="G193" t="s">
-        <v>736</v>
+        <v>672</v>
       </c>
       <c r="H193" t="s">
-        <v>817</v>
-      </c>
-      <c r="J193" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="194" spans="2:10" x14ac:dyDescent="0.25">
+        <v>753</v>
+      </c>
+      <c r="J193" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="194" spans="2:10">
       <c r="E194" t="s">
         <v>157</v>
       </c>
       <c r="G194" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="H194" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="195" spans="2:10" x14ac:dyDescent="0.25">
+        <v>526</v>
+      </c>
+      <c r="J194" s="1" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="195" spans="2:10">
       <c r="E195" t="s">
         <v>158</v>
       </c>
       <c r="G195" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="H195" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="196" spans="2:10" x14ac:dyDescent="0.25">
+        <v>527</v>
+      </c>
+      <c r="J195" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="196" spans="2:10">
       <c r="E196" t="s">
         <v>159</v>
       </c>
       <c r="G196" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="H196" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="197" spans="2:10" x14ac:dyDescent="0.25">
+        <v>528</v>
+      </c>
+      <c r="J196" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="197" spans="2:10">
       <c r="D197" t="s">
         <v>160</v>
       </c>
       <c r="G197" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="H197" t="s">
-        <v>567</v>
-      </c>
-      <c r="J197" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="198" spans="2:10" x14ac:dyDescent="0.25">
+        <v>529</v>
+      </c>
+      <c r="J197" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="198" spans="2:10">
       <c r="D198" t="s">
         <v>161</v>
       </c>
       <c r="G198" t="s">
-        <v>736</v>
+        <v>672</v>
       </c>
       <c r="H198" t="s">
-        <v>818</v>
-      </c>
-      <c r="J198" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="199" spans="2:10" x14ac:dyDescent="0.25">
+        <v>754</v>
+      </c>
+      <c r="J198" s="1" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="199" spans="2:10">
       <c r="D199" t="s">
         <v>162</v>
       </c>
       <c r="G199" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="H199" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="200" spans="2:10" x14ac:dyDescent="0.25">
+        <v>531</v>
+      </c>
+      <c r="J199" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="200" spans="2:10">
       <c r="C200" t="s">
         <v>281</v>
       </c>
@@ -5966,72 +6341,78 @@
         <v>309</v>
       </c>
       <c r="H200" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="201" spans="2:10" x14ac:dyDescent="0.25">
+        <v>532</v>
+      </c>
+      <c r="J200" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="201" spans="2:10">
       <c r="B201" t="s">
         <v>302</v>
       </c>
       <c r="G201" t="s">
-        <v>718</v>
+        <v>654</v>
       </c>
       <c r="H201" t="s">
-        <v>860</v>
+        <v>795</v>
       </c>
       <c r="I201" t="s">
-        <v>571</v>
-      </c>
-      <c r="J201" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="202" spans="2:10" x14ac:dyDescent="0.25">
+        <v>533</v>
+      </c>
+      <c r="J201" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="202" spans="2:10">
       <c r="C202" t="s">
-        <v>819</v>
+        <v>755</v>
       </c>
       <c r="G202" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H202" t="s">
-        <v>861</v>
+        <v>796</v>
       </c>
       <c r="I202" t="s">
-        <v>573</v>
-      </c>
-      <c r="J202" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="203" spans="2:10" x14ac:dyDescent="0.25">
+        <v>535</v>
+      </c>
+      <c r="J202" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="203" spans="2:10">
       <c r="D203" t="s">
         <v>163</v>
       </c>
       <c r="G203" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H203" t="s">
-        <v>820</v>
+        <v>756</v>
       </c>
       <c r="I203" t="s">
-        <v>575</v>
-      </c>
-      <c r="J203" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="204" spans="2:10" x14ac:dyDescent="0.25">
+        <v>536</v>
+      </c>
+      <c r="J203" s="1" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="204" spans="2:10">
       <c r="E204" t="s">
         <v>164</v>
       </c>
       <c r="G204" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H204" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="205" spans="2:10" x14ac:dyDescent="0.25">
+        <v>757</v>
+      </c>
+      <c r="J204" s="1" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="205" spans="2:10">
       <c r="F205" t="s">
         <v>165</v>
       </c>
@@ -6039,10 +6420,13 @@
         <v>309</v>
       </c>
       <c r="H205" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="206" spans="2:10" x14ac:dyDescent="0.25">
+        <v>537</v>
+      </c>
+      <c r="J205" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="206" spans="2:10">
       <c r="F206" t="s">
         <v>166</v>
       </c>
@@ -6050,10 +6434,13 @@
         <v>309</v>
       </c>
       <c r="H206" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="207" spans="2:10" x14ac:dyDescent="0.25">
+        <v>538</v>
+      </c>
+      <c r="J206" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="207" spans="2:10">
       <c r="E207" t="s">
         <v>167</v>
       </c>
@@ -6061,10 +6448,13 @@
         <v>309</v>
       </c>
       <c r="H207" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="208" spans="2:10" x14ac:dyDescent="0.25">
+        <v>539</v>
+      </c>
+      <c r="J207" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="208" spans="2:10">
       <c r="E208" t="s">
         <v>168</v>
       </c>
@@ -6072,121 +6462,145 @@
         <v>309</v>
       </c>
       <c r="H208" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="209" spans="4:10" x14ac:dyDescent="0.25">
+        <v>540</v>
+      </c>
+      <c r="J208" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="209" spans="4:10">
       <c r="D209" t="s">
         <v>303</v>
       </c>
       <c r="G209" t="s">
-        <v>718</v>
+        <v>654</v>
       </c>
       <c r="H209" t="s">
-        <v>862</v>
+        <v>797</v>
       </c>
       <c r="I209" t="s">
-        <v>581</v>
-      </c>
-      <c r="J209" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="210" spans="4:10" x14ac:dyDescent="0.25">
+        <v>541</v>
+      </c>
+      <c r="J209" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="210" spans="4:10">
       <c r="E210" t="s">
         <v>169</v>
       </c>
       <c r="G210" t="s">
-        <v>582</v>
+        <v>542</v>
       </c>
       <c r="H210" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="211" spans="4:10" x14ac:dyDescent="0.25">
+        <v>543</v>
+      </c>
+      <c r="J210" s="1" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="211" spans="4:10">
       <c r="E211" t="s">
         <v>170</v>
       </c>
       <c r="G211" t="s">
-        <v>582</v>
+        <v>542</v>
       </c>
       <c r="H211" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="212" spans="4:10" x14ac:dyDescent="0.25">
+        <v>544</v>
+      </c>
+      <c r="J211" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="212" spans="4:10">
       <c r="E212" t="s">
         <v>171</v>
       </c>
       <c r="G212" t="s">
-        <v>582</v>
+        <v>542</v>
       </c>
       <c r="H212" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="213" spans="4:10" x14ac:dyDescent="0.25">
+        <v>545</v>
+      </c>
+      <c r="J212" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="213" spans="4:10">
       <c r="E213" t="s">
         <v>172</v>
       </c>
       <c r="G213" t="s">
-        <v>582</v>
+        <v>542</v>
       </c>
       <c r="H213" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="214" spans="4:10" x14ac:dyDescent="0.25">
+        <v>546</v>
+      </c>
+      <c r="J213" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="214" spans="4:10">
       <c r="E214" t="s">
         <v>173</v>
       </c>
       <c r="G214" t="s">
-        <v>582</v>
+        <v>542</v>
       </c>
       <c r="H214" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="215" spans="4:10" x14ac:dyDescent="0.25">
+        <v>547</v>
+      </c>
+      <c r="J214" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="215" spans="4:10">
       <c r="E215" t="s">
         <v>174</v>
       </c>
       <c r="G215" t="s">
-        <v>582</v>
+        <v>542</v>
       </c>
       <c r="H215" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="216" spans="4:10" x14ac:dyDescent="0.25">
+        <v>548</v>
+      </c>
+      <c r="J215" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="216" spans="4:10">
       <c r="D216" t="s">
         <v>175</v>
       </c>
       <c r="G216" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H216" t="s">
-        <v>823</v>
+        <v>758</v>
       </c>
       <c r="I216" t="s">
-        <v>589</v>
-      </c>
-      <c r="J216" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="217" spans="4:10" x14ac:dyDescent="0.25">
+        <v>549</v>
+      </c>
+      <c r="J216" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="217" spans="4:10">
       <c r="E217" t="s">
-        <v>824</v>
+        <v>759</v>
       </c>
       <c r="G217" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H217" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="218" spans="4:10" x14ac:dyDescent="0.25">
+        <v>760</v>
+      </c>
+      <c r="J217" s="1" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="218" spans="4:10">
       <c r="F218" t="s">
         <v>176</v>
       </c>
@@ -6194,10 +6608,13 @@
         <v>309</v>
       </c>
       <c r="H218" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="219" spans="4:10" x14ac:dyDescent="0.25">
+        <v>550</v>
+      </c>
+      <c r="J218" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="219" spans="4:10">
       <c r="F219" t="s">
         <v>177</v>
       </c>
@@ -6205,10 +6622,13 @@
         <v>309</v>
       </c>
       <c r="H219" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="220" spans="4:10" x14ac:dyDescent="0.25">
+        <v>551</v>
+      </c>
+      <c r="J219" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="220" spans="4:10">
       <c r="F220" t="s">
         <v>178</v>
       </c>
@@ -6216,21 +6636,27 @@
         <v>309</v>
       </c>
       <c r="H220" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="221" spans="4:10" x14ac:dyDescent="0.25">
+        <v>552</v>
+      </c>
+      <c r="J220" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="221" spans="4:10">
       <c r="E221" t="s">
         <v>179</v>
       </c>
       <c r="G221" t="s">
-        <v>754</v>
+        <v>690</v>
       </c>
       <c r="H221" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="222" spans="4:10" x14ac:dyDescent="0.25">
+        <v>761</v>
+      </c>
+      <c r="J221" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="222" spans="4:10">
       <c r="F222" t="s">
         <v>180</v>
       </c>
@@ -6238,10 +6664,13 @@
         <v>309</v>
       </c>
       <c r="H222" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="223" spans="4:10" x14ac:dyDescent="0.25">
+        <v>553</v>
+      </c>
+      <c r="J222" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="223" spans="4:10">
       <c r="E223" t="s">
         <v>181</v>
       </c>
@@ -6249,10 +6678,13 @@
         <v>309</v>
       </c>
       <c r="H223" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="224" spans="4:10" x14ac:dyDescent="0.25">
+        <v>554</v>
+      </c>
+      <c r="J223" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="224" spans="4:10">
       <c r="E224" t="s">
         <v>182</v>
       </c>
@@ -6260,10 +6692,13 @@
         <v>309</v>
       </c>
       <c r="H224" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="225" spans="4:10" x14ac:dyDescent="0.25">
+        <v>555</v>
+      </c>
+      <c r="J224" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="225" spans="4:10">
       <c r="E225" t="s">
         <v>183</v>
       </c>
@@ -6271,10 +6706,13 @@
         <v>309</v>
       </c>
       <c r="H225" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="226" spans="4:10" x14ac:dyDescent="0.25">
+        <v>556</v>
+      </c>
+      <c r="J225" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="226" spans="4:10">
       <c r="E226" t="s">
         <v>184</v>
       </c>
@@ -6282,10 +6720,13 @@
         <v>309</v>
       </c>
       <c r="H226" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="227" spans="4:10" x14ac:dyDescent="0.25">
+        <v>557</v>
+      </c>
+      <c r="J226" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="227" spans="4:10">
       <c r="E227" t="s">
         <v>185</v>
       </c>
@@ -6293,27 +6734,30 @@
         <v>309</v>
       </c>
       <c r="H227" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="228" spans="4:10" x14ac:dyDescent="0.25">
+        <v>558</v>
+      </c>
+      <c r="J227" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="228" spans="4:10">
       <c r="D228" t="s">
         <v>277</v>
       </c>
       <c r="G228" t="s">
-        <v>718</v>
+        <v>654</v>
       </c>
       <c r="H228" t="s">
-        <v>827</v>
+        <v>762</v>
       </c>
       <c r="I228" t="s">
-        <v>600</v>
-      </c>
-      <c r="J228" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="229" spans="4:10" x14ac:dyDescent="0.25">
+        <v>559</v>
+      </c>
+      <c r="J228" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="229" spans="4:10">
       <c r="E229" t="s">
         <v>186</v>
       </c>
@@ -6321,10 +6765,13 @@
         <v>309</v>
       </c>
       <c r="H229" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="230" spans="4:10" x14ac:dyDescent="0.25">
+        <v>561</v>
+      </c>
+      <c r="J229" s="1" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="230" spans="4:10">
       <c r="E230" t="s">
         <v>187</v>
       </c>
@@ -6332,10 +6779,13 @@
         <v>309</v>
       </c>
       <c r="H230" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="231" spans="4:10" x14ac:dyDescent="0.25">
+        <v>562</v>
+      </c>
+      <c r="J230" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="231" spans="4:10">
       <c r="E231" t="s">
         <v>188</v>
       </c>
@@ -6343,10 +6793,13 @@
         <v>309</v>
       </c>
       <c r="H231" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="232" spans="4:10" x14ac:dyDescent="0.25">
+        <v>563</v>
+      </c>
+      <c r="J231" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="232" spans="4:10">
       <c r="E232" t="s">
         <v>189</v>
       </c>
@@ -6354,10 +6807,13 @@
         <v>309</v>
       </c>
       <c r="H232" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="233" spans="4:10" x14ac:dyDescent="0.25">
+        <v>564</v>
+      </c>
+      <c r="J232" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="233" spans="4:10">
       <c r="E233" t="s">
         <v>190</v>
       </c>
@@ -6365,27 +6821,30 @@
         <v>309</v>
       </c>
       <c r="H233" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="234" spans="4:10" x14ac:dyDescent="0.25">
+        <v>565</v>
+      </c>
+      <c r="J233" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="234" spans="4:10">
       <c r="D234" t="s">
         <v>191</v>
       </c>
       <c r="G234" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H234" t="s">
-        <v>828</v>
+        <v>763</v>
       </c>
       <c r="I234" t="s">
-        <v>607</v>
-      </c>
-      <c r="J234" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="235" spans="4:10" x14ac:dyDescent="0.25">
+        <v>566</v>
+      </c>
+      <c r="J234" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="235" spans="4:10" ht="51.75">
       <c r="E235" t="s">
         <v>192</v>
       </c>
@@ -6393,10 +6852,13 @@
         <v>309</v>
       </c>
       <c r="H235" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="236" spans="4:10" x14ac:dyDescent="0.25">
+        <v>567</v>
+      </c>
+      <c r="J235" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="236" spans="4:10">
       <c r="E236" t="s">
         <v>193</v>
       </c>
@@ -6404,99 +6866,117 @@
         <v>309</v>
       </c>
       <c r="H236" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="237" spans="4:10" x14ac:dyDescent="0.25">
+        <v>568</v>
+      </c>
+      <c r="J236" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="237" spans="4:10">
       <c r="D237" t="s">
         <v>194</v>
       </c>
       <c r="G237" t="s">
-        <v>738</v>
+        <v>674</v>
       </c>
       <c r="H237" t="s">
-        <v>829</v>
+        <v>764</v>
       </c>
       <c r="I237" t="s">
-        <v>611</v>
-      </c>
-      <c r="J237" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="238" spans="4:10" x14ac:dyDescent="0.25">
+        <v>569</v>
+      </c>
+      <c r="J237" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="238" spans="4:10">
       <c r="E238" t="s">
         <v>195</v>
       </c>
       <c r="G238" t="s">
-        <v>613</v>
+        <v>570</v>
       </c>
       <c r="H238" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="239" spans="4:10" x14ac:dyDescent="0.25">
+        <v>571</v>
+      </c>
+      <c r="J238" s="1" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="239" spans="4:10">
       <c r="E239" t="s">
         <v>196</v>
       </c>
       <c r="G239" t="s">
-        <v>613</v>
+        <v>570</v>
       </c>
       <c r="H239" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="240" spans="4:10" x14ac:dyDescent="0.25">
+        <v>572</v>
+      </c>
+      <c r="J239" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="240" spans="4:10">
       <c r="D240" t="s">
         <v>197</v>
       </c>
       <c r="G240" t="s">
-        <v>739</v>
+        <v>675</v>
       </c>
       <c r="H240" t="s">
-        <v>830</v>
+        <v>765</v>
       </c>
       <c r="I240" t="s">
-        <v>616</v>
-      </c>
-      <c r="J240" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="241" spans="3:10" x14ac:dyDescent="0.25">
+        <v>573</v>
+      </c>
+      <c r="J240" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="241" spans="3:10">
       <c r="E241" t="s">
         <v>198</v>
       </c>
       <c r="G241" t="s">
-        <v>618</v>
+        <v>574</v>
       </c>
       <c r="H241" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="242" spans="3:10" x14ac:dyDescent="0.25">
+        <v>575</v>
+      </c>
+      <c r="J241" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="242" spans="3:10">
       <c r="E242" t="s">
         <v>199</v>
       </c>
       <c r="G242" t="s">
-        <v>618</v>
+        <v>574</v>
       </c>
       <c r="H242" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="243" spans="3:10" x14ac:dyDescent="0.25">
+        <v>576</v>
+      </c>
+      <c r="J242" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="243" spans="3:10">
       <c r="E243" t="s">
         <v>200</v>
       </c>
       <c r="G243" t="s">
-        <v>618</v>
+        <v>574</v>
       </c>
       <c r="H243" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="244" spans="3:10" x14ac:dyDescent="0.25">
+        <v>577</v>
+      </c>
+      <c r="J243" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="244" spans="3:10">
       <c r="C244" t="s">
         <v>270</v>
       </c>
@@ -6504,41 +6984,44 @@
         <v>309</v>
       </c>
       <c r="H244" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="245" spans="3:10" x14ac:dyDescent="0.25">
+        <v>678</v>
+      </c>
+      <c r="J244" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="245" spans="3:10">
       <c r="C245" t="s">
         <v>296</v>
       </c>
       <c r="G245" t="s">
-        <v>719</v>
+        <v>655</v>
       </c>
       <c r="H245" t="s">
-        <v>831</v>
+        <v>766</v>
       </c>
       <c r="I245" t="s">
-        <v>622</v>
-      </c>
-      <c r="J245" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="246" spans="3:10" x14ac:dyDescent="0.25">
+        <v>578</v>
+      </c>
+      <c r="J245" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="246" spans="3:10">
       <c r="D246" t="s">
         <v>201</v>
       </c>
       <c r="G246" t="s">
-        <v>740</v>
+        <v>676</v>
       </c>
       <c r="H246" t="s">
-        <v>832</v>
-      </c>
-      <c r="J246" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="247" spans="3:10" x14ac:dyDescent="0.25">
+        <v>767</v>
+      </c>
+      <c r="J246" s="1" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="247" spans="3:10">
       <c r="E247" t="s">
         <v>202</v>
       </c>
@@ -6546,27 +7029,30 @@
         <v>309</v>
       </c>
       <c r="H247" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="248" spans="3:10" x14ac:dyDescent="0.25">
+        <v>579</v>
+      </c>
+      <c r="J247" s="1" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="248" spans="3:10">
       <c r="D248" t="s">
         <v>297</v>
       </c>
       <c r="G248" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H248" t="s">
-        <v>833</v>
+        <v>768</v>
       </c>
       <c r="I248" t="s">
-        <v>626</v>
-      </c>
-      <c r="J248" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="249" spans="3:10" x14ac:dyDescent="0.25">
+        <v>580</v>
+      </c>
+      <c r="J248" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="249" spans="3:10">
       <c r="E249" t="s">
         <v>203</v>
       </c>
@@ -6574,10 +7060,13 @@
         <v>309</v>
       </c>
       <c r="H249" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="250" spans="3:10" x14ac:dyDescent="0.25">
+        <v>581</v>
+      </c>
+      <c r="J249" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="250" spans="3:10">
       <c r="E250" t="s">
         <v>204</v>
       </c>
@@ -6585,10 +7074,13 @@
         <v>309</v>
       </c>
       <c r="H250" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="251" spans="3:10" x14ac:dyDescent="0.25">
+        <v>582</v>
+      </c>
+      <c r="J250" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="251" spans="3:10">
       <c r="E251" t="s">
         <v>205</v>
       </c>
@@ -6596,27 +7088,30 @@
         <v>309</v>
       </c>
       <c r="H251" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="252" spans="3:10" x14ac:dyDescent="0.25">
+        <v>583</v>
+      </c>
+      <c r="J251" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="252" spans="3:10">
       <c r="D252" t="s">
         <v>206</v>
       </c>
       <c r="G252" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H252" t="s">
-        <v>834</v>
+        <v>769</v>
       </c>
       <c r="I252" t="s">
-        <v>631</v>
-      </c>
-      <c r="J252" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="253" spans="3:10" x14ac:dyDescent="0.25">
+        <v>584</v>
+      </c>
+      <c r="J252" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="253" spans="3:10">
       <c r="E253" t="s">
         <v>207</v>
       </c>
@@ -6624,63 +7119,72 @@
         <v>309</v>
       </c>
       <c r="H253" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="254" spans="3:10" x14ac:dyDescent="0.25">
+        <v>585</v>
+      </c>
+      <c r="J253" s="1" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="254" spans="3:10">
       <c r="D254" t="s">
         <v>208</v>
       </c>
       <c r="G254" t="s">
-        <v>835</v>
+        <v>770</v>
       </c>
       <c r="H254" t="s">
-        <v>836</v>
+        <v>771</v>
       </c>
       <c r="I254" t="s">
-        <v>634</v>
-      </c>
-      <c r="J254" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="255" spans="3:10" x14ac:dyDescent="0.25">
+        <v>586</v>
+      </c>
+      <c r="J254" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="255" spans="3:10">
       <c r="E255" t="s">
         <v>209</v>
       </c>
       <c r="G255" t="s">
-        <v>636</v>
+        <v>588</v>
       </c>
       <c r="H255" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="256" spans="3:10" x14ac:dyDescent="0.25">
+        <v>589</v>
+      </c>
+      <c r="J255" s="1" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="256" spans="3:10">
       <c r="E256" t="s">
         <v>210</v>
       </c>
       <c r="G256" t="s">
-        <v>636</v>
+        <v>588</v>
       </c>
       <c r="H256" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="257" spans="3:10" x14ac:dyDescent="0.25">
+        <v>590</v>
+      </c>
+      <c r="J256" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="257" spans="3:10">
       <c r="D257" t="s">
-        <v>837</v>
+        <v>772</v>
       </c>
       <c r="G257" t="s">
-        <v>741</v>
+        <v>677</v>
       </c>
       <c r="H257" t="s">
-        <v>838</v>
-      </c>
-      <c r="J257" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="258" spans="3:10" x14ac:dyDescent="0.25">
+        <v>773</v>
+      </c>
+      <c r="J257" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="258" spans="3:10">
       <c r="E258" t="s">
         <v>211</v>
       </c>
@@ -6688,10 +7192,13 @@
         <v>309</v>
       </c>
       <c r="H258" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="259" spans="3:10" x14ac:dyDescent="0.25">
+        <v>591</v>
+      </c>
+      <c r="J258" s="1" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="259" spans="3:10">
       <c r="E259" t="s">
         <v>212</v>
       </c>
@@ -6699,10 +7206,13 @@
         <v>309</v>
       </c>
       <c r="H259" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="260" spans="3:10" x14ac:dyDescent="0.25">
+        <v>592</v>
+      </c>
+      <c r="J259" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="260" spans="3:10">
       <c r="E260" t="s">
         <v>213</v>
       </c>
@@ -6710,44 +7220,47 @@
         <v>309</v>
       </c>
       <c r="H260" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="261" spans="3:10" x14ac:dyDescent="0.25">
+        <v>593</v>
+      </c>
+      <c r="J260" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="261" spans="3:10">
       <c r="C261" t="s">
         <v>304</v>
       </c>
       <c r="G261" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H261" t="s">
-        <v>839</v>
+        <v>774</v>
       </c>
       <c r="I261" t="s">
-        <v>643</v>
-      </c>
-      <c r="J261" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="262" spans="3:10" x14ac:dyDescent="0.25">
+        <v>594</v>
+      </c>
+      <c r="J261" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="262" spans="3:10">
       <c r="D262" t="s">
         <v>214</v>
       </c>
       <c r="G262" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H262" t="s">
-        <v>840</v>
+        <v>775</v>
       </c>
       <c r="I262" t="s">
-        <v>645</v>
-      </c>
-      <c r="J262" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="263" spans="3:10" x14ac:dyDescent="0.25">
+        <v>595</v>
+      </c>
+      <c r="J262" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="263" spans="3:10">
       <c r="E263" t="s">
         <v>215</v>
       </c>
@@ -6755,10 +7268,13 @@
         <v>309</v>
       </c>
       <c r="H263" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="264" spans="3:10" x14ac:dyDescent="0.25">
+        <v>596</v>
+      </c>
+      <c r="J263" s="1" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="264" spans="3:10">
       <c r="E264" t="s">
         <v>216</v>
       </c>
@@ -6766,10 +7282,13 @@
         <v>309</v>
       </c>
       <c r="H264" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="265" spans="3:10" x14ac:dyDescent="0.25">
+        <v>597</v>
+      </c>
+      <c r="J264" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="265" spans="3:10">
       <c r="E265" t="s">
         <v>217</v>
       </c>
@@ -6777,10 +7296,13 @@
         <v>309</v>
       </c>
       <c r="H265" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="266" spans="3:10" x14ac:dyDescent="0.25">
+        <v>598</v>
+      </c>
+      <c r="J265" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="266" spans="3:10">
       <c r="E266" t="s">
         <v>218</v>
       </c>
@@ -6788,27 +7310,30 @@
         <v>309</v>
       </c>
       <c r="H266" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="267" spans="3:10" x14ac:dyDescent="0.25">
+        <v>599</v>
+      </c>
+      <c r="J266" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="267" spans="3:10">
       <c r="D267" t="s">
         <v>219</v>
       </c>
       <c r="G267" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H267" t="s">
-        <v>841</v>
+        <v>776</v>
       </c>
       <c r="I267" t="s">
-        <v>651</v>
-      </c>
-      <c r="J267" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="268" spans="3:10" x14ac:dyDescent="0.25">
+        <v>600</v>
+      </c>
+      <c r="J267" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="268" spans="3:10">
       <c r="E268" t="s">
         <v>220</v>
       </c>
@@ -6816,10 +7341,13 @@
         <v>309</v>
       </c>
       <c r="H268" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="269" spans="3:10" x14ac:dyDescent="0.25">
+        <v>601</v>
+      </c>
+      <c r="J268" s="1" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="269" spans="3:10">
       <c r="E269" t="s">
         <v>221</v>
       </c>
@@ -6827,10 +7355,13 @@
         <v>309</v>
       </c>
       <c r="H269" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="270" spans="3:10" x14ac:dyDescent="0.25">
+        <v>602</v>
+      </c>
+      <c r="J269" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="270" spans="3:10">
       <c r="E270" t="s">
         <v>222</v>
       </c>
@@ -6838,10 +7369,13 @@
         <v>309</v>
       </c>
       <c r="H270" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="271" spans="3:10" x14ac:dyDescent="0.25">
+        <v>603</v>
+      </c>
+      <c r="J270" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="271" spans="3:10">
       <c r="D271" t="s">
         <v>278</v>
       </c>
@@ -6849,44 +7383,47 @@
         <v>309</v>
       </c>
       <c r="H271" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="272" spans="3:10" x14ac:dyDescent="0.25">
+        <v>604</v>
+      </c>
+      <c r="J271" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="272" spans="3:10">
       <c r="C272" t="s">
         <v>223</v>
       </c>
       <c r="G272" t="s">
-        <v>738</v>
+        <v>674</v>
       </c>
       <c r="H272" t="s">
-        <v>842</v>
+        <v>777</v>
       </c>
       <c r="I272" t="s">
-        <v>657</v>
-      </c>
-      <c r="J272" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="273" spans="3:10" x14ac:dyDescent="0.25">
+        <v>605</v>
+      </c>
+      <c r="J272" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="273" spans="3:10">
       <c r="D273" t="s">
         <v>224</v>
       </c>
       <c r="G273" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H273" t="s">
-        <v>843</v>
+        <v>778</v>
       </c>
       <c r="I273" t="s">
-        <v>659</v>
-      </c>
-      <c r="J273" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="274" spans="3:10" x14ac:dyDescent="0.25">
+        <v>606</v>
+      </c>
+      <c r="J273" s="1" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="274" spans="3:10">
       <c r="E274" t="s">
         <v>225</v>
       </c>
@@ -6894,10 +7431,13 @@
         <v>309</v>
       </c>
       <c r="H274" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="275" spans="3:10" x14ac:dyDescent="0.25">
+        <v>607</v>
+      </c>
+      <c r="J274" s="1" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="275" spans="3:10">
       <c r="E275" t="s">
         <v>226</v>
       </c>
@@ -6905,10 +7445,13 @@
         <v>309</v>
       </c>
       <c r="H275" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="276" spans="3:10" x14ac:dyDescent="0.25">
+        <v>608</v>
+      </c>
+      <c r="J275" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="276" spans="3:10">
       <c r="E276" t="s">
         <v>227</v>
       </c>
@@ -6916,21 +7459,27 @@
         <v>309</v>
       </c>
       <c r="H276" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="277" spans="3:10" x14ac:dyDescent="0.25">
+        <v>609</v>
+      </c>
+      <c r="J276" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="277" spans="3:10">
       <c r="D277" t="s">
         <v>228</v>
       </c>
       <c r="G277" t="s">
-        <v>754</v>
+        <v>690</v>
       </c>
       <c r="H277" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="278" spans="3:10" x14ac:dyDescent="0.25">
+        <v>779</v>
+      </c>
+      <c r="J277" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="278" spans="3:10">
       <c r="E278" t="s">
         <v>229</v>
       </c>
@@ -6938,10 +7487,13 @@
         <v>309</v>
       </c>
       <c r="H278" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="279" spans="3:10" x14ac:dyDescent="0.25">
+        <v>610</v>
+      </c>
+      <c r="J278" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="279" spans="3:10">
       <c r="D279" t="s">
         <v>230</v>
       </c>
@@ -6949,13 +7501,16 @@
         <v>309</v>
       </c>
       <c r="H279" t="s">
-        <v>665</v>
+        <v>611</v>
       </c>
       <c r="I279" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="280" spans="3:10" x14ac:dyDescent="0.25">
+        <v>605</v>
+      </c>
+      <c r="J279" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="280" spans="3:10">
       <c r="D280" t="s">
         <v>231</v>
       </c>
@@ -6963,27 +7518,30 @@
         <v>309</v>
       </c>
       <c r="H280" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="281" spans="3:10" x14ac:dyDescent="0.25">
+        <v>612</v>
+      </c>
+      <c r="J280" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="281" spans="3:10">
       <c r="C281" t="s">
         <v>305</v>
       </c>
       <c r="G281" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H281" t="s">
-        <v>845</v>
+        <v>780</v>
       </c>
       <c r="I281" t="s">
-        <v>667</v>
-      </c>
-      <c r="J281" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="282" spans="3:10" x14ac:dyDescent="0.25">
+        <v>613</v>
+      </c>
+      <c r="J281" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="282" spans="3:10">
       <c r="D282" t="s">
         <v>232</v>
       </c>
@@ -6991,16 +7549,16 @@
         <v>309</v>
       </c>
       <c r="H282" t="s">
-        <v>846</v>
+        <v>781</v>
       </c>
       <c r="I282" t="s">
-        <v>669</v>
-      </c>
-      <c r="J282" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="283" spans="3:10" x14ac:dyDescent="0.25">
+        <v>615</v>
+      </c>
+      <c r="J282" s="1" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="283" spans="3:10">
       <c r="E283" t="s">
         <v>233</v>
       </c>
@@ -7008,49 +7566,58 @@
         <v>309</v>
       </c>
       <c r="H283" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="284" spans="3:10" x14ac:dyDescent="0.25">
+        <v>616</v>
+      </c>
+      <c r="J283" s="1" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="284" spans="3:10">
       <c r="E284" t="s">
         <v>234</v>
       </c>
       <c r="G284" t="s">
-        <v>672</v>
+        <v>617</v>
       </c>
       <c r="H284" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="285" spans="3:10" x14ac:dyDescent="0.25">
+        <v>618</v>
+      </c>
+      <c r="J284" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="285" spans="3:10">
       <c r="E285" t="s">
         <v>235</v>
       </c>
       <c r="G285" t="s">
-        <v>672</v>
+        <v>617</v>
       </c>
       <c r="H285" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="286" spans="3:10" x14ac:dyDescent="0.25">
+        <v>619</v>
+      </c>
+      <c r="J285" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="286" spans="3:10">
       <c r="D286" t="s">
         <v>236</v>
       </c>
       <c r="G286" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H286" t="s">
-        <v>847</v>
+        <v>782</v>
       </c>
       <c r="I286" t="s">
-        <v>667</v>
-      </c>
-      <c r="J286" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="287" spans="3:10" x14ac:dyDescent="0.25">
+        <v>613</v>
+      </c>
+      <c r="J286" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="287" spans="3:10">
       <c r="E287" t="s">
         <v>237</v>
       </c>
@@ -7058,10 +7625,13 @@
         <v>309</v>
       </c>
       <c r="H287" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="288" spans="3:10" x14ac:dyDescent="0.25">
+        <v>620</v>
+      </c>
+      <c r="J287" s="1" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="288" spans="3:10">
       <c r="E288" t="s">
         <v>238</v>
       </c>
@@ -7069,10 +7639,13 @@
         <v>309</v>
       </c>
       <c r="H288" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="289" spans="3:10" x14ac:dyDescent="0.25">
+        <v>621</v>
+      </c>
+      <c r="J288" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="289" spans="3:10">
       <c r="E289" t="s">
         <v>239</v>
       </c>
@@ -7080,10 +7653,13 @@
         <v>309</v>
       </c>
       <c r="H289" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="290" spans="3:10" x14ac:dyDescent="0.25">
+        <v>622</v>
+      </c>
+      <c r="J289" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="290" spans="3:10">
       <c r="D290" t="s">
         <v>240</v>
       </c>
@@ -7091,30 +7667,33 @@
         <v>309</v>
       </c>
       <c r="H290" t="s">
-        <v>679</v>
+        <v>623</v>
       </c>
       <c r="I290" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="291" spans="3:10" x14ac:dyDescent="0.25">
+        <v>613</v>
+      </c>
+      <c r="J290" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="291" spans="3:10">
       <c r="D291" t="s">
         <v>241</v>
       </c>
       <c r="G291" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H291" t="s">
-        <v>848</v>
+        <v>783</v>
       </c>
       <c r="I291" t="s">
-        <v>680</v>
-      </c>
-      <c r="J291" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="292" spans="3:10" x14ac:dyDescent="0.25">
+        <v>624</v>
+      </c>
+      <c r="J291" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="292" spans="3:10">
       <c r="E292" t="s">
         <v>242</v>
       </c>
@@ -7122,27 +7701,30 @@
         <v>309</v>
       </c>
       <c r="H292" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="293" spans="3:10" x14ac:dyDescent="0.25">
+        <v>625</v>
+      </c>
+      <c r="J292" s="1" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="293" spans="3:10">
       <c r="C293" t="s">
         <v>271</v>
       </c>
       <c r="G293" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H293" t="s">
-        <v>849</v>
+        <v>784</v>
       </c>
       <c r="I293" t="s">
-        <v>683</v>
-      </c>
-      <c r="J293" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="294" spans="3:10" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="J293" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="294" spans="3:10">
       <c r="D294" t="s">
         <v>230</v>
       </c>
@@ -7150,44 +7732,47 @@
         <v>309</v>
       </c>
       <c r="H294" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="295" spans="3:10" x14ac:dyDescent="0.25">
+        <v>611</v>
+      </c>
+      <c r="J294" s="1" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="295" spans="3:10">
       <c r="C295" t="s">
         <v>306</v>
       </c>
       <c r="G295" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H295" t="s">
-        <v>850</v>
+        <v>785</v>
       </c>
       <c r="I295" t="s">
-        <v>685</v>
-      </c>
-      <c r="J295" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="296" spans="3:10" x14ac:dyDescent="0.25">
+        <v>627</v>
+      </c>
+      <c r="J295" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="296" spans="3:10">
       <c r="D296" t="s">
-        <v>851</v>
+        <v>786</v>
       </c>
       <c r="G296" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H296" t="s">
-        <v>852</v>
+        <v>787</v>
       </c>
       <c r="I296" t="s">
-        <v>687</v>
-      </c>
-      <c r="J296" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="297" spans="3:10" x14ac:dyDescent="0.25">
+        <v>628</v>
+      </c>
+      <c r="J296" s="1" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="297" spans="3:10">
       <c r="E297" t="s">
         <v>243</v>
       </c>
@@ -7195,10 +7780,13 @@
         <v>309</v>
       </c>
       <c r="H297" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="298" spans="3:10" x14ac:dyDescent="0.25">
+        <v>596</v>
+      </c>
+      <c r="J297" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="298" spans="3:10">
       <c r="E298" t="s">
         <v>244</v>
       </c>
@@ -7206,10 +7794,13 @@
         <v>309</v>
       </c>
       <c r="H298" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="299" spans="3:10" x14ac:dyDescent="0.25">
+        <v>597</v>
+      </c>
+      <c r="J298" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="299" spans="3:10">
       <c r="E299" t="s">
         <v>245</v>
       </c>
@@ -7217,27 +7808,30 @@
         <v>309</v>
       </c>
       <c r="H299" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="300" spans="3:10" x14ac:dyDescent="0.25">
+        <v>598</v>
+      </c>
+      <c r="J299" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="300" spans="3:10">
       <c r="D300" t="s">
-        <v>853</v>
+        <v>788</v>
       </c>
       <c r="G300" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H300" t="s">
-        <v>854</v>
+        <v>789</v>
       </c>
       <c r="I300" t="s">
-        <v>689</v>
-      </c>
-      <c r="J300" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="301" spans="3:10" x14ac:dyDescent="0.25">
+        <v>629</v>
+      </c>
+      <c r="J300" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="301" spans="3:10">
       <c r="E301" t="s">
         <v>246</v>
       </c>
@@ -7245,10 +7839,13 @@
         <v>309</v>
       </c>
       <c r="H301" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="302" spans="3:10" x14ac:dyDescent="0.25">
+        <v>631</v>
+      </c>
+      <c r="J301" s="1" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="302" spans="3:10">
       <c r="E302" t="s">
         <v>247</v>
       </c>
@@ -7256,10 +7853,13 @@
         <v>309</v>
       </c>
       <c r="H302" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="303" spans="3:10" x14ac:dyDescent="0.25">
+        <v>632</v>
+      </c>
+      <c r="J302" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="303" spans="3:10">
       <c r="E303" t="s">
         <v>248</v>
       </c>
@@ -7267,132 +7867,159 @@
         <v>309</v>
       </c>
       <c r="H303" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="304" spans="3:10" x14ac:dyDescent="0.25">
+        <v>633</v>
+      </c>
+      <c r="J303" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="304" spans="3:10">
       <c r="D304" t="s">
         <v>249</v>
       </c>
       <c r="G304" t="s">
-        <v>718</v>
+        <v>654</v>
       </c>
       <c r="H304" t="s">
-        <v>855</v>
+        <v>790</v>
       </c>
       <c r="I304" t="s">
-        <v>694</v>
-      </c>
-      <c r="J304" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="305" spans="3:10" x14ac:dyDescent="0.25">
+        <v>634</v>
+      </c>
+      <c r="J304" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="305" spans="3:10">
       <c r="E305" t="s">
         <v>250</v>
       </c>
       <c r="G305" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="H305" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="306" spans="3:10" x14ac:dyDescent="0.25">
+        <v>635</v>
+      </c>
+      <c r="J305" s="1" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="306" spans="3:10">
       <c r="E306" t="s">
         <v>251</v>
       </c>
       <c r="G306" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="H306" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="307" spans="3:10" x14ac:dyDescent="0.25">
+        <v>636</v>
+      </c>
+      <c r="J306" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="307" spans="3:10">
       <c r="E307" t="s">
         <v>252</v>
       </c>
       <c r="G307" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="H307" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="308" spans="3:10" x14ac:dyDescent="0.25">
+        <v>637</v>
+      </c>
+      <c r="J307" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="308" spans="3:10">
       <c r="E308" t="s">
         <v>253</v>
       </c>
       <c r="G308" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="H308" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="309" spans="3:10" x14ac:dyDescent="0.25">
+        <v>638</v>
+      </c>
+      <c r="J308" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="309" spans="3:10">
       <c r="E309" t="s">
         <v>254</v>
       </c>
       <c r="G309" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="H309" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="310" spans="3:10" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="J309" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="310" spans="3:10">
       <c r="D310" t="s">
         <v>255</v>
       </c>
       <c r="G310" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="H310" t="s">
-        <v>701</v>
+        <v>640</v>
       </c>
       <c r="I310" t="s">
-        <v>702</v>
-      </c>
-      <c r="J310" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="311" spans="3:10" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+      <c r="J310" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="311" spans="3:10">
       <c r="E311" t="s">
         <v>256</v>
       </c>
       <c r="G311" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="H311" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="312" spans="3:10" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+      <c r="J311" s="1" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="312" spans="3:10">
       <c r="E312" t="s">
         <v>257</v>
       </c>
       <c r="G312" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="H312" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="313" spans="3:10" x14ac:dyDescent="0.25">
+        <v>643</v>
+      </c>
+      <c r="J312" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="313" spans="3:10">
       <c r="E313" t="s">
         <v>258</v>
       </c>
       <c r="G313" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="H313" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="314" spans="3:10" x14ac:dyDescent="0.25">
+        <v>644</v>
+      </c>
+      <c r="J313" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="314" spans="3:10">
       <c r="D314" t="s">
         <v>259</v>
       </c>
@@ -7400,30 +8027,33 @@
         <v>309</v>
       </c>
       <c r="H314" t="s">
-        <v>707</v>
+        <v>645</v>
       </c>
       <c r="I314" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="315" spans="3:10" x14ac:dyDescent="0.25">
+        <v>627</v>
+      </c>
+      <c r="J314" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="315" spans="3:10">
       <c r="C315" t="s">
         <v>260</v>
       </c>
       <c r="G315" t="s">
-        <v>715</v>
+        <v>651</v>
       </c>
       <c r="H315" t="s">
-        <v>856</v>
+        <v>791</v>
       </c>
       <c r="I315" t="s">
-        <v>473</v>
-      </c>
-      <c r="J315" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="316" spans="3:10" x14ac:dyDescent="0.25">
+        <v>448</v>
+      </c>
+      <c r="J315" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="316" spans="3:10">
       <c r="D316" t="s">
         <v>188</v>
       </c>
@@ -7431,10 +8061,13 @@
         <v>309</v>
       </c>
       <c r="H316" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="317" spans="3:10" x14ac:dyDescent="0.25">
+        <v>563</v>
+      </c>
+      <c r="J316" s="1" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="317" spans="3:10">
       <c r="C317" t="s">
         <v>261</v>
       </c>
@@ -7442,41 +8075,47 @@
         <v>309</v>
       </c>
       <c r="H317" t="s">
-        <v>709</v>
+        <v>646</v>
       </c>
       <c r="I317" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="318" spans="3:10" x14ac:dyDescent="0.25">
+        <v>448</v>
+      </c>
+      <c r="J317" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="318" spans="3:10">
       <c r="C318" t="s">
         <v>262</v>
       </c>
       <c r="G318" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="H318" t="s">
-        <v>857</v>
+        <v>792</v>
       </c>
       <c r="I318" t="s">
-        <v>710</v>
-      </c>
-      <c r="J318" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="319" spans="3:10" x14ac:dyDescent="0.25">
+        <v>647</v>
+      </c>
+      <c r="J318" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="319" spans="3:10">
       <c r="D319" t="s">
-        <v>858</v>
+        <v>793</v>
       </c>
       <c r="G319" t="s">
-        <v>754</v>
+        <v>690</v>
       </c>
       <c r="H319" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="320" spans="3:10" x14ac:dyDescent="0.25">
+        <v>794</v>
+      </c>
+      <c r="J319" s="1" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="320" spans="3:10">
       <c r="D320" t="s">
         <v>263</v>
       </c>
@@ -7484,10 +8123,13 @@
         <v>309</v>
       </c>
       <c r="H320" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="321" spans="4:8" x14ac:dyDescent="0.25">
+        <v>648</v>
+      </c>
+      <c r="J320" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="321" spans="4:10">
       <c r="D321" t="s">
         <v>264</v>
       </c>
@@ -7495,7 +8137,190 @@
         <v>309</v>
       </c>
       <c r="H321" t="s">
-        <v>713</v>
+        <v>649</v>
+      </c>
+      <c r="J321" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="322" spans="4:10">
+      <c r="J322" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="323" spans="4:10">
+      <c r="J323" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="324" spans="4:10">
+      <c r="J324" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="325" spans="4:10">
+      <c r="J325" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="326" spans="4:10">
+      <c r="J326" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="327" spans="4:10">
+      <c r="J327" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="328" spans="4:10">
+      <c r="J328" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="329" spans="4:10">
+      <c r="J329" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="330" spans="4:10">
+      <c r="J330" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="331" spans="4:10">
+      <c r="J331" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="332" spans="4:10">
+      <c r="J332" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="333" spans="4:10">
+      <c r="J333" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="334" spans="4:10">
+      <c r="J334" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="335" spans="4:10">
+      <c r="J335" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="336" spans="4:10">
+      <c r="J336" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="337" spans="10:10">
+      <c r="J337" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="338" spans="10:10">
+      <c r="J338" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="339" spans="10:10">
+      <c r="J339" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="340" spans="10:10">
+      <c r="J340" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="341" spans="10:10">
+      <c r="J341" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="342" spans="10:10">
+      <c r="J342" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="343" spans="10:10">
+      <c r="J343" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="344" spans="10:10">
+      <c r="J344" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="345" spans="10:10">
+      <c r="J345" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="346" spans="10:10">
+      <c r="J346" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="347" spans="10:10">
+      <c r="J347" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="348" spans="10:10">
+      <c r="J348" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="349" spans="10:10">
+      <c r="J349" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="350" spans="10:10">
+      <c r="J350" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="351" spans="10:10">
+      <c r="J351" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="352" spans="10:10">
+      <c r="J352" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="353" spans="10:10">
+      <c r="J353" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="354" spans="10:10">
+      <c r="J354" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="355" spans="10:10">
+      <c r="J355" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="356" spans="10:10">
+      <c r="J356" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="357" spans="10:10">
+      <c r="J357" s="1" t="s">
+        <v>678</v>
       </c>
     </row>
   </sheetData>
